--- a/resources/metadata_process_scripts/sources/catalog.xlsx
+++ b/resources/metadata_process_scripts/sources/catalog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12228" uniqueCount="2437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12280" uniqueCount="2449">
   <si>
     <t>ds:DatName</t>
   </si>
@@ -6705,6 +6705,9 @@
     <t>ds:prjURL</t>
   </si>
   <si>
+    <t>ds:prjWebpage</t>
+  </si>
+  <si>
     <t>ds:prjKeywords</t>
   </si>
   <si>
@@ -6963,13 +6966,19 @@
     <t>https://ds.datascientia.eu/community/public/projects/1e465a20-1650-42f7-88d4-d7b1b8ed6bb3</t>
   </si>
   <si>
-    <t>https://ds.datascientia.eu/community/public/projects/</t>
+    <t>https://ds.datascientia.eu/community/public/projects/2f39ee2e-4012-4fa8-9794-a56bce243d3e</t>
   </si>
   <si>
     <t>https://ds.datascientia.eu/community/public/projects/896bbb55-5ee2-4653-9b43-69cc88633ec8</t>
   </si>
   <si>
-    <t>https://datascientia.disi.unitn.it/projects/su2osm/</t>
+    <t>https://ds.datascientia.eu/community/public/projects/8b227ff7-803e-4f7b-8765-75ea2b7a8113</t>
+  </si>
+  <si>
+    <t>https://datascientia.disi.unitn.it/projects/su2/</t>
+  </si>
+  <si>
+    <t>https://datascientia.disi.unitn.it/projects/diversityone/</t>
   </si>
   <si>
     <t>Academic Performance, Daily Routines, Lifestyle, Smartphone data, Sensor data</t>
@@ -6987,9 +6996,15 @@
     <t>Diversity, Social Practices, Eating Habits, Smartphone data, Sensor data</t>
   </si>
   <si>
+    <t>Big-Thick Data, Human Behaviors, Observation Context, Reference Context, Personal Context</t>
+  </si>
+  <si>
     <t>Data collection</t>
   </si>
   <si>
+    <t>Data Collection, Data Integration</t>
+  </si>
+  <si>
     <t>The Wenet Chat Application 1 project was based on a chatbot that collected questions and answers from university students in Italy, Denmark, Paraguay, the United Kingdom, and Mongolia. It was conducted in March and June 2021 to improve the knowledge about students' lives to promote the design of better and more targeted technology and support tools for students. It was a European Union WeNet Horizon 2020-funded project with the overall goal of developing a diversity-aware, machine-mediated paradigm for social interactions. Data was collected with a Telegram App and the i-Log Application. Some of the data collected included the respondent’s career information (department, study course, study year,) and demographics (age, gender…). Questions were sent on the Telegram App and user answers were recorded, the i-Log App recorded sensor data (such as location, accelerometer…) from the user device. This data was collected in three phases, the first phase entailed interacting with the Telegram App Ask4Help, and sensor data was also collected during this phase. The second phase involved respondents answering a questionnaire, and in the third phase, they participated in a focus group to provide feedback.</t>
   </si>
   <si>
@@ -7017,15 +7032,18 @@
     <t>European Union’s Horizon 2020 WeNet project, under grant agreement 823786</t>
   </si>
   <si>
+    <t>European Union’s Horizon 2020 WeNet project, under grant agreement 823784</t>
+  </si>
+  <si>
     <t>European Union’s Horizon 2020 WeNet project, under grant agreement 823789</t>
   </si>
   <si>
+    <t>Datasets</t>
+  </si>
+  <si>
     <t>Datasets, Publications</t>
   </si>
   <si>
-    <t>Datasets</t>
-  </si>
-  <si>
     <t>Fausto Giunchiglia</t>
   </si>
   <si>
@@ -7050,6 +7068,9 @@
     <t>Ivano Bison</t>
   </si>
   <si>
+    <t>Amarsanaa Ganbold</t>
+  </si>
+  <si>
     <t>Phan Thanh Trung</t>
   </si>
   <si>
@@ -7089,12 +7110,18 @@
     <t>Ronald Chenu Abente Acosta, Matteo Busso, Marcelo Rodas Britez, Andrea Bontempelli, Fausto Giunchiglia</t>
   </si>
   <si>
+    <t>Altangerel Chagnaa, Tsolmon Zundui</t>
+  </si>
+  <si>
     <t>Pham Doan Hai Phu</t>
   </si>
   <si>
     <t>Athina Zoe, George Papagiannitsis</t>
   </si>
   <si>
+    <t>Xiaoyue Li</t>
+  </si>
+  <si>
     <t>Trento (Italy)</t>
   </si>
   <si>
@@ -7134,6 +7161,9 @@
     <t>Questionnaire, Chat Application, Focus Group</t>
   </si>
   <si>
+    <t>Intensive Longitudinal Survey, Phone Sensors, Human Annotators in OpenStreetMap</t>
+  </si>
+  <si>
     <t>CER UniTrento</t>
   </si>
   <si>
@@ -7155,6 +7185,9 @@
     <t>Instituto Potosino de Investigación Científica y Tecnológica</t>
   </si>
   <si>
+    <t>National University of Mongolia</t>
+  </si>
+  <si>
     <t>FPT University</t>
   </si>
   <si>
@@ -7186,6 +7219,9 @@
   </si>
   <si>
     <t>Giunchiglia, F., Bison, I., Busso, M., Chenu-Abente, R., Rodas Britez, M. D., de Götzen, A., ... &amp; Sierra, C. (2022). A worldwide diversity chat application pilot on interactions and social practices (2021-2nd Wave).</t>
+  </si>
+  <si>
+    <t>Giunchiglia, F., Xiaoyue, L. Big-Thick Data generation via reference and personal context unification, 27TH European Conference on Artificial Intelligence (2024).</t>
   </si>
   <si>
     <t>002.AAAB.AAA.**</t>
@@ -27740,7 +27776,7 @@
         <v>1021</v>
       </c>
       <c r="X252" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y252" s="3">
         <v>44176</v>
@@ -27779,7 +27815,7 @@
         <v>1</v>
       </c>
       <c r="AQ252" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR252" t="s">
         <v>1862</v>
@@ -27820,7 +27856,7 @@
         <v>1021</v>
       </c>
       <c r="X253" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y253" s="3">
         <v>44176</v>
@@ -27859,7 +27895,7 @@
         <v>1</v>
       </c>
       <c r="AQ253" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR253" t="s">
         <v>1862</v>
@@ -27900,7 +27936,7 @@
         <v>1022</v>
       </c>
       <c r="X254" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y254" s="3">
         <v>44176</v>
@@ -27939,7 +27975,7 @@
         <v>1</v>
       </c>
       <c r="AQ254" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR254" t="s">
         <v>1862</v>
@@ -27980,7 +28016,7 @@
         <v>1023</v>
       </c>
       <c r="X255" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y255" s="3">
         <v>44176</v>
@@ -28019,7 +28055,7 @@
         <v>1</v>
       </c>
       <c r="AQ255" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR255" t="s">
         <v>1862</v>
@@ -28060,7 +28096,7 @@
         <v>1022</v>
       </c>
       <c r="X256" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y256" s="3">
         <v>44176</v>
@@ -28099,7 +28135,7 @@
         <v>1</v>
       </c>
       <c r="AQ256" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR256" t="s">
         <v>1862</v>
@@ -28140,7 +28176,7 @@
         <v>1022</v>
       </c>
       <c r="X257" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y257" s="3">
         <v>44176</v>
@@ -28179,7 +28215,7 @@
         <v>1</v>
       </c>
       <c r="AQ257" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR257" t="s">
         <v>1862</v>
@@ -28220,7 +28256,7 @@
         <v>1024</v>
       </c>
       <c r="X258" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y258" s="3">
         <v>44176</v>
@@ -28259,7 +28295,7 @@
         <v>1</v>
       </c>
       <c r="AQ258" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR258" t="s">
         <v>1862</v>
@@ -28300,7 +28336,7 @@
         <v>1024</v>
       </c>
       <c r="X259" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y259" s="3">
         <v>44176</v>
@@ -28339,7 +28375,7 @@
         <v>1</v>
       </c>
       <c r="AQ259" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR259" t="s">
         <v>1862</v>
@@ -28380,7 +28416,7 @@
         <v>1022</v>
       </c>
       <c r="X260" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y260" s="3">
         <v>44176</v>
@@ -28419,7 +28455,7 @@
         <v>1</v>
       </c>
       <c r="AQ260" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR260" t="s">
         <v>1862</v>
@@ -28460,7 +28496,7 @@
         <v>1021</v>
       </c>
       <c r="X261" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y261" s="3">
         <v>44176</v>
@@ -28499,7 +28535,7 @@
         <v>1</v>
       </c>
       <c r="AQ261" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR261" t="s">
         <v>1862</v>
@@ -28540,7 +28576,7 @@
         <v>1023</v>
       </c>
       <c r="X262" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y262" s="3">
         <v>44176</v>
@@ -28579,7 +28615,7 @@
         <v>1</v>
       </c>
       <c r="AQ262" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR262" t="s">
         <v>1862</v>
@@ -28620,7 +28656,7 @@
         <v>1025</v>
       </c>
       <c r="X263" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y263" s="3">
         <v>44176</v>
@@ -28659,7 +28695,7 @@
         <v>1</v>
       </c>
       <c r="AQ263" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR263" t="s">
         <v>1862</v>
@@ -28700,7 +28736,7 @@
         <v>1026</v>
       </c>
       <c r="X264" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y264" s="3">
         <v>44176</v>
@@ -28739,7 +28775,7 @@
         <v>1</v>
       </c>
       <c r="AQ264" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR264" t="s">
         <v>1862</v>
@@ -28780,7 +28816,7 @@
         <v>1026</v>
       </c>
       <c r="X265" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y265" s="3">
         <v>44176</v>
@@ -28819,7 +28855,7 @@
         <v>1</v>
       </c>
       <c r="AQ265" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR265" t="s">
         <v>1862</v>
@@ -28860,7 +28896,7 @@
         <v>1026</v>
       </c>
       <c r="X266" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y266" s="3">
         <v>44176</v>
@@ -28899,7 +28935,7 @@
         <v>1</v>
       </c>
       <c r="AQ266" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR266" t="s">
         <v>1862</v>
@@ -28940,7 +28976,7 @@
         <v>1023</v>
       </c>
       <c r="X267" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y267" s="3">
         <v>44176</v>
@@ -28979,7 +29015,7 @@
         <v>1</v>
       </c>
       <c r="AQ267" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR267" t="s">
         <v>1862</v>
@@ -29020,7 +29056,7 @@
         <v>1023</v>
       </c>
       <c r="X268" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y268" s="3">
         <v>44176</v>
@@ -29059,7 +29095,7 @@
         <v>1</v>
       </c>
       <c r="AQ268" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR268" t="s">
         <v>1862</v>
@@ -29100,7 +29136,7 @@
         <v>1025</v>
       </c>
       <c r="X269" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y269" s="3">
         <v>44176</v>
@@ -29139,7 +29175,7 @@
         <v>1</v>
       </c>
       <c r="AQ269" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR269" t="s">
         <v>1862</v>
@@ -29180,7 +29216,7 @@
         <v>1026</v>
       </c>
       <c r="X270" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y270" s="3">
         <v>44176</v>
@@ -29219,7 +29255,7 @@
         <v>1</v>
       </c>
       <c r="AQ270" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR270" t="s">
         <v>1862</v>
@@ -29257,7 +29293,7 @@
         <v>1019</v>
       </c>
       <c r="X271" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y271" s="3">
         <v>44176</v>
@@ -29296,7 +29332,7 @@
         <v>1</v>
       </c>
       <c r="AQ271" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR271" t="s">
         <v>1862</v>
@@ -29334,7 +29370,7 @@
         <v>1019</v>
       </c>
       <c r="X272" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y272" s="3">
         <v>44176</v>
@@ -29373,7 +29409,7 @@
         <v>1</v>
       </c>
       <c r="AQ272" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR272" t="s">
         <v>1862</v>
@@ -29411,7 +29447,7 @@
         <v>1019</v>
       </c>
       <c r="X273" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y273" s="3">
         <v>44176</v>
@@ -29450,7 +29486,7 @@
         <v>1</v>
       </c>
       <c r="AQ273" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR273" t="s">
         <v>1862</v>
@@ -29491,7 +29527,7 @@
         <v>1022</v>
       </c>
       <c r="X274" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y274" s="3">
         <v>44176</v>
@@ -29530,7 +29566,7 @@
         <v>1</v>
       </c>
       <c r="AQ274" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR274" t="s">
         <v>1862</v>
@@ -29571,7 +29607,7 @@
         <v>1022</v>
       </c>
       <c r="X275" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y275" s="3">
         <v>44176</v>
@@ -29610,7 +29646,7 @@
         <v>1</v>
       </c>
       <c r="AQ275" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR275" t="s">
         <v>1862</v>
@@ -29651,7 +29687,7 @@
         <v>1021</v>
       </c>
       <c r="X276" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y276" s="3">
         <v>44176</v>
@@ -29690,7 +29726,7 @@
         <v>1</v>
       </c>
       <c r="AQ276" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR276" t="s">
         <v>1862</v>
@@ -29731,7 +29767,7 @@
         <v>1021</v>
       </c>
       <c r="X277" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y277" s="3">
         <v>44176</v>
@@ -29770,7 +29806,7 @@
         <v>1</v>
       </c>
       <c r="AQ277" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR277" t="s">
         <v>1862</v>
@@ -29808,7 +29844,7 @@
         <v>1020</v>
       </c>
       <c r="X278" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y278" s="3">
         <v>44176</v>
@@ -29847,7 +29883,7 @@
         <v>1</v>
       </c>
       <c r="AQ278" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR278" t="s">
         <v>1862</v>
@@ -29888,7 +29924,7 @@
         <v>1022</v>
       </c>
       <c r="X279" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y279" s="3">
         <v>44176</v>
@@ -29927,7 +29963,7 @@
         <v>1</v>
       </c>
       <c r="AQ279" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR279" t="s">
         <v>1862</v>
@@ -29968,7 +30004,7 @@
         <v>1022</v>
       </c>
       <c r="X280" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y280" s="3">
         <v>44176</v>
@@ -30007,7 +30043,7 @@
         <v>1</v>
       </c>
       <c r="AQ280" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR280" t="s">
         <v>1862</v>
@@ -30048,7 +30084,7 @@
         <v>1024</v>
       </c>
       <c r="X281" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y281" s="3">
         <v>44176</v>
@@ -30087,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AQ281" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR281" t="s">
         <v>1862</v>
@@ -30128,7 +30164,7 @@
         <v>1024</v>
       </c>
       <c r="X282" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y282" s="3">
         <v>44176</v>
@@ -30167,7 +30203,7 @@
         <v>1</v>
       </c>
       <c r="AQ282" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR282" t="s">
         <v>1862</v>
@@ -48331,7 +48367,7 @@
         <v>2121</v>
       </c>
       <c r="X75" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y75" s="3">
         <v>44176</v>
@@ -48361,7 +48397,7 @@
         <v>1</v>
       </c>
       <c r="AQ75" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR75" t="s">
         <v>1862</v>
@@ -48399,7 +48435,7 @@
         <v>2121</v>
       </c>
       <c r="X76" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y76" s="3">
         <v>44176</v>
@@ -48429,7 +48465,7 @@
         <v>1</v>
       </c>
       <c r="AQ76" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR76" t="s">
         <v>1862</v>
@@ -48467,7 +48503,7 @@
         <v>2121</v>
       </c>
       <c r="X77" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y77" s="3">
         <v>44176</v>
@@ -48497,7 +48533,7 @@
         <v>1</v>
       </c>
       <c r="AQ77" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR77" t="s">
         <v>1862</v>
@@ -48535,7 +48571,7 @@
         <v>2121</v>
       </c>
       <c r="X78" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y78" s="3">
         <v>44176</v>
@@ -48565,7 +48601,7 @@
         <v>1</v>
       </c>
       <c r="AQ78" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR78" t="s">
         <v>1862</v>
@@ -48603,7 +48639,7 @@
         <v>1020</v>
       </c>
       <c r="X79" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y79" s="3">
         <v>44176</v>
@@ -48633,7 +48669,7 @@
         <v>1</v>
       </c>
       <c r="AQ79" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR79" t="s">
         <v>1862</v>
@@ -48671,7 +48707,7 @@
         <v>2121</v>
       </c>
       <c r="X80" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y80" s="3">
         <v>44176</v>
@@ -48701,7 +48737,7 @@
         <v>1</v>
       </c>
       <c r="AQ80" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR80" t="s">
         <v>1862</v>
@@ -48739,7 +48775,7 @@
         <v>2121</v>
       </c>
       <c r="X81" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y81" s="3">
         <v>44176</v>
@@ -48769,7 +48805,7 @@
         <v>1</v>
       </c>
       <c r="AQ81" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR81" t="s">
         <v>1862</v>
@@ -48807,7 +48843,7 @@
         <v>2121</v>
       </c>
       <c r="X82" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y82" s="3">
         <v>44176</v>
@@ -48837,7 +48873,7 @@
         <v>1</v>
       </c>
       <c r="AQ82" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR82" t="s">
         <v>1862</v>
@@ -48875,7 +48911,7 @@
         <v>1019</v>
       </c>
       <c r="X83" s="3">
-        <v>44151</v>
+        <v>44102</v>
       </c>
       <c r="Y83" s="3">
         <v>44176</v>
@@ -48905,7 +48941,7 @@
         <v>1</v>
       </c>
       <c r="AQ83" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AR83" t="s">
         <v>1862</v>
@@ -53496,10 +53532,10 @@
         <v>1020</v>
       </c>
       <c r="X151" s="3">
-        <v>43227</v>
+        <v>45436</v>
       </c>
       <c r="Y151" s="3">
-        <v>43258</v>
+        <v>45528</v>
       </c>
       <c r="Z151">
         <v>3</v>
@@ -53697,10 +53733,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO26"/>
+  <dimension ref="A1:AP26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:41">
+    <row r="1" spans="1:42">
       <c r="A1" s="1" t="s">
         <v>2227</v>
       </c>
@@ -53824,2281 +53860,2468 @@
       <c r="AO1" s="1" t="s">
         <v>2267</v>
       </c>
-    </row>
-    <row r="2" spans="1:41">
+      <c r="AP1" s="1" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42">
       <c r="A2" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2293</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2318</v>
+        <v>2294</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2319</v>
       </c>
       <c r="D2" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="E2" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F2" t="s">
         <v>2017</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="3">
         <v>43231</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>43257</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>2332</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2341</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2342</v>
+      </c>
+      <c r="N2" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O2" t="s">
+        <v>2354</v>
+      </c>
+      <c r="P2" t="s">
+        <v>2355</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>2368</v>
+      </c>
+      <c r="S2">
+        <v>145</v>
+      </c>
+      <c r="T2">
+        <v>158</v>
+      </c>
+      <c r="U2" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V2" s="3">
+        <v>42914</v>
+      </c>
+      <c r="W2" t="s">
+        <v>2382</v>
+      </c>
+      <c r="X2" t="s">
+        <v>2392</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>2396</v>
+      </c>
+      <c r="AA2">
+        <v>46.07</v>
+      </c>
+      <c r="AB2">
+        <v>11.13</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>2402</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>657</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>2427</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>2429</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>2434</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>2439</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42">
+      <c r="A3" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E3" t="s">
         <v>2327</v>
       </c>
-      <c r="J2" t="s">
-        <v>2334</v>
-      </c>
-      <c r="K2" t="s">
-        <v>2336</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2346</v>
-      </c>
-      <c r="N2" t="s">
-        <v>2347</v>
-      </c>
-      <c r="O2" t="s">
-        <v>2348</v>
-      </c>
-      <c r="P2" t="s">
-        <v>2359</v>
-      </c>
-      <c r="R2">
-        <v>145</v>
-      </c>
-      <c r="S2">
-        <v>158</v>
-      </c>
-      <c r="T2" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U2" s="3">
-        <v>42914</v>
-      </c>
-      <c r="V2" t="s">
-        <v>2372</v>
-      </c>
-      <c r="W2" t="s">
-        <v>2381</v>
-      </c>
-      <c r="X2" t="s">
-        <v>2385</v>
-      </c>
-      <c r="Z2">
-        <v>46.07</v>
-      </c>
-      <c r="AA2">
-        <v>11.13</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>2390</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>657</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>2415</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>2416</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>2417</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>2422</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>1851</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>1855</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>2427</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41">
-      <c r="A3" t="s">
-        <v>2269</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>2294</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2319</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2323</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>2018</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="3">
         <v>44021</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>44026</v>
       </c>
-      <c r="H3" t="s">
-        <v>2328</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2334</v>
+      <c r="I3" t="s">
+        <v>2333</v>
       </c>
       <c r="K3" t="s">
-        <v>2336</v>
-      </c>
-      <c r="M3" t="s">
-        <v>2346</v>
+        <v>2341</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2342</v>
       </c>
       <c r="N3" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O3" t="s">
-        <v>2349</v>
+        <v>2354</v>
       </c>
       <c r="P3" t="s">
-        <v>2359</v>
-      </c>
-      <c r="R3">
-        <v>157</v>
+        <v>2356</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>2368</v>
       </c>
       <c r="S3">
         <v>157</v>
       </c>
-      <c r="T3" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U3" s="3">
+      <c r="T3">
+        <v>157</v>
+      </c>
+      <c r="U3" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V3" s="3">
         <v>43193</v>
       </c>
-      <c r="V3" t="s">
-        <v>2372</v>
-      </c>
-      <c r="X3" t="s">
-        <v>2386</v>
-      </c>
-      <c r="Z3">
+      <c r="W3" t="s">
+        <v>2382</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>2397</v>
+      </c>
+      <c r="AA3">
         <v>46.07</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>11.13</v>
       </c>
-      <c r="AC3" t="s">
-        <v>2391</v>
-      </c>
       <c r="AD3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="AE3" t="s">
         <v>657</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
         <v>1851</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AM3" t="s">
         <v>1855</v>
       </c>
-      <c r="AM3" t="s">
-        <v>2428</v>
-      </c>
       <c r="AN3" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:41">
+        <v>2440</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42">
       <c r="A4" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>2295</v>
-      </c>
-      <c r="C4" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>2320</v>
       </c>
       <c r="D4" t="s">
         <v>2323</v>
       </c>
       <c r="E4" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F4" t="s">
         <v>2019</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>44342</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>44420</v>
       </c>
-      <c r="H4" t="s">
-        <v>2329</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="I4" t="s">
         <v>2334</v>
       </c>
       <c r="K4" t="s">
-        <v>2337</v>
-      </c>
-      <c r="M4" t="s">
-        <v>2346</v>
+        <v>2341</v>
+      </c>
+      <c r="L4" t="s">
+        <v>2343</v>
       </c>
       <c r="N4" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O4" t="s">
-        <v>2350</v>
+        <v>2354</v>
       </c>
       <c r="P4" t="s">
-        <v>2360</v>
-      </c>
-      <c r="R4">
+        <v>2357</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>2369</v>
+      </c>
+      <c r="S4">
         <v>6598</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>20</v>
       </c>
-      <c r="T4" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U4" s="3">
+      <c r="U4" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V4" s="3">
         <v>44011</v>
       </c>
-      <c r="V4" t="s">
-        <v>2373</v>
-      </c>
-      <c r="X4" t="s">
-        <v>2387</v>
-      </c>
-      <c r="Z4">
+      <c r="W4" t="s">
+        <v>2383</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AA4">
         <v>10.9</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>76.90000000000001</v>
       </c>
-      <c r="AC4" t="s">
-        <v>2392</v>
-      </c>
       <c r="AD4" t="s">
+        <v>2404</v>
+      </c>
+      <c r="AE4" t="s">
         <v>657</v>
       </c>
-      <c r="AH4" t="s">
-        <v>2418</v>
-      </c>
-      <c r="AI4" s="4" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>1031</v>
+      <c r="AI4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AJ4" s="4" t="s">
+        <v>2435</v>
       </c>
       <c r="AK4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL4" t="s">
         <v>1852</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>1856</v>
       </c>
-      <c r="AM4" t="s">
-        <v>2429</v>
-      </c>
       <c r="AN4" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41">
+        <v>2441</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42">
       <c r="A5" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>2296</v>
-      </c>
-      <c r="C5" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>2320</v>
       </c>
       <c r="D5" t="s">
         <v>2323</v>
       </c>
       <c r="E5" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F5" t="s">
         <v>2019</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>44102</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>44176</v>
       </c>
-      <c r="H5" t="s">
-        <v>2330</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2334</v>
+      <c r="I5" t="s">
+        <v>2335</v>
       </c>
       <c r="K5" t="s">
-        <v>2338</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2346</v>
+        <v>2341</v>
+      </c>
+      <c r="L5" t="s">
+        <v>2344</v>
       </c>
       <c r="N5" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O5" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="P5" t="s">
-        <v>2361</v>
-      </c>
-      <c r="R5">
+        <v>2358</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="S5">
         <v>1342</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>25</v>
       </c>
-      <c r="T5" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U5" s="3">
+      <c r="U5" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V5" s="3">
         <v>43938</v>
       </c>
-      <c r="V5" t="s">
-        <v>2374</v>
-      </c>
-      <c r="X5" t="s">
-        <v>2387</v>
-      </c>
-      <c r="Z5">
+      <c r="W5" t="s">
+        <v>2384</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AA5">
         <v>-25.26</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>-57.57</v>
       </c>
-      <c r="AC5" t="s">
-        <v>2393</v>
-      </c>
       <c r="AD5" t="s">
+        <v>2405</v>
+      </c>
+      <c r="AE5" t="s">
         <v>657</v>
       </c>
-      <c r="AH5" t="s">
-        <v>2418</v>
-      </c>
-      <c r="AI5" s="4" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>1031</v>
+      <c r="AI5" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>2435</v>
       </c>
       <c r="AK5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL5" t="s">
         <v>1852</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AM5" t="s">
         <v>1857</v>
       </c>
-      <c r="AM5" t="s">
-        <v>2429</v>
-      </c>
       <c r="AN5" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:41">
+        <v>2441</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:42">
       <c r="A6" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>2297</v>
-      </c>
-      <c r="C6" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>2320</v>
       </c>
       <c r="D6" t="s">
         <v>2323</v>
       </c>
       <c r="E6" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F6" t="s">
         <v>2019</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>44102</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>44176</v>
       </c>
-      <c r="H6" t="s">
-        <v>2327</v>
-      </c>
-      <c r="J6" t="s">
-        <v>2334</v>
+      <c r="I6" t="s">
+        <v>2332</v>
       </c>
       <c r="K6" t="s">
-        <v>2339</v>
-      </c>
-      <c r="M6" t="s">
-        <v>2346</v>
+        <v>2341</v>
+      </c>
+      <c r="L6" t="s">
+        <v>2345</v>
       </c>
       <c r="N6" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O6" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="P6" t="s">
-        <v>2362</v>
-      </c>
-      <c r="R6">
+        <v>2359</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>2371</v>
+      </c>
+      <c r="S6">
         <v>443</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>18</v>
       </c>
-      <c r="T6" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U6" s="3">
+      <c r="U6" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V6" s="3">
         <v>43971</v>
       </c>
-      <c r="V6" t="s">
-        <v>2375</v>
-      </c>
       <c r="W6" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="X6" t="s">
-        <v>2387</v>
-      </c>
-      <c r="Z6">
+        <v>2393</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AA6">
         <v>55.67</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>12.56</v>
       </c>
-      <c r="AC6" t="s">
-        <v>2394</v>
-      </c>
       <c r="AD6" t="s">
+        <v>2406</v>
+      </c>
+      <c r="AE6" t="s">
         <v>657</v>
       </c>
-      <c r="AH6" t="s">
-        <v>2418</v>
-      </c>
-      <c r="AI6" s="4" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>1031</v>
+      <c r="AI6" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AJ6" s="4" t="s">
+        <v>2435</v>
       </c>
       <c r="AK6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL6" t="s">
         <v>1852</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AM6" t="s">
         <v>1858</v>
       </c>
-      <c r="AM6" t="s">
-        <v>2429</v>
-      </c>
       <c r="AN6" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41">
+        <v>2441</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42">
       <c r="A7" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2298</v>
-      </c>
-      <c r="C7" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>2320</v>
       </c>
       <c r="D7" t="s">
         <v>2323</v>
       </c>
       <c r="E7" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F7" t="s">
         <v>2019</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>44116</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>44365</v>
       </c>
-      <c r="H7" t="s">
-        <v>2327</v>
-      </c>
-      <c r="J7" t="s">
-        <v>2334</v>
+      <c r="I7" t="s">
+        <v>2332</v>
       </c>
       <c r="K7" t="s">
-        <v>2340</v>
-      </c>
-      <c r="M7" t="s">
+        <v>2341</v>
+      </c>
+      <c r="L7" t="s">
         <v>2346</v>
       </c>
       <c r="N7" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O7" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="P7" t="s">
-        <v>2363</v>
-      </c>
-      <c r="R7">
+        <v>2360</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>2372</v>
+      </c>
+      <c r="S7">
         <v>989</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>40</v>
       </c>
-      <c r="T7" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U7" s="3">
+      <c r="U7" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V7" s="3">
         <v>43980</v>
       </c>
-      <c r="V7" t="s">
-        <v>2376</v>
-      </c>
-      <c r="X7" t="s">
-        <v>2387</v>
-      </c>
-      <c r="Z7">
+      <c r="W7" t="s">
+        <v>2386</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AA7">
         <v>43.83</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>126.5</v>
       </c>
-      <c r="AC7" t="s">
-        <v>2395</v>
-      </c>
       <c r="AD7" t="s">
+        <v>2407</v>
+      </c>
+      <c r="AE7" t="s">
         <v>657</v>
       </c>
-      <c r="AH7" t="s">
-        <v>2418</v>
-      </c>
-      <c r="AI7" s="4" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>1031</v>
+      <c r="AI7" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AJ7" s="4" t="s">
+        <v>2435</v>
       </c>
       <c r="AK7" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL7" t="s">
         <v>1853</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AM7" t="s">
         <v>1859</v>
       </c>
-      <c r="AM7" t="s">
-        <v>2429</v>
-      </c>
       <c r="AN7" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41">
+        <v>2441</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42">
       <c r="A8" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2299</v>
-      </c>
-      <c r="C8" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>2320</v>
       </c>
       <c r="D8" t="s">
         <v>2323</v>
       </c>
       <c r="E8" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F8" t="s">
         <v>2019</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44123</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>44183</v>
       </c>
-      <c r="H8" t="s">
-        <v>2331</v>
-      </c>
-      <c r="J8" t="s">
-        <v>2334</v>
+      <c r="I8" t="s">
+        <v>2336</v>
       </c>
       <c r="K8" t="s">
         <v>2341</v>
       </c>
-      <c r="M8" t="s">
-        <v>2346</v>
+      <c r="L8" t="s">
+        <v>2347</v>
       </c>
       <c r="N8" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O8" t="s">
         <v>2354</v>
       </c>
       <c r="P8" t="s">
-        <v>2364</v>
-      </c>
-      <c r="R8">
+        <v>2361</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>2373</v>
+      </c>
+      <c r="S8">
         <v>1980</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>59</v>
       </c>
-      <c r="T8" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V8" s="3">
         <v>43865</v>
       </c>
-      <c r="V8" t="s">
-        <v>2377</v>
-      </c>
-      <c r="X8" t="s">
+      <c r="W8" t="s">
         <v>2387</v>
       </c>
-      <c r="Z8">
+      <c r="Y8" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AA8">
         <v>51.5</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>0.12</v>
       </c>
-      <c r="AC8" t="s">
-        <v>2396</v>
-      </c>
       <c r="AD8" t="s">
+        <v>2408</v>
+      </c>
+      <c r="AE8" t="s">
         <v>657</v>
       </c>
-      <c r="AH8" t="s">
-        <v>2418</v>
-      </c>
-      <c r="AI8" s="4" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>1031</v>
+      <c r="AI8" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AJ8" s="4" t="s">
+        <v>2435</v>
       </c>
       <c r="AK8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL8" t="s">
         <v>1852</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AM8" t="s">
         <v>1860</v>
       </c>
-      <c r="AM8" t="s">
-        <v>2429</v>
-      </c>
       <c r="AN8" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:41">
+        <v>2441</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:42">
       <c r="A9" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>2300</v>
-      </c>
-      <c r="C9" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>2320</v>
       </c>
       <c r="D9" t="s">
         <v>2323</v>
       </c>
       <c r="E9" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F9" t="s">
         <v>2019</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>43707</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>44422</v>
       </c>
-      <c r="H9" t="s">
-        <v>2332</v>
-      </c>
-      <c r="J9" t="s">
-        <v>2334</v>
+      <c r="I9" t="s">
+        <v>2337</v>
       </c>
       <c r="K9" t="s">
-        <v>2342</v>
-      </c>
-      <c r="M9" t="s">
-        <v>2346</v>
+        <v>2341</v>
+      </c>
+      <c r="L9" t="s">
+        <v>2348</v>
       </c>
       <c r="N9" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O9" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="P9" t="s">
-        <v>2365</v>
-      </c>
-      <c r="R9">
+        <v>2362</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>2374</v>
+      </c>
+      <c r="S9">
         <v>88</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>20</v>
       </c>
-      <c r="T9" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V9" s="3">
         <v>43689</v>
       </c>
-      <c r="V9" t="s">
-        <v>2378</v>
-      </c>
-      <c r="X9" t="s">
-        <v>2387</v>
-      </c>
-      <c r="Z9">
+      <c r="W9" t="s">
+        <v>2388</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AA9">
         <v>22.15</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>-100.9</v>
       </c>
-      <c r="AC9" t="s">
-        <v>2397</v>
-      </c>
       <c r="AD9" t="s">
+        <v>2409</v>
+      </c>
+      <c r="AE9" t="s">
         <v>657</v>
       </c>
-      <c r="AH9" t="s">
-        <v>2418</v>
-      </c>
-      <c r="AI9" s="4" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>1031</v>
+      <c r="AI9" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AJ9" s="4" t="s">
+        <v>2435</v>
       </c>
       <c r="AK9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL9" t="s">
         <v>1854</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AM9" t="s">
         <v>1861</v>
       </c>
-      <c r="AM9" t="s">
-        <v>2429</v>
-      </c>
       <c r="AN9" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:41">
+        <v>2441</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:42">
       <c r="A10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>2301</v>
-      </c>
-      <c r="C10" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>2320</v>
       </c>
       <c r="D10" t="s">
         <v>2323</v>
       </c>
       <c r="E10" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F10" t="s">
         <v>2019</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>44102</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>44176</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
+        <v>2332</v>
+      </c>
+      <c r="K10" t="s">
+        <v>2341</v>
+      </c>
+      <c r="L10" t="s">
+        <v>2349</v>
+      </c>
+      <c r="N10" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O10" t="s">
+        <v>2354</v>
+      </c>
+      <c r="P10" t="s">
+        <v>2363</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>2368</v>
+      </c>
+      <c r="S10">
+        <v>5692</v>
+      </c>
+      <c r="T10">
+        <v>221</v>
+      </c>
+      <c r="U10" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V10" s="3">
+        <v>43720</v>
+      </c>
+      <c r="W10" t="s">
+        <v>2382</v>
+      </c>
+      <c r="X10" t="s">
+        <v>2394</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AA10">
+        <v>46.07</v>
+      </c>
+      <c r="AB10">
+        <v>11.13</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>2410</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>657</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AJ10" s="4" t="s">
+        <v>2435</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>2441</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42">
+      <c r="A11" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2323</v>
+      </c>
+      <c r="E11" t="s">
         <v>2327</v>
       </c>
-      <c r="J10" t="s">
-        <v>2334</v>
-      </c>
-      <c r="K10" t="s">
-        <v>2343</v>
-      </c>
-      <c r="M10" t="s">
-        <v>2346</v>
-      </c>
-      <c r="N10" t="s">
-        <v>2347</v>
-      </c>
-      <c r="O10" t="s">
-        <v>2356</v>
-      </c>
-      <c r="P10" t="s">
-        <v>2359</v>
-      </c>
-      <c r="R10">
-        <v>5692</v>
-      </c>
-      <c r="S10">
-        <v>221</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="F11" t="s">
+        <v>2019</v>
+      </c>
+      <c r="G11" s="3">
+        <v>44102</v>
+      </c>
+      <c r="H11" s="3">
+        <v>44176</v>
+      </c>
+      <c r="I11" t="s">
+        <v>2338</v>
+      </c>
+      <c r="K11" t="s">
+        <v>2341</v>
+      </c>
+      <c r="L11" t="s">
+        <v>2350</v>
+      </c>
+      <c r="N11" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O11" t="s">
+        <v>2354</v>
+      </c>
+      <c r="P11" t="s">
+        <v>2364</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="S11">
+        <v>3972</v>
+      </c>
+      <c r="T11">
+        <v>164</v>
+      </c>
+      <c r="U11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V11" s="3">
+        <v>43931</v>
+      </c>
+      <c r="W11" t="s">
+        <v>2389</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AA11">
+        <v>47.92</v>
+      </c>
+      <c r="AB11">
+        <v>106.9</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>2411</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>657</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AJ11" s="4" t="s">
+        <v>2435</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>1862</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>2441</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:42">
+      <c r="A12" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F12" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G12" s="3">
+        <v>44271</v>
+      </c>
+      <c r="H12" s="3">
+        <v>44286</v>
+      </c>
+      <c r="I12" t="s">
+        <v>2335</v>
+      </c>
+      <c r="K12" t="s">
+        <v>2340</v>
+      </c>
+      <c r="L12" t="s">
+        <v>2344</v>
+      </c>
+      <c r="N12" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O12" t="s">
+        <v>2354</v>
+      </c>
+      <c r="P12" t="s">
+        <v>2358</v>
+      </c>
+      <c r="Q12" t="s">
         <v>2370</v>
-      </c>
-      <c r="U10" s="3">
-        <v>43720</v>
-      </c>
-      <c r="V10" t="s">
-        <v>2372</v>
-      </c>
-      <c r="W10" t="s">
-        <v>2383</v>
-      </c>
-      <c r="X10" t="s">
-        <v>2387</v>
-      </c>
-      <c r="Z10">
-        <v>46.07</v>
-      </c>
-      <c r="AA10">
-        <v>11.13</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>2398</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>657</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>2418</v>
-      </c>
-      <c r="AI10" s="4" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>1852</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>1855</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>2429</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:41">
-      <c r="A11" t="s">
-        <v>2277</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>2302</v>
-      </c>
-      <c r="E11" t="s">
-        <v>2019</v>
-      </c>
-      <c r="F11" s="3">
-        <v>44102</v>
-      </c>
-      <c r="G11" s="3">
-        <v>44176</v>
-      </c>
-      <c r="M11" t="s">
-        <v>2346</v>
-      </c>
-      <c r="P11" t="s">
-        <v>2366</v>
-      </c>
-      <c r="S11">
-        <v>164</v>
-      </c>
-      <c r="Z11">
-        <v>47.92</v>
-      </c>
-      <c r="AA11">
-        <v>106.9</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>2399</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>657</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>2418</v>
-      </c>
-      <c r="AI11" s="4" t="s">
-        <v>2423</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>1852</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>1862</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>2429</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:41">
-      <c r="A12" t="s">
-        <v>2278</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>2303</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2323</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2324</v>
-      </c>
-      <c r="F12" s="3">
-        <v>44271</v>
-      </c>
-      <c r="G12" s="3">
-        <v>44286</v>
-      </c>
-      <c r="H12" t="s">
-        <v>2330</v>
-      </c>
-      <c r="J12" t="s">
-        <v>2335</v>
-      </c>
-      <c r="K12" t="s">
-        <v>2338</v>
-      </c>
-      <c r="M12" t="s">
-        <v>2346</v>
-      </c>
-      <c r="N12" t="s">
-        <v>2347</v>
-      </c>
-      <c r="O12" t="s">
-        <v>2351</v>
-      </c>
-      <c r="P12" t="s">
-        <v>2361</v>
-      </c>
-      <c r="R12">
-        <v>21</v>
       </c>
       <c r="S12">
         <v>21</v>
       </c>
-      <c r="T12" t="s">
+      <c r="T12">
+        <v>21</v>
+      </c>
+      <c r="U12" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V12" s="3">
+        <v>43938</v>
+      </c>
+      <c r="W12" t="s">
+        <v>2384</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>2399</v>
+      </c>
+      <c r="AA12">
+        <v>-25.26</v>
+      </c>
+      <c r="AB12">
+        <v>-57.57</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>2412</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>657</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>2431</v>
+      </c>
+      <c r="AJ12" s="4" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>1851</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>1857</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>2442</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42">
+      <c r="A13" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F13" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G13" s="3">
+        <v>44267</v>
+      </c>
+      <c r="H13" s="3">
+        <v>44283</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2332</v>
+      </c>
+      <c r="K13" t="s">
+        <v>2340</v>
+      </c>
+      <c r="L13" t="s">
+        <v>2345</v>
+      </c>
+      <c r="N13" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O13" t="s">
+        <v>2354</v>
+      </c>
+      <c r="P13" t="s">
+        <v>2359</v>
+      </c>
+      <c r="Q13" t="s">
         <v>2371</v>
       </c>
-      <c r="U12" s="3">
-        <v>43938</v>
-      </c>
-      <c r="V12" t="s">
-        <v>2374</v>
-      </c>
-      <c r="X12" t="s">
-        <v>2388</v>
-      </c>
-      <c r="Z12">
-        <v>-25.26</v>
-      </c>
-      <c r="AA12">
-        <v>-57.57</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>2400</v>
-      </c>
-      <c r="AD12" t="s">
+      <c r="S13">
+        <v>39</v>
+      </c>
+      <c r="T13">
+        <v>29</v>
+      </c>
+      <c r="U13" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V13" s="3">
+        <v>43971</v>
+      </c>
+      <c r="W13" t="s">
+        <v>2385</v>
+      </c>
+      <c r="X13" t="s">
+        <v>2393</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>2399</v>
+      </c>
+      <c r="AA13">
+        <v>55.67</v>
+      </c>
+      <c r="AB13">
+        <v>12.56</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>2413</v>
+      </c>
+      <c r="AE13" t="s">
         <v>657</v>
       </c>
-      <c r="AH12" t="s">
-        <v>2419</v>
-      </c>
-      <c r="AI12" s="4" t="s">
-        <v>2424</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK12" t="s">
+      <c r="AI13" t="s">
+        <v>2431</v>
+      </c>
+      <c r="AJ13" s="4" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL13" t="s">
         <v>1851</v>
       </c>
-      <c r="AL12" t="s">
-        <v>1857</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>2430</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:41">
-      <c r="A13" t="s">
-        <v>2279</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>2304</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2323</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="AM13" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>2442</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42">
+      <c r="A14" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D14" t="s">
         <v>2324</v>
       </c>
-      <c r="F13" s="3">
+      <c r="E14" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F14" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G14" s="3">
         <v>44267</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H14" s="3">
         <v>44283</v>
       </c>
-      <c r="H13" t="s">
-        <v>2327</v>
-      </c>
-      <c r="J13" t="s">
-        <v>2335</v>
-      </c>
-      <c r="K13" t="s">
-        <v>2339</v>
-      </c>
-      <c r="M13" t="s">
-        <v>2346</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="I14" t="s">
+        <v>2336</v>
+      </c>
+      <c r="K14" t="s">
+        <v>2340</v>
+      </c>
+      <c r="L14" t="s">
         <v>2347</v>
       </c>
-      <c r="O13" t="s">
-        <v>2352</v>
-      </c>
-      <c r="P13" t="s">
-        <v>2362</v>
-      </c>
-      <c r="R13">
-        <v>39</v>
-      </c>
-      <c r="S13">
-        <v>29</v>
-      </c>
-      <c r="T13" t="s">
-        <v>2371</v>
-      </c>
-      <c r="U13" s="3">
-        <v>43971</v>
-      </c>
-      <c r="V13" t="s">
-        <v>2375</v>
-      </c>
-      <c r="W13" t="s">
-        <v>2382</v>
-      </c>
-      <c r="X13" t="s">
-        <v>2388</v>
-      </c>
-      <c r="Z13">
-        <v>55.67</v>
-      </c>
-      <c r="AA13">
-        <v>12.56</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>2401</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>657</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>2419</v>
-      </c>
-      <c r="AI13" s="4" t="s">
-        <v>2424</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>1858</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>2430</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:41">
-      <c r="A14" t="s">
-        <v>2280</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>2305</v>
-      </c>
-      <c r="C14" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D14" t="s">
-        <v>2323</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2324</v>
-      </c>
-      <c r="F14" s="3">
-        <v>44267</v>
-      </c>
-      <c r="G14" s="3">
-        <v>44283</v>
-      </c>
-      <c r="H14" t="s">
-        <v>2331</v>
-      </c>
-      <c r="J14" t="s">
-        <v>2335</v>
-      </c>
-      <c r="K14" t="s">
-        <v>2341</v>
-      </c>
-      <c r="M14" t="s">
-        <v>2346</v>
-      </c>
       <c r="N14" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O14" t="s">
         <v>2354</v>
       </c>
       <c r="P14" t="s">
+        <v>2361</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>2373</v>
+      </c>
+      <c r="S14">
+        <v>45</v>
+      </c>
+      <c r="T14">
+        <v>10</v>
+      </c>
+      <c r="U14" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V14" s="3">
+        <v>43865</v>
+      </c>
+      <c r="W14" t="s">
+        <v>2387</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>2399</v>
+      </c>
+      <c r="AA14">
+        <v>51.5</v>
+      </c>
+      <c r="AB14">
+        <v>0.12</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>2414</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>657</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>2431</v>
+      </c>
+      <c r="AJ14" s="4" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>1851</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>1860</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>2442</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42">
+      <c r="A15" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F15" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G15" s="3">
+        <v>44351</v>
+      </c>
+      <c r="H15" s="3">
+        <v>44365</v>
+      </c>
+      <c r="I15" t="s">
+        <v>2332</v>
+      </c>
+      <c r="K15" t="s">
+        <v>2340</v>
+      </c>
+      <c r="L15" t="s">
+        <v>2349</v>
+      </c>
+      <c r="N15" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O15" t="s">
+        <v>2354</v>
+      </c>
+      <c r="P15" t="s">
+        <v>2363</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>2368</v>
+      </c>
+      <c r="S15">
+        <v>48</v>
+      </c>
+      <c r="T15">
+        <v>33</v>
+      </c>
+      <c r="U15" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V15" s="3">
+        <v>43720</v>
+      </c>
+      <c r="W15" t="s">
+        <v>2382</v>
+      </c>
+      <c r="X15" t="s">
+        <v>2394</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>2399</v>
+      </c>
+      <c r="AA15">
+        <v>46.07</v>
+      </c>
+      <c r="AB15">
+        <v>11.13</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>2415</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>657</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>2431</v>
+      </c>
+      <c r="AJ15" s="4" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>1851</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>2442</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42">
+      <c r="A16" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G16" s="3">
+        <v>44267</v>
+      </c>
+      <c r="H16" s="3">
+        <v>44283</v>
+      </c>
+      <c r="I16" t="s">
+        <v>2338</v>
+      </c>
+      <c r="K16" t="s">
+        <v>2340</v>
+      </c>
+      <c r="L16" t="s">
+        <v>2350</v>
+      </c>
+      <c r="N16" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O16" t="s">
+        <v>2354</v>
+      </c>
+      <c r="P16" t="s">
         <v>2364</v>
       </c>
-      <c r="R14">
-        <v>45</v>
-      </c>
-      <c r="S14">
-        <v>10</v>
-      </c>
-      <c r="T14" t="s">
-        <v>2371</v>
-      </c>
-      <c r="U14" s="3">
-        <v>43865</v>
-      </c>
-      <c r="V14" t="s">
-        <v>2377</v>
-      </c>
-      <c r="X14" t="s">
-        <v>2388</v>
-      </c>
-      <c r="Z14">
-        <v>51.5</v>
-      </c>
-      <c r="AA14">
-        <v>0.12</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>2402</v>
-      </c>
-      <c r="AD14" t="s">
+      <c r="Q16" t="s">
+        <v>2375</v>
+      </c>
+      <c r="S16">
+        <v>40</v>
+      </c>
+      <c r="T16">
+        <v>24</v>
+      </c>
+      <c r="U16" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V16" s="3">
+        <v>43931</v>
+      </c>
+      <c r="W16" t="s">
+        <v>2389</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>2399</v>
+      </c>
+      <c r="AA16">
+        <v>47.92</v>
+      </c>
+      <c r="AB16">
+        <v>106.9</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>2416</v>
+      </c>
+      <c r="AE16" t="s">
         <v>657</v>
       </c>
-      <c r="AH14" t="s">
-        <v>2419</v>
-      </c>
-      <c r="AI14" s="4" t="s">
-        <v>2424</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK14" t="s">
+      <c r="AI16" t="s">
+        <v>2431</v>
+      </c>
+      <c r="AJ16" s="4" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL16" t="s">
         <v>1851</v>
       </c>
-      <c r="AL14" t="s">
-        <v>1860</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>2430</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:41">
-      <c r="A15" t="s">
-        <v>2281</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>2306</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D15" t="s">
-        <v>2323</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="AM16" t="s">
+        <v>1862</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>2442</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:42">
+      <c r="A17" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D17" t="s">
         <v>2324</v>
       </c>
-      <c r="F15" s="3">
-        <v>44351</v>
-      </c>
-      <c r="G15" s="3">
-        <v>44365</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="E17" t="s">
         <v>2327</v>
       </c>
-      <c r="J15" t="s">
+      <c r="F17" t="s">
+        <v>2330</v>
+      </c>
+      <c r="G17" s="3">
+        <v>44578</v>
+      </c>
+      <c r="H17" s="3">
+        <v>44599</v>
+      </c>
+      <c r="I17" t="s">
         <v>2335</v>
       </c>
-      <c r="K15" t="s">
-        <v>2343</v>
-      </c>
-      <c r="M15" t="s">
-        <v>2346</v>
-      </c>
-      <c r="N15" t="s">
-        <v>2347</v>
-      </c>
-      <c r="O15" t="s">
-        <v>2356</v>
-      </c>
-      <c r="P15" t="s">
-        <v>2359</v>
-      </c>
-      <c r="R15">
-        <v>48</v>
-      </c>
-      <c r="S15">
-        <v>33</v>
-      </c>
-      <c r="T15" t="s">
-        <v>2371</v>
-      </c>
-      <c r="U15" s="3">
-        <v>43720</v>
-      </c>
-      <c r="V15" t="s">
-        <v>2372</v>
-      </c>
-      <c r="W15" t="s">
-        <v>2383</v>
-      </c>
-      <c r="X15" t="s">
-        <v>2388</v>
-      </c>
-      <c r="Z15">
-        <v>46.07</v>
-      </c>
-      <c r="AA15">
-        <v>11.13</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>2403</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>657</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>2419</v>
-      </c>
-      <c r="AI15" s="4" t="s">
-        <v>2424</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>1851</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>1855</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>2430</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41">
-      <c r="A16" t="s">
-        <v>2282</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>2307</v>
-      </c>
-      <c r="E16" t="s">
-        <v>2324</v>
-      </c>
-      <c r="F16" s="3">
-        <v>44267</v>
-      </c>
-      <c r="G16" s="3">
-        <v>44283</v>
-      </c>
-      <c r="M16" t="s">
-        <v>2346</v>
-      </c>
-      <c r="P16" t="s">
-        <v>2366</v>
-      </c>
-      <c r="S16">
-        <v>24</v>
-      </c>
-      <c r="Z16">
-        <v>47.92</v>
-      </c>
-      <c r="AA16">
-        <v>106.9</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>2404</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>657</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>2419</v>
-      </c>
-      <c r="AI16" s="4" t="s">
-        <v>2424</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>1851</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>1862</v>
-      </c>
-      <c r="AM16" t="s">
-        <v>2430</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41">
-      <c r="A17" t="s">
-        <v>2283</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>2308</v>
-      </c>
-      <c r="C17" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D17" t="s">
-        <v>2323</v>
-      </c>
-      <c r="E17" t="s">
-        <v>2325</v>
-      </c>
-      <c r="F17" s="3">
-        <v>44578</v>
-      </c>
-      <c r="G17" s="3">
-        <v>44599</v>
-      </c>
-      <c r="H17" t="s">
-        <v>2330</v>
-      </c>
-      <c r="J17" t="s">
-        <v>2335</v>
-      </c>
       <c r="K17" t="s">
-        <v>2338</v>
-      </c>
-      <c r="M17" t="s">
-        <v>2346</v>
+        <v>2340</v>
+      </c>
+      <c r="L17" t="s">
+        <v>2344</v>
       </c>
       <c r="N17" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O17" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="P17" t="s">
-        <v>2361</v>
-      </c>
-      <c r="R17">
-        <v>23</v>
+        <v>2358</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>2370</v>
       </c>
       <c r="S17">
         <v>23</v>
       </c>
-      <c r="T17" t="s">
+      <c r="T17">
+        <v>23</v>
+      </c>
+      <c r="U17" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V17" s="3">
+        <v>43938</v>
+      </c>
+      <c r="W17" t="s">
+        <v>2384</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AA17">
+        <v>25.26</v>
+      </c>
+      <c r="AB17">
+        <v>57.57</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>2417</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>657</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>2432</v>
+      </c>
+      <c r="AJ17" s="4" t="s">
+        <v>2437</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>1851</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>1857</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>2443</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:42">
+      <c r="A18" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F18" t="s">
+        <v>2330</v>
+      </c>
+      <c r="G18" s="3">
+        <v>44522</v>
+      </c>
+      <c r="H18" s="3">
+        <v>44551</v>
+      </c>
+      <c r="I18" t="s">
+        <v>2332</v>
+      </c>
+      <c r="K18" t="s">
+        <v>2340</v>
+      </c>
+      <c r="L18" t="s">
+        <v>2345</v>
+      </c>
+      <c r="N18" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O18" t="s">
+        <v>2354</v>
+      </c>
+      <c r="P18" t="s">
+        <v>2359</v>
+      </c>
+      <c r="Q18" t="s">
         <v>2371</v>
-      </c>
-      <c r="U17" s="3">
-        <v>43938</v>
-      </c>
-      <c r="V17" t="s">
-        <v>2374</v>
-      </c>
-      <c r="X17" t="s">
-        <v>2389</v>
-      </c>
-      <c r="Z17">
-        <v>25.26</v>
-      </c>
-      <c r="AA17">
-        <v>57.57</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>2405</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>657</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>2420</v>
-      </c>
-      <c r="AI17" s="4" t="s">
-        <v>2425</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>1851</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>1857</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>2431</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:41">
-      <c r="A18" t="s">
-        <v>2284</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>2309</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D18" t="s">
-        <v>2323</v>
-      </c>
-      <c r="E18" t="s">
-        <v>2325</v>
-      </c>
-      <c r="F18" s="3">
-        <v>44522</v>
-      </c>
-      <c r="G18" s="3">
-        <v>44551</v>
-      </c>
-      <c r="H18" t="s">
-        <v>2327</v>
-      </c>
-      <c r="J18" t="s">
-        <v>2335</v>
-      </c>
-      <c r="K18" t="s">
-        <v>2339</v>
-      </c>
-      <c r="M18" t="s">
-        <v>2346</v>
-      </c>
-      <c r="N18" t="s">
-        <v>2347</v>
-      </c>
-      <c r="O18" t="s">
-        <v>2352</v>
-      </c>
-      <c r="P18" t="s">
-        <v>2362</v>
-      </c>
-      <c r="R18">
-        <v>46</v>
       </c>
       <c r="S18">
         <v>46</v>
       </c>
-      <c r="T18" t="s">
-        <v>2371</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="T18">
+        <v>46</v>
+      </c>
+      <c r="U18" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V18" s="3">
         <v>43971</v>
       </c>
-      <c r="V18" t="s">
-        <v>2375</v>
-      </c>
       <c r="W18" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="X18" t="s">
-        <v>2389</v>
-      </c>
-      <c r="Z18">
+        <v>2393</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AA18">
         <v>55.67</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>12.56</v>
       </c>
-      <c r="AC18" t="s">
-        <v>2406</v>
-      </c>
       <c r="AD18" t="s">
+        <v>2418</v>
+      </c>
+      <c r="AE18" t="s">
         <v>657</v>
       </c>
-      <c r="AH18" t="s">
-        <v>2420</v>
-      </c>
-      <c r="AI18" s="4" t="s">
-        <v>2425</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>1031</v>
+      <c r="AI18" t="s">
+        <v>2432</v>
+      </c>
+      <c r="AJ18" s="4" t="s">
+        <v>2437</v>
       </c>
       <c r="AK18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL18" t="s">
         <v>1851</v>
       </c>
-      <c r="AL18" t="s">
+      <c r="AM18" t="s">
         <v>1858</v>
       </c>
-      <c r="AM18" t="s">
-        <v>2431</v>
-      </c>
       <c r="AN18" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41">
+        <v>2443</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:42">
       <c r="A19" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>2310</v>
-      </c>
-      <c r="C19" t="s">
-        <v>2321</v>
+        <v>2311</v>
       </c>
       <c r="D19" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="E19" t="s">
-        <v>2325</v>
-      </c>
-      <c r="F19" s="3">
+        <v>2327</v>
+      </c>
+      <c r="F19" t="s">
+        <v>2330</v>
+      </c>
+      <c r="G19" s="3">
         <v>44522</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>44536</v>
       </c>
-      <c r="H19" t="s">
-        <v>2331</v>
-      </c>
-      <c r="J19" t="s">
-        <v>2335</v>
+      <c r="I19" t="s">
+        <v>2336</v>
       </c>
       <c r="K19" t="s">
-        <v>2341</v>
-      </c>
-      <c r="M19" t="s">
-        <v>2346</v>
+        <v>2340</v>
+      </c>
+      <c r="L19" t="s">
+        <v>2347</v>
       </c>
       <c r="N19" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O19" t="s">
         <v>2354</v>
       </c>
       <c r="P19" t="s">
-        <v>2364</v>
-      </c>
-      <c r="R19">
-        <v>19</v>
+        <v>2361</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>2373</v>
       </c>
       <c r="S19">
         <v>19</v>
       </c>
-      <c r="T19" t="s">
-        <v>2371</v>
-      </c>
-      <c r="U19" s="3">
+      <c r="T19">
+        <v>19</v>
+      </c>
+      <c r="U19" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V19" s="3">
         <v>43865</v>
       </c>
-      <c r="V19" t="s">
-        <v>2377</v>
-      </c>
-      <c r="X19" t="s">
-        <v>2389</v>
-      </c>
-      <c r="Z19">
+      <c r="W19" t="s">
+        <v>2387</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AA19">
         <v>51.5</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>0.12</v>
       </c>
-      <c r="AC19" t="s">
-        <v>2407</v>
-      </c>
       <c r="AD19" t="s">
+        <v>2419</v>
+      </c>
+      <c r="AE19" t="s">
         <v>657</v>
       </c>
-      <c r="AH19" t="s">
-        <v>2420</v>
-      </c>
-      <c r="AI19" s="4" t="s">
-        <v>2425</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>1031</v>
+      <c r="AI19" t="s">
+        <v>2432</v>
+      </c>
+      <c r="AJ19" s="4" t="s">
+        <v>2437</v>
       </c>
       <c r="AK19" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL19" t="s">
         <v>1851</v>
       </c>
-      <c r="AL19" t="s">
+      <c r="AM19" t="s">
         <v>1860</v>
       </c>
-      <c r="AM19" t="s">
-        <v>2431</v>
-      </c>
       <c r="AN19" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:41">
+        <v>2443</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:42">
       <c r="A20" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>2311</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2321</v>
+        <v>2312</v>
       </c>
       <c r="D20" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="E20" t="s">
-        <v>2325</v>
-      </c>
-      <c r="F20" s="3">
+        <v>2327</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2330</v>
+      </c>
+      <c r="G20" s="3">
         <v>44520</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>44538</v>
       </c>
-      <c r="H20" t="s">
-        <v>2327</v>
-      </c>
-      <c r="J20" t="s">
-        <v>2335</v>
+      <c r="I20" t="s">
+        <v>2332</v>
       </c>
       <c r="K20" t="s">
-        <v>2343</v>
-      </c>
-      <c r="M20" t="s">
-        <v>2346</v>
+        <v>2340</v>
+      </c>
+      <c r="L20" t="s">
+        <v>2349</v>
       </c>
       <c r="N20" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O20" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="P20" t="s">
-        <v>2359</v>
-      </c>
-      <c r="R20">
-        <v>31</v>
+        <v>2363</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>2368</v>
       </c>
       <c r="S20">
         <v>31</v>
       </c>
-      <c r="T20" t="s">
-        <v>2371</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="T20">
+        <v>31</v>
+      </c>
+      <c r="U20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V20" s="3">
         <v>43720</v>
       </c>
-      <c r="V20" t="s">
-        <v>2372</v>
-      </c>
       <c r="W20" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="X20" t="s">
-        <v>2389</v>
-      </c>
-      <c r="Z20">
+        <v>2394</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AA20">
         <v>46.07</v>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <v>11.13</v>
       </c>
-      <c r="AC20" t="s">
-        <v>2408</v>
-      </c>
       <c r="AD20" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AE20" t="s">
         <v>657</v>
       </c>
-      <c r="AH20" t="s">
-        <v>2420</v>
-      </c>
-      <c r="AI20" s="4" t="s">
-        <v>2425</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>1031</v>
+      <c r="AI20" t="s">
+        <v>2432</v>
+      </c>
+      <c r="AJ20" s="4" t="s">
+        <v>2437</v>
       </c>
       <c r="AK20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL20" t="s">
         <v>1851</v>
       </c>
-      <c r="AL20" t="s">
+      <c r="AM20" t="s">
         <v>1855</v>
       </c>
-      <c r="AM20" t="s">
-        <v>2431</v>
-      </c>
       <c r="AN20" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:41">
+        <v>2443</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:42">
       <c r="A21" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>2312</v>
+        <v>2313</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2324</v>
       </c>
       <c r="E21" t="s">
-        <v>2325</v>
-      </c>
-      <c r="F21" s="3">
+        <v>2327</v>
+      </c>
+      <c r="F21" t="s">
+        <v>2330</v>
+      </c>
+      <c r="G21" s="3">
         <v>44522</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>44536</v>
       </c>
-      <c r="M21" t="s">
-        <v>2346</v>
+      <c r="I21" t="s">
+        <v>2338</v>
+      </c>
+      <c r="K21" t="s">
+        <v>2340</v>
+      </c>
+      <c r="L21" t="s">
+        <v>2350</v>
+      </c>
+      <c r="N21" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O21" t="s">
+        <v>2354</v>
       </c>
       <c r="P21" t="s">
-        <v>2366</v>
+        <v>2364</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>2375</v>
       </c>
       <c r="S21">
         <v>31</v>
       </c>
-      <c r="Z21">
+      <c r="T21">
+        <v>31</v>
+      </c>
+      <c r="U21" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V21" s="3">
+        <v>43931</v>
+      </c>
+      <c r="W21" t="s">
+        <v>2389</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AA21">
         <v>47.92</v>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <v>106.9</v>
       </c>
-      <c r="AC21" t="s">
-        <v>2409</v>
-      </c>
       <c r="AD21" t="s">
+        <v>2421</v>
+      </c>
+      <c r="AE21" t="s">
         <v>657</v>
       </c>
-      <c r="AH21" t="s">
-        <v>2420</v>
-      </c>
-      <c r="AI21" s="4" t="s">
-        <v>2425</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>1031</v>
+      <c r="AI21" t="s">
+        <v>2432</v>
+      </c>
+      <c r="AJ21" s="4" t="s">
+        <v>2437</v>
       </c>
       <c r="AK21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL21" t="s">
         <v>1851</v>
       </c>
-      <c r="AL21" t="s">
+      <c r="AM21" t="s">
         <v>1862</v>
       </c>
-      <c r="AM21" t="s">
-        <v>2431</v>
-      </c>
       <c r="AN21" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:41">
+        <v>2443</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:42">
       <c r="A22" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>2313</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2322</v>
+        <v>2314</v>
       </c>
       <c r="D22" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="E22" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F22" t="s">
         <v>2023</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>44725</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>44753</v>
       </c>
-      <c r="H22" t="s">
-        <v>2329</v>
-      </c>
-      <c r="J22" t="s">
-        <v>2335</v>
+      <c r="I22" t="s">
+        <v>2334</v>
       </c>
       <c r="K22" t="s">
-        <v>2344</v>
-      </c>
-      <c r="M22" t="s">
-        <v>2346</v>
+        <v>2340</v>
+      </c>
+      <c r="L22" t="s">
+        <v>2351</v>
       </c>
       <c r="N22" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O22" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
       <c r="P22" t="s">
-        <v>2367</v>
-      </c>
-      <c r="R22">
-        <v>112</v>
+        <v>2365</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>2376</v>
       </c>
       <c r="S22">
         <v>112</v>
       </c>
-      <c r="T22" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="T22">
+        <v>112</v>
+      </c>
+      <c r="U22" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V22" s="3">
         <v>44663</v>
       </c>
-      <c r="V22" t="s">
-        <v>2379</v>
-      </c>
-      <c r="Z22">
+      <c r="W22" t="s">
+        <v>2390</v>
+      </c>
+      <c r="AA22">
         <v>21.03</v>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <v>105.8</v>
       </c>
-      <c r="AC22" t="s">
-        <v>2410</v>
-      </c>
       <c r="AD22" t="s">
+        <v>2422</v>
+      </c>
+      <c r="AE22" t="s">
         <v>657</v>
       </c>
-      <c r="AK22" t="s">
+      <c r="AL22" t="s">
         <v>1851</v>
       </c>
-      <c r="AL22" t="s">
+      <c r="AM22" t="s">
         <v>1863</v>
       </c>
-      <c r="AM22" t="s">
-        <v>2432</v>
-      </c>
       <c r="AN22" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:41">
+        <v>2444</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42">
       <c r="A23" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>2314</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2320</v>
+        <v>2315</v>
       </c>
       <c r="D23" t="s">
         <v>2323</v>
       </c>
       <c r="E23" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F23" t="s">
         <v>2024</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44719</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44748</v>
       </c>
-      <c r="H23" t="s">
-        <v>2333</v>
-      </c>
-      <c r="J23" t="s">
-        <v>2335</v>
+      <c r="I23" t="s">
+        <v>2339</v>
       </c>
       <c r="K23" t="s">
-        <v>2345</v>
-      </c>
-      <c r="M23" t="s">
-        <v>2346</v>
+        <v>2340</v>
+      </c>
+      <c r="L23" t="s">
+        <v>2352</v>
       </c>
       <c r="N23" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="O23" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
       <c r="P23" t="s">
-        <v>2368</v>
-      </c>
-      <c r="R23">
-        <v>164</v>
+        <v>2366</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>2377</v>
       </c>
       <c r="S23">
         <v>164</v>
       </c>
-      <c r="T23" t="s">
-        <v>2370</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="T23">
+        <v>164</v>
+      </c>
+      <c r="U23" t="s">
+        <v>2379</v>
+      </c>
+      <c r="V23" s="3">
         <v>44635</v>
       </c>
-      <c r="V23" t="s">
-        <v>2380</v>
-      </c>
       <c r="W23" t="s">
-        <v>2384</v>
-      </c>
-      <c r="Z23">
+        <v>2391</v>
+      </c>
+      <c r="X23" t="s">
+        <v>2395</v>
+      </c>
+      <c r="AA23">
         <v>40.64</v>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <v>22.94</v>
       </c>
-      <c r="AC23" t="s">
-        <v>2411</v>
-      </c>
       <c r="AD23" t="s">
+        <v>2423</v>
+      </c>
+      <c r="AE23" t="s">
         <v>657</v>
       </c>
-      <c r="AK23" t="s">
+      <c r="AL23" t="s">
         <v>1851</v>
       </c>
-      <c r="AL23" t="s">
+      <c r="AM23" t="s">
         <v>1864</v>
       </c>
-      <c r="AM23" t="s">
-        <v>2432</v>
-      </c>
       <c r="AN23" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:41">
+        <v>2444</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:42">
       <c r="A24" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>2315</v>
-      </c>
-      <c r="E24" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>2316</v>
+      </c>
+      <c r="F24" t="s">
+        <v>2331</v>
+      </c>
+      <c r="G24" s="3">
+        <v>45058.09375</v>
+      </c>
+      <c r="H24" s="3">
+        <v>45089.09375</v>
+      </c>
+      <c r="N24" t="s">
+        <v>2353</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>2368</v>
+      </c>
+      <c r="T24">
+        <v>62</v>
+      </c>
+      <c r="AA24">
+        <v>46.04</v>
+      </c>
+      <c r="AB24">
+        <v>11.07</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>2424</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>657</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>2445</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42">
+      <c r="A25" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>2317</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2025</v>
+      </c>
+      <c r="G25" s="3">
+        <v>45369</v>
+      </c>
+      <c r="H25" s="3">
+        <v>45425</v>
+      </c>
+      <c r="N25" t="s">
+        <v>2353</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>2378</v>
+      </c>
+      <c r="T25">
+        <v>73</v>
+      </c>
+      <c r="AA25">
+        <v>0.335</v>
+      </c>
+      <c r="AB25">
+        <v>32.56</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>2425</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>657</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>2433</v>
+      </c>
+      <c r="AJ25" s="4" t="s">
+        <v>2438</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>1865</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>2446</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:42">
+      <c r="A26" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D26" t="s">
         <v>2326</v>
       </c>
-      <c r="F24" s="3">
-        <v>45058.09375</v>
-      </c>
-      <c r="G24" s="3">
-        <v>45089.09375</v>
-      </c>
-      <c r="M24" t="s">
-        <v>2346</v>
-      </c>
-      <c r="P24" t="s">
-        <v>2359</v>
-      </c>
-      <c r="S24">
-        <v>62</v>
-      </c>
-      <c r="Z24">
-        <v>46.04</v>
-      </c>
-      <c r="AA24">
-        <v>11.07</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>2412</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>657</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>1852</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>1855</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>2433</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:41">
-      <c r="A25" t="s">
-        <v>2291</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>2316</v>
-      </c>
-      <c r="E25" t="s">
-        <v>2025</v>
-      </c>
-      <c r="F25" s="3">
-        <v>45369</v>
-      </c>
-      <c r="G25" s="3">
-        <v>45425</v>
-      </c>
-      <c r="M25" t="s">
-        <v>2346</v>
-      </c>
-      <c r="P25" t="s">
-        <v>2369</v>
-      </c>
-      <c r="S25">
-        <v>73</v>
-      </c>
-      <c r="Z25">
-        <v>0.335</v>
-      </c>
-      <c r="AA25">
-        <v>32.56</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>2413</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>657</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>2421</v>
-      </c>
-      <c r="AI25" s="4" t="s">
-        <v>2426</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>1852</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>1865</v>
-      </c>
-      <c r="AM25" t="s">
-        <v>2434</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:41">
-      <c r="A26" t="s">
-        <v>2292</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>2317</v>
-      </c>
       <c r="E26" t="s">
+        <v>2328</v>
+      </c>
+      <c r="F26" t="s">
         <v>2026</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>45436</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>45528</v>
       </c>
-      <c r="M26" t="s">
-        <v>2346</v>
+      <c r="I26" t="s">
+        <v>2332</v>
+      </c>
+      <c r="J26" t="s">
+        <v>2340</v>
+      </c>
+      <c r="K26" t="s">
+        <v>2341</v>
+      </c>
+      <c r="L26" t="s">
+        <v>2342</v>
+      </c>
+      <c r="N26" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O26" t="s">
+        <v>2354</v>
       </c>
       <c r="P26" t="s">
-        <v>2359</v>
+        <v>2367</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>2368</v>
       </c>
       <c r="S26">
         <v>158</v>
       </c>
-      <c r="Z26">
+      <c r="T26">
+        <v>158</v>
+      </c>
+      <c r="U26" t="s">
+        <v>2381</v>
+      </c>
+      <c r="W26" t="s">
+        <v>2382</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>2401</v>
+      </c>
+      <c r="AA26">
         <v>46.07</v>
       </c>
-      <c r="AA26">
+      <c r="AB26">
         <v>11.13</v>
       </c>
-      <c r="AC26" t="s">
-        <v>2414</v>
-      </c>
       <c r="AD26" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AE26" t="s">
         <v>657</v>
       </c>
-      <c r="AH26" t="s">
-        <v>2421</v>
-      </c>
-      <c r="AI26" s="4" t="s">
-        <v>2426</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>1031</v>
+      <c r="AI26" t="s">
+        <v>2433</v>
+      </c>
+      <c r="AJ26" s="4" t="s">
+        <v>2438</v>
       </c>
       <c r="AK26" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AL26" t="s">
         <v>1852</v>
       </c>
-      <c r="AL26" t="s">
+      <c r="AM26" t="s">
         <v>1855</v>
       </c>
-      <c r="AM26" t="s">
-        <v>2435</v>
-      </c>
       <c r="AN26" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AO26" t="b">
+        <v>2447</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AP26" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="AF2" r:id="rId2"/>
-    <hyperlink ref="AI2" r:id="rId3"/>
-    <hyperlink ref="B3" r:id="rId4"/>
-    <hyperlink ref="B4" r:id="rId5"/>
-    <hyperlink ref="AI4" r:id="rId6"/>
-    <hyperlink ref="B5" r:id="rId7"/>
-    <hyperlink ref="AI5" r:id="rId8"/>
-    <hyperlink ref="B6" r:id="rId9"/>
-    <hyperlink ref="AI6" r:id="rId10"/>
-    <hyperlink ref="B7" r:id="rId11"/>
-    <hyperlink ref="AI7" r:id="rId12"/>
-    <hyperlink ref="B8" r:id="rId13"/>
-    <hyperlink ref="AI8" r:id="rId14"/>
-    <hyperlink ref="B9" r:id="rId15"/>
-    <hyperlink ref="AI9" r:id="rId16"/>
-    <hyperlink ref="B10" r:id="rId17"/>
-    <hyperlink ref="AI10" r:id="rId18"/>
-    <hyperlink ref="B11" r:id="rId19"/>
-    <hyperlink ref="AI11" r:id="rId20"/>
-    <hyperlink ref="B12" r:id="rId21"/>
-    <hyperlink ref="AI12" r:id="rId22"/>
-    <hyperlink ref="B13" r:id="rId23"/>
-    <hyperlink ref="AI13" r:id="rId24"/>
-    <hyperlink ref="B14" r:id="rId25"/>
-    <hyperlink ref="AI14" r:id="rId26"/>
-    <hyperlink ref="B15" r:id="rId27"/>
-    <hyperlink ref="AI15" r:id="rId28"/>
-    <hyperlink ref="B16" r:id="rId29"/>
-    <hyperlink ref="AI16" r:id="rId30"/>
-    <hyperlink ref="B17" r:id="rId31"/>
-    <hyperlink ref="AI17" r:id="rId32"/>
-    <hyperlink ref="B18" r:id="rId33"/>
-    <hyperlink ref="AI18" r:id="rId34"/>
-    <hyperlink ref="B19" r:id="rId35"/>
-    <hyperlink ref="AI19" r:id="rId36"/>
-    <hyperlink ref="B20" r:id="rId37"/>
-    <hyperlink ref="AI20" r:id="rId38"/>
-    <hyperlink ref="B21" r:id="rId39"/>
-    <hyperlink ref="AI21" r:id="rId40"/>
-    <hyperlink ref="B22" r:id="rId41"/>
-    <hyperlink ref="B23" r:id="rId42"/>
-    <hyperlink ref="B24" r:id="rId43"/>
-    <hyperlink ref="B25" r:id="rId44"/>
-    <hyperlink ref="AI25" r:id="rId45"/>
-    <hyperlink ref="B26" r:id="rId46"/>
-    <hyperlink ref="AI26" r:id="rId47"/>
+    <hyperlink ref="C2" r:id="rId2"/>
+    <hyperlink ref="AG2" r:id="rId3"/>
+    <hyperlink ref="AJ2" r:id="rId4"/>
+    <hyperlink ref="B3" r:id="rId5"/>
+    <hyperlink ref="B4" r:id="rId6"/>
+    <hyperlink ref="C4" r:id="rId7"/>
+    <hyperlink ref="AJ4" r:id="rId8"/>
+    <hyperlink ref="B5" r:id="rId9"/>
+    <hyperlink ref="C5" r:id="rId10"/>
+    <hyperlink ref="AJ5" r:id="rId11"/>
+    <hyperlink ref="B6" r:id="rId12"/>
+    <hyperlink ref="C6" r:id="rId13"/>
+    <hyperlink ref="AJ6" r:id="rId14"/>
+    <hyperlink ref="B7" r:id="rId15"/>
+    <hyperlink ref="C7" r:id="rId16"/>
+    <hyperlink ref="AJ7" r:id="rId17"/>
+    <hyperlink ref="B8" r:id="rId18"/>
+    <hyperlink ref="C8" r:id="rId19"/>
+    <hyperlink ref="AJ8" r:id="rId20"/>
+    <hyperlink ref="B9" r:id="rId21"/>
+    <hyperlink ref="C9" r:id="rId22"/>
+    <hyperlink ref="AJ9" r:id="rId23"/>
+    <hyperlink ref="B10" r:id="rId24"/>
+    <hyperlink ref="C10" r:id="rId25"/>
+    <hyperlink ref="AJ10" r:id="rId26"/>
+    <hyperlink ref="B11" r:id="rId27"/>
+    <hyperlink ref="C11" r:id="rId28"/>
+    <hyperlink ref="AJ11" r:id="rId29"/>
+    <hyperlink ref="B12" r:id="rId30"/>
+    <hyperlink ref="AJ12" r:id="rId31"/>
+    <hyperlink ref="B13" r:id="rId32"/>
+    <hyperlink ref="AJ13" r:id="rId33"/>
+    <hyperlink ref="B14" r:id="rId34"/>
+    <hyperlink ref="AJ14" r:id="rId35"/>
+    <hyperlink ref="B15" r:id="rId36"/>
+    <hyperlink ref="AJ15" r:id="rId37"/>
+    <hyperlink ref="B16" r:id="rId38"/>
+    <hyperlink ref="AJ16" r:id="rId39"/>
+    <hyperlink ref="B17" r:id="rId40"/>
+    <hyperlink ref="AJ17" r:id="rId41"/>
+    <hyperlink ref="B18" r:id="rId42"/>
+    <hyperlink ref="AJ18" r:id="rId43"/>
+    <hyperlink ref="B19" r:id="rId44"/>
+    <hyperlink ref="AJ19" r:id="rId45"/>
+    <hyperlink ref="B20" r:id="rId46"/>
+    <hyperlink ref="AJ20" r:id="rId47"/>
+    <hyperlink ref="B21" r:id="rId48"/>
+    <hyperlink ref="AJ21" r:id="rId49"/>
+    <hyperlink ref="B22" r:id="rId50"/>
+    <hyperlink ref="B23" r:id="rId51"/>
+    <hyperlink ref="B24" r:id="rId52"/>
+    <hyperlink ref="C24" r:id="rId53"/>
+    <hyperlink ref="B25" r:id="rId54"/>
+    <hyperlink ref="AJ25" r:id="rId55"/>
+    <hyperlink ref="B26" r:id="rId56"/>
+    <hyperlink ref="AJ26" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/metadata_process_scripts/sources/catalog.xlsx
+++ b/resources/metadata_process_scripts/sources/catalog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12280" uniqueCount="2449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12304" uniqueCount="2447">
   <si>
     <t>ds:DatName</t>
   </si>
@@ -7302,22 +7302,16 @@
     <t>2018-SmartUnitn2-additional_material-questionnaire</t>
   </si>
   <si>
+    <t>Dataset paper and data collection methodology</t>
+  </si>
+  <si>
     <t>https://drive.google.com/file/d/1yY8RNaWO_eh4-UnXHkL2jpZld2739K3K/view?usp=share_link</t>
   </si>
   <si>
-    <t>2018-SmartUnitn2-technical_report</t>
-  </si>
-  <si>
-    <t>2022_WeNet_Diversity1_Technical-Report(2020-2021)</t>
-  </si>
-  <si>
-    <t>2021-Chatbot1-technical_report</t>
-  </si>
-  <si>
-    <t>2022_LivePeople_Chatbot2_Data_Descriptor</t>
-  </si>
-  <si>
-    <t>Big-Thick Data generation via reference and personal context unification</t>
+    <t>https://arxiv.org/abs/2502.03347</t>
+  </si>
+  <si>
+    <t>Dataset technical report</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1mSIBHgKJBw07crEjMTYEi3ylpPL-62fB/view?usp=sharing</t>
@@ -53947,16 +53941,16 @@
         <v>2427</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="AH2" t="s">
         <v>1031</v>
       </c>
       <c r="AI2" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="AK2" t="s">
         <v>1031</v>
@@ -53968,10 +53962,10 @@
         <v>1855</v>
       </c>
       <c r="AN2" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="AO2" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP2" t="b">
         <v>1</v>
@@ -54057,10 +54051,10 @@
         <v>1855</v>
       </c>
       <c r="AN3" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="AO3" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP3" t="b">
         <v>1</v>
@@ -54142,11 +54136,20 @@
       <c r="AE4" t="s">
         <v>657</v>
       </c>
+      <c r="AF4" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>1031</v>
+      </c>
       <c r="AI4" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AJ4" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="AK4" t="s">
         <v>1031</v>
@@ -54158,10 +54161,10 @@
         <v>1856</v>
       </c>
       <c r="AN4" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="AO4" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP4" t="b">
         <v>1</v>
@@ -54243,11 +54246,20 @@
       <c r="AE5" t="s">
         <v>657</v>
       </c>
+      <c r="AF5" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>1031</v>
+      </c>
       <c r="AI5" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AJ5" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="AK5" t="s">
         <v>1031</v>
@@ -54259,10 +54271,10 @@
         <v>1857</v>
       </c>
       <c r="AN5" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="AO5" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP5" t="b">
         <v>1</v>
@@ -54347,11 +54359,20 @@
       <c r="AE6" t="s">
         <v>657</v>
       </c>
+      <c r="AF6" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AG6" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>1031</v>
+      </c>
       <c r="AI6" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AJ6" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="AK6" t="s">
         <v>1031</v>
@@ -54363,10 +54384,10 @@
         <v>1858</v>
       </c>
       <c r="AN6" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="AO6" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP6" t="b">
         <v>1</v>
@@ -54448,11 +54469,20 @@
       <c r="AE7" t="s">
         <v>657</v>
       </c>
+      <c r="AF7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>1031</v>
+      </c>
       <c r="AI7" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="AK7" t="s">
         <v>1031</v>
@@ -54464,10 +54494,10 @@
         <v>1859</v>
       </c>
       <c r="AN7" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="AO7" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP7" t="b">
         <v>1</v>
@@ -54549,11 +54579,20 @@
       <c r="AE8" t="s">
         <v>657</v>
       </c>
+      <c r="AF8" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AG8" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>1031</v>
+      </c>
       <c r="AI8" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="AK8" t="s">
         <v>1031</v>
@@ -54565,10 +54604,10 @@
         <v>1860</v>
       </c>
       <c r="AN8" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="AO8" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP8" t="b">
         <v>1</v>
@@ -54650,11 +54689,20 @@
       <c r="AE9" t="s">
         <v>657</v>
       </c>
+      <c r="AF9" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>1031</v>
+      </c>
       <c r="AI9" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AJ9" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="AK9" t="s">
         <v>1031</v>
@@ -54666,10 +54714,10 @@
         <v>1861</v>
       </c>
       <c r="AN9" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="AO9" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP9" t="b">
         <v>1</v>
@@ -54754,11 +54802,20 @@
       <c r="AE10" t="s">
         <v>657</v>
       </c>
+      <c r="AF10" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AG10" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>1031</v>
+      </c>
       <c r="AI10" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AJ10" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="AK10" t="s">
         <v>1031</v>
@@ -54770,10 +54827,10 @@
         <v>1855</v>
       </c>
       <c r="AN10" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="AO10" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP10" t="b">
         <v>1</v>
@@ -54855,11 +54912,20 @@
       <c r="AE11" t="s">
         <v>657</v>
       </c>
+      <c r="AF11" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AG11" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>1031</v>
+      </c>
       <c r="AI11" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="AJ11" s="4" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="AK11" t="s">
         <v>1031</v>
@@ -54871,10 +54937,10 @@
         <v>1862</v>
       </c>
       <c r="AN11" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="AO11" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP11" t="b">
         <v>1</v>
@@ -54957,7 +55023,7 @@
         <v>2431</v>
       </c>
       <c r="AJ12" s="4" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="AK12" t="s">
         <v>1031</v>
@@ -54969,10 +55035,10 @@
         <v>1857</v>
       </c>
       <c r="AN12" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="AO12" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP12" t="b">
         <v>1</v>
@@ -55058,7 +55124,7 @@
         <v>2431</v>
       </c>
       <c r="AJ13" s="4" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="AK13" t="s">
         <v>1031</v>
@@ -55070,10 +55136,10 @@
         <v>1858</v>
       </c>
       <c r="AN13" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="AO13" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP13" t="b">
         <v>1</v>
@@ -55156,7 +55222,7 @@
         <v>2431</v>
       </c>
       <c r="AJ14" s="4" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="AK14" t="s">
         <v>1031</v>
@@ -55168,10 +55234,10 @@
         <v>1860</v>
       </c>
       <c r="AN14" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="AO14" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP14" t="b">
         <v>1</v>
@@ -55257,7 +55323,7 @@
         <v>2431</v>
       </c>
       <c r="AJ15" s="4" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="AK15" t="s">
         <v>1031</v>
@@ -55269,10 +55335,10 @@
         <v>1855</v>
       </c>
       <c r="AN15" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="AO15" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP15" t="b">
         <v>1</v>
@@ -55355,7 +55421,7 @@
         <v>2431</v>
       </c>
       <c r="AJ16" s="4" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="AK16" t="s">
         <v>1031</v>
@@ -55367,10 +55433,10 @@
         <v>1862</v>
       </c>
       <c r="AN16" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="AO16" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP16" t="b">
         <v>1</v>
@@ -55450,10 +55516,10 @@
         <v>657</v>
       </c>
       <c r="AI17" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="AJ17" s="4" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="AK17" t="s">
         <v>1031</v>
@@ -55465,10 +55531,10 @@
         <v>1857</v>
       </c>
       <c r="AN17" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="AO17" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP17" t="b">
         <v>1</v>
@@ -55551,10 +55617,10 @@
         <v>657</v>
       </c>
       <c r="AI18" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="AJ18" s="4" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="AK18" t="s">
         <v>1031</v>
@@ -55566,10 +55632,10 @@
         <v>1858</v>
       </c>
       <c r="AN18" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="AO18" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP18" t="b">
         <v>1</v>
@@ -55649,10 +55715,10 @@
         <v>657</v>
       </c>
       <c r="AI19" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="AJ19" s="4" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="AK19" t="s">
         <v>1031</v>
@@ -55664,10 +55730,10 @@
         <v>1860</v>
       </c>
       <c r="AN19" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="AO19" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP19" t="b">
         <v>1</v>
@@ -55750,10 +55816,10 @@
         <v>657</v>
       </c>
       <c r="AI20" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="AJ20" s="4" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="AK20" t="s">
         <v>1031</v>
@@ -55765,10 +55831,10 @@
         <v>1855</v>
       </c>
       <c r="AN20" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="AO20" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP20" t="b">
         <v>1</v>
@@ -55848,10 +55914,10 @@
         <v>657</v>
       </c>
       <c r="AI21" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="AJ21" s="4" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="AK21" t="s">
         <v>1031</v>
@@ -55863,10 +55929,10 @@
         <v>1862</v>
       </c>
       <c r="AN21" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="AO21" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP21" t="b">
         <v>1</v>
@@ -55949,10 +56015,10 @@
         <v>1863</v>
       </c>
       <c r="AN22" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="AO22" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP22" t="b">
         <v>1</v>
@@ -56038,10 +56104,10 @@
         <v>1864</v>
       </c>
       <c r="AN23" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="AO23" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP23" t="b">
         <v>1</v>
@@ -56094,10 +56160,10 @@
         <v>1855</v>
       </c>
       <c r="AN24" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="AO24" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP24" t="b">
         <v>0</v>
@@ -56141,10 +56207,10 @@
         <v>657</v>
       </c>
       <c r="AI25" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="AJ25" s="4" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="AK25" t="s">
         <v>1031</v>
@@ -56156,10 +56222,10 @@
         <v>1865</v>
       </c>
       <c r="AN25" t="s">
+        <v>2444</v>
+      </c>
+      <c r="AO25" t="s">
         <v>2446</v>
-      </c>
-      <c r="AO25" t="s">
-        <v>2448</v>
       </c>
       <c r="AP25" t="b">
         <v>1</v>
@@ -56239,10 +56305,10 @@
         <v>657</v>
       </c>
       <c r="AI26" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="AJ26" s="4" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="AK26" t="s">
         <v>1031</v>
@@ -56254,10 +56320,10 @@
         <v>1855</v>
       </c>
       <c r="AN26" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="AO26" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="AP26" t="b">
         <v>1</v>
@@ -56272,56 +56338,64 @@
     <hyperlink ref="B3" r:id="rId5"/>
     <hyperlink ref="B4" r:id="rId6"/>
     <hyperlink ref="C4" r:id="rId7"/>
-    <hyperlink ref="AJ4" r:id="rId8"/>
-    <hyperlink ref="B5" r:id="rId9"/>
-    <hyperlink ref="C5" r:id="rId10"/>
-    <hyperlink ref="AJ5" r:id="rId11"/>
-    <hyperlink ref="B6" r:id="rId12"/>
-    <hyperlink ref="C6" r:id="rId13"/>
-    <hyperlink ref="AJ6" r:id="rId14"/>
-    <hyperlink ref="B7" r:id="rId15"/>
-    <hyperlink ref="C7" r:id="rId16"/>
-    <hyperlink ref="AJ7" r:id="rId17"/>
-    <hyperlink ref="B8" r:id="rId18"/>
-    <hyperlink ref="C8" r:id="rId19"/>
-    <hyperlink ref="AJ8" r:id="rId20"/>
-    <hyperlink ref="B9" r:id="rId21"/>
-    <hyperlink ref="C9" r:id="rId22"/>
-    <hyperlink ref="AJ9" r:id="rId23"/>
-    <hyperlink ref="B10" r:id="rId24"/>
-    <hyperlink ref="C10" r:id="rId25"/>
-    <hyperlink ref="AJ10" r:id="rId26"/>
-    <hyperlink ref="B11" r:id="rId27"/>
-    <hyperlink ref="C11" r:id="rId28"/>
-    <hyperlink ref="AJ11" r:id="rId29"/>
-    <hyperlink ref="B12" r:id="rId30"/>
-    <hyperlink ref="AJ12" r:id="rId31"/>
-    <hyperlink ref="B13" r:id="rId32"/>
-    <hyperlink ref="AJ13" r:id="rId33"/>
-    <hyperlink ref="B14" r:id="rId34"/>
-    <hyperlink ref="AJ14" r:id="rId35"/>
-    <hyperlink ref="B15" r:id="rId36"/>
-    <hyperlink ref="AJ15" r:id="rId37"/>
-    <hyperlink ref="B16" r:id="rId38"/>
-    <hyperlink ref="AJ16" r:id="rId39"/>
-    <hyperlink ref="B17" r:id="rId40"/>
-    <hyperlink ref="AJ17" r:id="rId41"/>
-    <hyperlink ref="B18" r:id="rId42"/>
-    <hyperlink ref="AJ18" r:id="rId43"/>
-    <hyperlink ref="B19" r:id="rId44"/>
-    <hyperlink ref="AJ19" r:id="rId45"/>
-    <hyperlink ref="B20" r:id="rId46"/>
-    <hyperlink ref="AJ20" r:id="rId47"/>
-    <hyperlink ref="B21" r:id="rId48"/>
-    <hyperlink ref="AJ21" r:id="rId49"/>
-    <hyperlink ref="B22" r:id="rId50"/>
-    <hyperlink ref="B23" r:id="rId51"/>
-    <hyperlink ref="B24" r:id="rId52"/>
-    <hyperlink ref="C24" r:id="rId53"/>
-    <hyperlink ref="B25" r:id="rId54"/>
-    <hyperlink ref="AJ25" r:id="rId55"/>
-    <hyperlink ref="B26" r:id="rId56"/>
-    <hyperlink ref="AJ26" r:id="rId57"/>
+    <hyperlink ref="AG4" r:id="rId8"/>
+    <hyperlink ref="AJ4" r:id="rId9"/>
+    <hyperlink ref="B5" r:id="rId10"/>
+    <hyperlink ref="C5" r:id="rId11"/>
+    <hyperlink ref="AG5" r:id="rId12"/>
+    <hyperlink ref="AJ5" r:id="rId13"/>
+    <hyperlink ref="B6" r:id="rId14"/>
+    <hyperlink ref="C6" r:id="rId15"/>
+    <hyperlink ref="AG6" r:id="rId16"/>
+    <hyperlink ref="AJ6" r:id="rId17"/>
+    <hyperlink ref="B7" r:id="rId18"/>
+    <hyperlink ref="C7" r:id="rId19"/>
+    <hyperlink ref="AG7" r:id="rId20"/>
+    <hyperlink ref="AJ7" r:id="rId21"/>
+    <hyperlink ref="B8" r:id="rId22"/>
+    <hyperlink ref="C8" r:id="rId23"/>
+    <hyperlink ref="AG8" r:id="rId24"/>
+    <hyperlink ref="AJ8" r:id="rId25"/>
+    <hyperlink ref="B9" r:id="rId26"/>
+    <hyperlink ref="C9" r:id="rId27"/>
+    <hyperlink ref="AG9" r:id="rId28"/>
+    <hyperlink ref="AJ9" r:id="rId29"/>
+    <hyperlink ref="B10" r:id="rId30"/>
+    <hyperlink ref="C10" r:id="rId31"/>
+    <hyperlink ref="AG10" r:id="rId32"/>
+    <hyperlink ref="AJ10" r:id="rId33"/>
+    <hyperlink ref="B11" r:id="rId34"/>
+    <hyperlink ref="C11" r:id="rId35"/>
+    <hyperlink ref="AG11" r:id="rId36"/>
+    <hyperlink ref="AJ11" r:id="rId37"/>
+    <hyperlink ref="B12" r:id="rId38"/>
+    <hyperlink ref="AJ12" r:id="rId39"/>
+    <hyperlink ref="B13" r:id="rId40"/>
+    <hyperlink ref="AJ13" r:id="rId41"/>
+    <hyperlink ref="B14" r:id="rId42"/>
+    <hyperlink ref="AJ14" r:id="rId43"/>
+    <hyperlink ref="B15" r:id="rId44"/>
+    <hyperlink ref="AJ15" r:id="rId45"/>
+    <hyperlink ref="B16" r:id="rId46"/>
+    <hyperlink ref="AJ16" r:id="rId47"/>
+    <hyperlink ref="B17" r:id="rId48"/>
+    <hyperlink ref="AJ17" r:id="rId49"/>
+    <hyperlink ref="B18" r:id="rId50"/>
+    <hyperlink ref="AJ18" r:id="rId51"/>
+    <hyperlink ref="B19" r:id="rId52"/>
+    <hyperlink ref="AJ19" r:id="rId53"/>
+    <hyperlink ref="B20" r:id="rId54"/>
+    <hyperlink ref="AJ20" r:id="rId55"/>
+    <hyperlink ref="B21" r:id="rId56"/>
+    <hyperlink ref="AJ21" r:id="rId57"/>
+    <hyperlink ref="B22" r:id="rId58"/>
+    <hyperlink ref="B23" r:id="rId59"/>
+    <hyperlink ref="B24" r:id="rId60"/>
+    <hyperlink ref="C24" r:id="rId61"/>
+    <hyperlink ref="B25" r:id="rId62"/>
+    <hyperlink ref="AJ25" r:id="rId63"/>
+    <hyperlink ref="B26" r:id="rId64"/>
+    <hyperlink ref="AJ26" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/metadata_process_scripts/sources/catalog.xlsx
+++ b/resources/metadata_process_scripts/sources/catalog.xlsx
@@ -4083,7 +4083,7 @@
     <t>002.AAAB.AAA.BS</t>
   </si>
   <si>
-    <t>002.AAAB.AAA.None</t>
+    <t>002.AAAB.AAA.AP</t>
   </si>
   <si>
     <t>002.AAAB.AAA.AG</t>
@@ -6378,7 +6378,7 @@
     <t>002.AAAB.AAA.BS-BT-BU-BV-BW-BX-BY</t>
   </si>
   <si>
-    <t>002.AAAB.AAA.None-AR-AS-AT</t>
+    <t>002.AAAB.AAA.AP-AR-AS-AT</t>
   </si>
   <si>
     <t>002.AAAB.AAA.AY-CF-BA-BB-BD-BG</t>

--- a/resources/metadata_process_scripts/sources/catalog.xlsx
+++ b/resources/metadata_process_scripts/sources/catalog.xlsx
@@ -4683,10 +4683,10 @@
     <t>https://drive.google.com/file/d/1fXlb2vJfp_HOs4XP_3jaLYM7rTipGygO/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/16loX2mvErVw_fzrBAYLX3uIwc_3FrwrA/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1i7-1KpYq-e7bkmqsACY_38sRtYwUpo1j/view?usp=sharing</t>
+    <t>https://drive.google.com/file/d/1jhkBFcruJil2f09xV1dYpjgQL-yqcbaj/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bOYnYNkhHjpRO1WW0e2yDCSrKd4KwA-s/view?usp=drive_link</t>
   </si>
   <si>
     <t>002.AAAB.AAA.AY</t>

--- a/resources/metadata_process_scripts/sources/catalog.xlsx
+++ b/resources/metadata_process_scripts/sources/catalog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12451" uniqueCount="2434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11854" uniqueCount="2434">
   <si>
     <t>ds:prjTitle</t>
   </si>
@@ -3873,10 +3873,10 @@
     <t>direct observation</t>
   </si>
   <si>
-    <t>Download request</t>
-  </si>
-  <si>
-    <t>https://datascientiafoundation.github.io/LivePeople/resources/download_request.pdf</t>
+    <t>Web form</t>
+  </si>
+  <si>
+    <t>https://ds.datascientia.eu/marketplace/welcome</t>
   </si>
   <si>
     <t>Codebook</t>
@@ -10565,9 +10565,6 @@
       <c r="AD2" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE2" t="s">
-        <v>212</v>
-      </c>
       <c r="AF2" t="s">
         <v>1287</v>
       </c>
@@ -10645,9 +10642,6 @@
       <c r="AD3" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE3" t="s">
-        <v>212</v>
-      </c>
       <c r="AF3" t="s">
         <v>1287</v>
       </c>
@@ -10725,9 +10719,6 @@
       <c r="AD4" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE4" t="s">
-        <v>212</v>
-      </c>
       <c r="AF4" t="s">
         <v>1287</v>
       </c>
@@ -10805,9 +10796,6 @@
       <c r="AD5" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE5" t="s">
-        <v>212</v>
-      </c>
       <c r="AF5" t="s">
         <v>1287</v>
       </c>
@@ -10885,9 +10873,6 @@
       <c r="AD6" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE6" t="s">
-        <v>212</v>
-      </c>
       <c r="AF6" t="s">
         <v>1287</v>
       </c>
@@ -10965,9 +10950,6 @@
       <c r="AD7" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE7" t="s">
-        <v>212</v>
-      </c>
       <c r="AF7" t="s">
         <v>1287</v>
       </c>
@@ -11045,9 +11027,6 @@
       <c r="AD8" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE8" t="s">
-        <v>212</v>
-      </c>
       <c r="AF8" t="s">
         <v>1287</v>
       </c>
@@ -11125,9 +11104,6 @@
       <c r="AD9" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE9" t="s">
-        <v>212</v>
-      </c>
       <c r="AF9" t="s">
         <v>1287</v>
       </c>
@@ -11205,9 +11181,6 @@
       <c r="AD10" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE10" t="s">
-        <v>212</v>
-      </c>
       <c r="AF10" t="s">
         <v>1287</v>
       </c>
@@ -11285,9 +11258,6 @@
       <c r="AD11" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE11" t="s">
-        <v>212</v>
-      </c>
       <c r="AF11" t="s">
         <v>1287</v>
       </c>
@@ -11365,9 +11335,6 @@
       <c r="AD12" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE12" t="s">
-        <v>212</v>
-      </c>
       <c r="AF12" t="s">
         <v>1287</v>
       </c>
@@ -11445,9 +11412,6 @@
       <c r="AD13" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE13" t="s">
-        <v>212</v>
-      </c>
       <c r="AF13" t="s">
         <v>1287</v>
       </c>
@@ -11525,9 +11489,6 @@
       <c r="AD14" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE14" t="s">
-        <v>212</v>
-      </c>
       <c r="AF14" t="s">
         <v>1287</v>
       </c>
@@ -11605,9 +11566,6 @@
       <c r="AD15" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE15" t="s">
-        <v>212</v>
-      </c>
       <c r="AF15" t="s">
         <v>1287</v>
       </c>
@@ -11685,9 +11643,6 @@
       <c r="AD16" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE16" t="s">
-        <v>212</v>
-      </c>
       <c r="AF16" t="s">
         <v>1287</v>
       </c>
@@ -11765,9 +11720,6 @@
       <c r="AD17" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE17" t="s">
-        <v>212</v>
-      </c>
       <c r="AF17" t="s">
         <v>1287</v>
       </c>
@@ -11845,9 +11797,6 @@
       <c r="AD18" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE18" t="s">
-        <v>212</v>
-      </c>
       <c r="AF18" t="s">
         <v>1287</v>
       </c>
@@ -11925,9 +11874,6 @@
       <c r="AD19" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE19" t="s">
-        <v>212</v>
-      </c>
       <c r="AF19" t="s">
         <v>1287</v>
       </c>
@@ -12005,9 +11951,6 @@
       <c r="AD20" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE20" t="s">
-        <v>212</v>
-      </c>
       <c r="AF20" t="s">
         <v>1287</v>
       </c>
@@ -12085,9 +12028,6 @@
       <c r="AD21" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE21" t="s">
-        <v>212</v>
-      </c>
       <c r="AF21" t="s">
         <v>1287</v>
       </c>
@@ -12165,9 +12105,6 @@
       <c r="AD22" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE22" t="s">
-        <v>212</v>
-      </c>
       <c r="AF22" t="s">
         <v>1287</v>
       </c>
@@ -12242,9 +12179,6 @@
       <c r="AD23" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE23" t="s">
-        <v>212</v>
-      </c>
       <c r="AF23" t="s">
         <v>1287</v>
       </c>
@@ -12322,9 +12256,6 @@
       <c r="AD24" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE24" t="s">
-        <v>212</v>
-      </c>
       <c r="AF24" t="s">
         <v>1287</v>
       </c>
@@ -12402,9 +12333,6 @@
       <c r="AD25" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE25" t="s">
-        <v>212</v>
-      </c>
       <c r="AF25" t="s">
         <v>1287</v>
       </c>
@@ -12482,9 +12410,6 @@
       <c r="AD26" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE26" t="s">
-        <v>212</v>
-      </c>
       <c r="AF26" t="s">
         <v>1287</v>
       </c>
@@ -12562,9 +12487,6 @@
       <c r="AD27" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE27" t="s">
-        <v>212</v>
-      </c>
       <c r="AF27" t="s">
         <v>1287</v>
       </c>
@@ -12639,9 +12561,6 @@
       <c r="AD28" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE28" t="s">
-        <v>212</v>
-      </c>
       <c r="AF28" t="s">
         <v>1287</v>
       </c>
@@ -12719,9 +12638,6 @@
       <c r="AD29" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE29" t="s">
-        <v>212</v>
-      </c>
       <c r="AF29" t="s">
         <v>1287</v>
       </c>
@@ -12799,9 +12715,6 @@
       <c r="AD30" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE30" t="s">
-        <v>212</v>
-      </c>
       <c r="AF30" t="s">
         <v>1287</v>
       </c>
@@ -12879,9 +12792,6 @@
       <c r="AD31" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE31" t="s">
-        <v>212</v>
-      </c>
       <c r="AF31" t="s">
         <v>1287</v>
       </c>
@@ -12959,9 +12869,6 @@
       <c r="AD32" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE32" t="s">
-        <v>212</v>
-      </c>
       <c r="AL32" t="s">
         <v>1611</v>
       </c>
@@ -13030,9 +12937,6 @@
       <c r="AD33" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE33" t="s">
-        <v>212</v>
-      </c>
       <c r="AL33" t="s">
         <v>1612</v>
       </c>
@@ -13101,9 +13005,6 @@
       <c r="AD34" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE34" t="s">
-        <v>212</v>
-      </c>
       <c r="AL34" t="s">
         <v>1613</v>
       </c>
@@ -13172,9 +13073,6 @@
       <c r="AD35" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE35" t="s">
-        <v>212</v>
-      </c>
       <c r="AL35" t="s">
         <v>1614</v>
       </c>
@@ -13243,9 +13141,6 @@
       <c r="AD36" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE36" t="s">
-        <v>212</v>
-      </c>
       <c r="AL36" t="s">
         <v>1615</v>
       </c>
@@ -13314,9 +13209,6 @@
       <c r="AD37" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE37" t="s">
-        <v>212</v>
-      </c>
       <c r="AF37" t="s">
         <v>1287</v>
       </c>
@@ -13394,9 +13286,6 @@
       <c r="AD38" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE38" t="s">
-        <v>212</v>
-      </c>
       <c r="AF38" t="s">
         <v>1287</v>
       </c>
@@ -13474,9 +13363,6 @@
       <c r="AD39" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE39" t="s">
-        <v>212</v>
-      </c>
       <c r="AF39" t="s">
         <v>1287</v>
       </c>
@@ -13554,9 +13440,6 @@
       <c r="AD40" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE40" t="s">
-        <v>212</v>
-      </c>
       <c r="AF40" t="s">
         <v>1287</v>
       </c>
@@ -13634,9 +13517,6 @@
       <c r="AD41" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE41" t="s">
-        <v>212</v>
-      </c>
       <c r="AF41" t="s">
         <v>1287</v>
       </c>
@@ -13714,9 +13594,6 @@
       <c r="AD42" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE42" t="s">
-        <v>212</v>
-      </c>
       <c r="AF42" t="s">
         <v>1287</v>
       </c>
@@ -13794,9 +13671,6 @@
       <c r="AD43" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE43" t="s">
-        <v>212</v>
-      </c>
       <c r="AF43" t="s">
         <v>1287</v>
       </c>
@@ -13874,9 +13748,6 @@
       <c r="AD44" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE44" t="s">
-        <v>212</v>
-      </c>
       <c r="AF44" t="s">
         <v>1287</v>
       </c>
@@ -13954,9 +13825,6 @@
       <c r="AD45" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE45" t="s">
-        <v>212</v>
-      </c>
       <c r="AF45" t="s">
         <v>1287</v>
       </c>
@@ -14034,9 +13902,6 @@
       <c r="AD46" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE46" t="s">
-        <v>212</v>
-      </c>
       <c r="AF46" t="s">
         <v>1287</v>
       </c>
@@ -14114,9 +13979,6 @@
       <c r="AD47" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE47" t="s">
-        <v>212</v>
-      </c>
       <c r="AF47" t="s">
         <v>1287</v>
       </c>
@@ -14194,9 +14056,6 @@
       <c r="AD48" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE48" t="s">
-        <v>212</v>
-      </c>
       <c r="AF48" t="s">
         <v>1287</v>
       </c>
@@ -14274,9 +14133,6 @@
       <c r="AD49" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE49" t="s">
-        <v>212</v>
-      </c>
       <c r="AL49" t="s">
         <v>1628</v>
       </c>
@@ -14345,9 +14201,6 @@
       <c r="AD50" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE50" t="s">
-        <v>212</v>
-      </c>
       <c r="AF50" t="s">
         <v>1287</v>
       </c>
@@ -14425,9 +14278,6 @@
       <c r="AD51" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE51" t="s">
-        <v>212</v>
-      </c>
       <c r="AF51" t="s">
         <v>1287</v>
       </c>
@@ -14505,9 +14355,6 @@
       <c r="AD52" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE52" t="s">
-        <v>212</v>
-      </c>
       <c r="AF52" t="s">
         <v>1287</v>
       </c>
@@ -14585,9 +14432,6 @@
       <c r="AD53" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE53" t="s">
-        <v>212</v>
-      </c>
       <c r="AF53" t="s">
         <v>1287</v>
       </c>
@@ -14665,9 +14509,6 @@
       <c r="AD54" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE54" t="s">
-        <v>212</v>
-      </c>
       <c r="AF54" t="s">
         <v>1287</v>
       </c>
@@ -14745,9 +14586,6 @@
       <c r="AD55" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE55" t="s">
-        <v>212</v>
-      </c>
       <c r="AF55" t="s">
         <v>1287</v>
       </c>
@@ -14822,9 +14660,6 @@
       <c r="AD56" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE56" t="s">
-        <v>212</v>
-      </c>
       <c r="AF56" t="s">
         <v>1287</v>
       </c>
@@ -14908,9 +14743,6 @@
       <c r="AD57" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE57" t="s">
-        <v>212</v>
-      </c>
       <c r="AF57" t="s">
         <v>1287</v>
       </c>
@@ -14994,9 +14826,6 @@
       <c r="AD58" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE58" t="s">
-        <v>212</v>
-      </c>
       <c r="AF58" t="s">
         <v>1287</v>
       </c>
@@ -15083,9 +14912,6 @@
       <c r="AD59" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE59" t="s">
-        <v>212</v>
-      </c>
       <c r="AF59" t="s">
         <v>1287</v>
       </c>
@@ -15163,9 +14989,6 @@
       <c r="AD60" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE60" t="s">
-        <v>212</v>
-      </c>
       <c r="AF60" t="s">
         <v>1287</v>
       </c>
@@ -15243,9 +15066,6 @@
       <c r="AD61" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE61" t="s">
-        <v>212</v>
-      </c>
       <c r="AF61" t="s">
         <v>1287</v>
       </c>
@@ -15323,9 +15143,6 @@
       <c r="AD62" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE62" t="s">
-        <v>212</v>
-      </c>
       <c r="AF62" t="s">
         <v>1287</v>
       </c>
@@ -15400,9 +15217,6 @@
       <c r="AD63" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE63" t="s">
-        <v>212</v>
-      </c>
       <c r="AF63" t="s">
         <v>1287</v>
       </c>
@@ -15480,9 +15294,6 @@
       <c r="AD64" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE64" t="s">
-        <v>212</v>
-      </c>
       <c r="AF64" t="s">
         <v>1287</v>
       </c>
@@ -15560,9 +15371,6 @@
       <c r="AD65" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE65" t="s">
-        <v>212</v>
-      </c>
       <c r="AF65" t="s">
         <v>1287</v>
       </c>
@@ -15640,9 +15448,6 @@
       <c r="AD66" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE66" t="s">
-        <v>212</v>
-      </c>
       <c r="AF66" t="s">
         <v>1287</v>
       </c>
@@ -15720,9 +15525,6 @@
       <c r="AD67" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE67" t="s">
-        <v>212</v>
-      </c>
       <c r="AF67" t="s">
         <v>1287</v>
       </c>
@@ -15800,9 +15602,6 @@
       <c r="AD68" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE68" t="s">
-        <v>212</v>
-      </c>
       <c r="AF68" t="s">
         <v>1287</v>
       </c>
@@ -15880,9 +15679,6 @@
       <c r="AD69" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE69" t="s">
-        <v>212</v>
-      </c>
       <c r="AF69" t="s">
         <v>1287</v>
       </c>
@@ -15960,9 +15756,6 @@
       <c r="AD70" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE70" t="s">
-        <v>212</v>
-      </c>
       <c r="AF70" t="s">
         <v>1287</v>
       </c>
@@ -16040,9 +15833,6 @@
       <c r="AD71" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE71" t="s">
-        <v>212</v>
-      </c>
       <c r="AF71" t="s">
         <v>1287</v>
       </c>
@@ -16120,9 +15910,6 @@
       <c r="AD72" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE72" t="s">
-        <v>212</v>
-      </c>
       <c r="AF72" t="s">
         <v>1287</v>
       </c>
@@ -16200,9 +15987,6 @@
       <c r="AD73" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE73" t="s">
-        <v>212</v>
-      </c>
       <c r="AF73" t="s">
         <v>1287</v>
       </c>
@@ -16280,9 +16064,6 @@
       <c r="AD74" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE74" t="s">
-        <v>212</v>
-      </c>
       <c r="AF74" t="s">
         <v>1287</v>
       </c>
@@ -16360,9 +16141,6 @@
       <c r="AD75" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE75" t="s">
-        <v>212</v>
-      </c>
       <c r="AF75" t="s">
         <v>1287</v>
       </c>
@@ -16440,9 +16218,6 @@
       <c r="AD76" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE76" t="s">
-        <v>212</v>
-      </c>
       <c r="AF76" t="s">
         <v>1287</v>
       </c>
@@ -16520,9 +16295,6 @@
       <c r="AD77" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE77" t="s">
-        <v>212</v>
-      </c>
       <c r="AF77" t="s">
         <v>1287</v>
       </c>
@@ -16600,9 +16372,6 @@
       <c r="AD78" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE78" t="s">
-        <v>212</v>
-      </c>
       <c r="AF78" t="s">
         <v>1287</v>
       </c>
@@ -16680,9 +16449,6 @@
       <c r="AD79" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE79" t="s">
-        <v>212</v>
-      </c>
       <c r="AF79" t="s">
         <v>1287</v>
       </c>
@@ -16760,9 +16526,6 @@
       <c r="AD80" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE80" t="s">
-        <v>212</v>
-      </c>
       <c r="AL80" t="s">
         <v>1659</v>
       </c>
@@ -16831,9 +16594,6 @@
       <c r="AD81" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE81" t="s">
-        <v>212</v>
-      </c>
       <c r="AF81" t="s">
         <v>1287</v>
       </c>
@@ -16911,9 +16671,6 @@
       <c r="AD82" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE82" t="s">
-        <v>212</v>
-      </c>
       <c r="AL82" t="s">
         <v>1661</v>
       </c>
@@ -16982,9 +16739,6 @@
       <c r="AD83" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE83" t="s">
-        <v>212</v>
-      </c>
       <c r="AF83" t="s">
         <v>1287</v>
       </c>
@@ -17062,9 +16816,6 @@
       <c r="AD84" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE84" t="s">
-        <v>212</v>
-      </c>
       <c r="AF84" t="s">
         <v>1287</v>
       </c>
@@ -17142,9 +16893,6 @@
       <c r="AD85" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE85" t="s">
-        <v>212</v>
-      </c>
       <c r="AF85" t="s">
         <v>1287</v>
       </c>
@@ -17222,9 +16970,6 @@
       <c r="AD86" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE86" t="s">
-        <v>212</v>
-      </c>
       <c r="AF86" t="s">
         <v>1287</v>
       </c>
@@ -17299,9 +17044,6 @@
       <c r="AD87" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE87" t="s">
-        <v>212</v>
-      </c>
       <c r="AF87" t="s">
         <v>1287</v>
       </c>
@@ -17385,9 +17127,6 @@
       <c r="AD88" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE88" t="s">
-        <v>212</v>
-      </c>
       <c r="AF88" t="s">
         <v>1287</v>
       </c>
@@ -17471,9 +17210,6 @@
       <c r="AD89" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE89" t="s">
-        <v>212</v>
-      </c>
       <c r="AF89" t="s">
         <v>1287</v>
       </c>
@@ -17560,9 +17296,6 @@
       <c r="AD90" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE90" t="s">
-        <v>212</v>
-      </c>
       <c r="AF90" t="s">
         <v>1287</v>
       </c>
@@ -17640,9 +17373,6 @@
       <c r="AD91" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE91" t="s">
-        <v>212</v>
-      </c>
       <c r="AF91" t="s">
         <v>1287</v>
       </c>
@@ -17720,9 +17450,6 @@
       <c r="AD92" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE92" t="s">
-        <v>212</v>
-      </c>
       <c r="AF92" t="s">
         <v>1287</v>
       </c>
@@ -17800,9 +17527,6 @@
       <c r="AD93" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE93" t="s">
-        <v>212</v>
-      </c>
       <c r="AF93" t="s">
         <v>1287</v>
       </c>
@@ -17877,9 +17601,6 @@
       <c r="AD94" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE94" t="s">
-        <v>212</v>
-      </c>
       <c r="AF94" t="s">
         <v>1287</v>
       </c>
@@ -17957,9 +17678,6 @@
       <c r="AD95" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE95" t="s">
-        <v>212</v>
-      </c>
       <c r="AF95" t="s">
         <v>1287</v>
       </c>
@@ -18037,9 +17755,6 @@
       <c r="AD96" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE96" t="s">
-        <v>212</v>
-      </c>
       <c r="AF96" t="s">
         <v>1287</v>
       </c>
@@ -18117,9 +17832,6 @@
       <c r="AD97" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE97" t="s">
-        <v>212</v>
-      </c>
       <c r="AF97" t="s">
         <v>1287</v>
       </c>
@@ -18197,9 +17909,6 @@
       <c r="AD98" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE98" t="s">
-        <v>212</v>
-      </c>
       <c r="AF98" t="s">
         <v>1287</v>
       </c>
@@ -18277,9 +17986,6 @@
       <c r="AD99" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE99" t="s">
-        <v>212</v>
-      </c>
       <c r="AF99" t="s">
         <v>1287</v>
       </c>
@@ -18357,9 +18063,6 @@
       <c r="AD100" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE100" t="s">
-        <v>212</v>
-      </c>
       <c r="AF100" t="s">
         <v>1287</v>
       </c>
@@ -18437,9 +18140,6 @@
       <c r="AD101" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE101" t="s">
-        <v>212</v>
-      </c>
       <c r="AF101" t="s">
         <v>1287</v>
       </c>
@@ -18517,9 +18217,6 @@
       <c r="AD102" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE102" t="s">
-        <v>212</v>
-      </c>
       <c r="AF102" t="s">
         <v>1287</v>
       </c>
@@ -18597,9 +18294,6 @@
       <c r="AD103" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE103" t="s">
-        <v>212</v>
-      </c>
       <c r="AF103" t="s">
         <v>1287</v>
       </c>
@@ -18677,9 +18371,6 @@
       <c r="AD104" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE104" t="s">
-        <v>212</v>
-      </c>
       <c r="AF104" t="s">
         <v>1287</v>
       </c>
@@ -18757,9 +18448,6 @@
       <c r="AD105" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE105" t="s">
-        <v>212</v>
-      </c>
       <c r="AF105" t="s">
         <v>1287</v>
       </c>
@@ -18837,9 +18525,6 @@
       <c r="AD106" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE106" t="s">
-        <v>212</v>
-      </c>
       <c r="AF106" t="s">
         <v>1287</v>
       </c>
@@ -18917,9 +18602,6 @@
       <c r="AD107" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE107" t="s">
-        <v>212</v>
-      </c>
       <c r="AF107" t="s">
         <v>1287</v>
       </c>
@@ -18997,9 +18679,6 @@
       <c r="AD108" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE108" t="s">
-        <v>212</v>
-      </c>
       <c r="AF108" t="s">
         <v>1287</v>
       </c>
@@ -19077,9 +18756,6 @@
       <c r="AD109" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE109" t="s">
-        <v>212</v>
-      </c>
       <c r="AF109" t="s">
         <v>1287</v>
       </c>
@@ -19157,9 +18833,6 @@
       <c r="AD110" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE110" t="s">
-        <v>212</v>
-      </c>
       <c r="AF110" t="s">
         <v>1287</v>
       </c>
@@ -19237,9 +18910,6 @@
       <c r="AD111" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE111" t="s">
-        <v>212</v>
-      </c>
       <c r="AL111" t="s">
         <v>1690</v>
       </c>
@@ -19308,9 +18978,6 @@
       <c r="AD112" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE112" t="s">
-        <v>212</v>
-      </c>
       <c r="AF112" t="s">
         <v>1287</v>
       </c>
@@ -19388,9 +19055,6 @@
       <c r="AD113" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE113" t="s">
-        <v>212</v>
-      </c>
       <c r="AL113" t="s">
         <v>1692</v>
       </c>
@@ -19459,9 +19123,6 @@
       <c r="AD114" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE114" t="s">
-        <v>212</v>
-      </c>
       <c r="AF114" t="s">
         <v>1287</v>
       </c>
@@ -19539,9 +19200,6 @@
       <c r="AD115" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE115" t="s">
-        <v>212</v>
-      </c>
       <c r="AF115" t="s">
         <v>1287</v>
       </c>
@@ -19619,9 +19277,6 @@
       <c r="AD116" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE116" t="s">
-        <v>212</v>
-      </c>
       <c r="AF116" t="s">
         <v>1287</v>
       </c>
@@ -19699,9 +19354,6 @@
       <c r="AD117" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE117" t="s">
-        <v>212</v>
-      </c>
       <c r="AF117" t="s">
         <v>1287</v>
       </c>
@@ -19776,9 +19428,6 @@
       <c r="AD118" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE118" t="s">
-        <v>212</v>
-      </c>
       <c r="AF118" t="s">
         <v>1287</v>
       </c>
@@ -19862,9 +19511,6 @@
       <c r="AD119" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE119" t="s">
-        <v>212</v>
-      </c>
       <c r="AF119" t="s">
         <v>1287</v>
       </c>
@@ -19948,9 +19594,6 @@
       <c r="AD120" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE120" t="s">
-        <v>212</v>
-      </c>
       <c r="AF120" t="s">
         <v>1287</v>
       </c>
@@ -20037,9 +19680,6 @@
       <c r="AD121" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE121" t="s">
-        <v>212</v>
-      </c>
       <c r="AF121" t="s">
         <v>1287</v>
       </c>
@@ -20117,9 +19757,6 @@
       <c r="AD122" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE122" t="s">
-        <v>212</v>
-      </c>
       <c r="AF122" t="s">
         <v>1287</v>
       </c>
@@ -20197,9 +19834,6 @@
       <c r="AD123" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE123" t="s">
-        <v>212</v>
-      </c>
       <c r="AF123" t="s">
         <v>1287</v>
       </c>
@@ -20277,9 +19911,6 @@
       <c r="AD124" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE124" t="s">
-        <v>212</v>
-      </c>
       <c r="AF124" t="s">
         <v>1287</v>
       </c>
@@ -20354,9 +19985,6 @@
       <c r="AD125" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE125" t="s">
-        <v>212</v>
-      </c>
       <c r="AF125" t="s">
         <v>1287</v>
       </c>
@@ -20434,9 +20062,6 @@
       <c r="AD126" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE126" t="s">
-        <v>212</v>
-      </c>
       <c r="AF126" t="s">
         <v>1287</v>
       </c>
@@ -20514,9 +20139,6 @@
       <c r="AD127" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE127" t="s">
-        <v>212</v>
-      </c>
       <c r="AF127" t="s">
         <v>1287</v>
       </c>
@@ -20594,9 +20216,6 @@
       <c r="AD128" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE128" t="s">
-        <v>212</v>
-      </c>
       <c r="AF128" t="s">
         <v>1287</v>
       </c>
@@ -20674,9 +20293,6 @@
       <c r="AD129" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE129" t="s">
-        <v>212</v>
-      </c>
       <c r="AF129" t="s">
         <v>1287</v>
       </c>
@@ -20754,9 +20370,6 @@
       <c r="AD130" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE130" t="s">
-        <v>212</v>
-      </c>
       <c r="AF130" t="s">
         <v>1287</v>
       </c>
@@ -20834,9 +20447,6 @@
       <c r="AD131" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE131" t="s">
-        <v>212</v>
-      </c>
       <c r="AF131" t="s">
         <v>1287</v>
       </c>
@@ -20914,9 +20524,6 @@
       <c r="AD132" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE132" t="s">
-        <v>212</v>
-      </c>
       <c r="AF132" t="s">
         <v>1287</v>
       </c>
@@ -20994,9 +20601,6 @@
       <c r="AD133" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE133" t="s">
-        <v>212</v>
-      </c>
       <c r="AF133" t="s">
         <v>1287</v>
       </c>
@@ -21074,9 +20678,6 @@
       <c r="AD134" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE134" t="s">
-        <v>212</v>
-      </c>
       <c r="AF134" t="s">
         <v>1287</v>
       </c>
@@ -21154,9 +20755,6 @@
       <c r="AD135" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE135" t="s">
-        <v>212</v>
-      </c>
       <c r="AF135" t="s">
         <v>1287</v>
       </c>
@@ -21234,9 +20832,6 @@
       <c r="AD136" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE136" t="s">
-        <v>212</v>
-      </c>
       <c r="AF136" t="s">
         <v>1287</v>
       </c>
@@ -21314,9 +20909,6 @@
       <c r="AD137" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE137" t="s">
-        <v>212</v>
-      </c>
       <c r="AF137" t="s">
         <v>1287</v>
       </c>
@@ -21394,9 +20986,6 @@
       <c r="AD138" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE138" t="s">
-        <v>212</v>
-      </c>
       <c r="AF138" t="s">
         <v>1287</v>
       </c>
@@ -21474,9 +21063,6 @@
       <c r="AD139" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE139" t="s">
-        <v>212</v>
-      </c>
       <c r="AF139" t="s">
         <v>1287</v>
       </c>
@@ -21554,9 +21140,6 @@
       <c r="AD140" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE140" t="s">
-        <v>212</v>
-      </c>
       <c r="AF140" t="s">
         <v>1287</v>
       </c>
@@ -21634,9 +21217,6 @@
       <c r="AD141" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE141" t="s">
-        <v>212</v>
-      </c>
       <c r="AF141" t="s">
         <v>1287</v>
       </c>
@@ -21714,9 +21294,6 @@
       <c r="AD142" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE142" t="s">
-        <v>212</v>
-      </c>
       <c r="AL142" t="s">
         <v>1721</v>
       </c>
@@ -21785,9 +21362,6 @@
       <c r="AD143" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE143" t="s">
-        <v>212</v>
-      </c>
       <c r="AF143" t="s">
         <v>1287</v>
       </c>
@@ -21865,9 +21439,6 @@
       <c r="AD144" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE144" t="s">
-        <v>212</v>
-      </c>
       <c r="AL144" t="s">
         <v>1723</v>
       </c>
@@ -21936,9 +21507,6 @@
       <c r="AD145" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE145" t="s">
-        <v>212</v>
-      </c>
       <c r="AF145" t="s">
         <v>1287</v>
       </c>
@@ -22016,9 +21584,6 @@
       <c r="AD146" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE146" t="s">
-        <v>212</v>
-      </c>
       <c r="AF146" t="s">
         <v>1287</v>
       </c>
@@ -22096,9 +21661,6 @@
       <c r="AD147" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE147" t="s">
-        <v>212</v>
-      </c>
       <c r="AF147" t="s">
         <v>1287</v>
       </c>
@@ -22176,9 +21738,6 @@
       <c r="AD148" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE148" t="s">
-        <v>212</v>
-      </c>
       <c r="AF148" t="s">
         <v>1287</v>
       </c>
@@ -22253,9 +21812,6 @@
       <c r="AD149" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE149" t="s">
-        <v>212</v>
-      </c>
       <c r="AF149" t="s">
         <v>1287</v>
       </c>
@@ -22339,9 +21895,6 @@
       <c r="AD150" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE150" t="s">
-        <v>212</v>
-      </c>
       <c r="AF150" t="s">
         <v>1287</v>
       </c>
@@ -22425,9 +21978,6 @@
       <c r="AD151" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE151" t="s">
-        <v>212</v>
-      </c>
       <c r="AF151" t="s">
         <v>1287</v>
       </c>
@@ -22514,9 +22064,6 @@
       <c r="AD152" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE152" t="s">
-        <v>212</v>
-      </c>
       <c r="AF152" t="s">
         <v>1287</v>
       </c>
@@ -22594,9 +22141,6 @@
       <c r="AD153" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE153" t="s">
-        <v>212</v>
-      </c>
       <c r="AF153" t="s">
         <v>1287</v>
       </c>
@@ -22674,9 +22218,6 @@
       <c r="AD154" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE154" t="s">
-        <v>212</v>
-      </c>
       <c r="AF154" t="s">
         <v>1287</v>
       </c>
@@ -22754,9 +22295,6 @@
       <c r="AD155" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE155" t="s">
-        <v>212</v>
-      </c>
       <c r="AF155" t="s">
         <v>1287</v>
       </c>
@@ -22831,9 +22369,6 @@
       <c r="AD156" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE156" t="s">
-        <v>212</v>
-      </c>
       <c r="AF156" t="s">
         <v>1287</v>
       </c>
@@ -22911,9 +22446,6 @@
       <c r="AD157" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE157" t="s">
-        <v>212</v>
-      </c>
       <c r="AF157" t="s">
         <v>1287</v>
       </c>
@@ -22991,9 +22523,6 @@
       <c r="AD158" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE158" t="s">
-        <v>212</v>
-      </c>
       <c r="AF158" t="s">
         <v>1287</v>
       </c>
@@ -23071,9 +22600,6 @@
       <c r="AD159" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE159" t="s">
-        <v>212</v>
-      </c>
       <c r="AF159" t="s">
         <v>1287</v>
       </c>
@@ -23151,9 +22677,6 @@
       <c r="AD160" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE160" t="s">
-        <v>212</v>
-      </c>
       <c r="AF160" t="s">
         <v>1287</v>
       </c>
@@ -23231,9 +22754,6 @@
       <c r="AD161" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE161" t="s">
-        <v>212</v>
-      </c>
       <c r="AF161" t="s">
         <v>1287</v>
       </c>
@@ -23311,9 +22831,6 @@
       <c r="AD162" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE162" t="s">
-        <v>212</v>
-      </c>
       <c r="AF162" t="s">
         <v>1287</v>
       </c>
@@ -23391,9 +22908,6 @@
       <c r="AD163" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE163" t="s">
-        <v>212</v>
-      </c>
       <c r="AF163" t="s">
         <v>1287</v>
       </c>
@@ -23471,9 +22985,6 @@
       <c r="AD164" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE164" t="s">
-        <v>212</v>
-      </c>
       <c r="AF164" t="s">
         <v>1287</v>
       </c>
@@ -23551,9 +23062,6 @@
       <c r="AD165" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE165" t="s">
-        <v>212</v>
-      </c>
       <c r="AF165" t="s">
         <v>1287</v>
       </c>
@@ -23631,9 +23139,6 @@
       <c r="AD166" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE166" t="s">
-        <v>212</v>
-      </c>
       <c r="AF166" t="s">
         <v>1287</v>
       </c>
@@ -23711,9 +23216,6 @@
       <c r="AD167" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE167" t="s">
-        <v>212</v>
-      </c>
       <c r="AF167" t="s">
         <v>1287</v>
       </c>
@@ -23791,9 +23293,6 @@
       <c r="AD168" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE168" t="s">
-        <v>212</v>
-      </c>
       <c r="AF168" t="s">
         <v>1287</v>
       </c>
@@ -23871,9 +23370,6 @@
       <c r="AD169" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE169" t="s">
-        <v>212</v>
-      </c>
       <c r="AF169" t="s">
         <v>1287</v>
       </c>
@@ -23951,9 +23447,6 @@
       <c r="AD170" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE170" t="s">
-        <v>212</v>
-      </c>
       <c r="AF170" t="s">
         <v>1287</v>
       </c>
@@ -24031,9 +23524,6 @@
       <c r="AD171" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE171" t="s">
-        <v>212</v>
-      </c>
       <c r="AF171" t="s">
         <v>1287</v>
       </c>
@@ -24111,9 +23601,6 @@
       <c r="AD172" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE172" t="s">
-        <v>212</v>
-      </c>
       <c r="AF172" t="s">
         <v>1287</v>
       </c>
@@ -24191,9 +23678,6 @@
       <c r="AD173" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE173" t="s">
-        <v>212</v>
-      </c>
       <c r="AL173" t="s">
         <v>1752</v>
       </c>
@@ -24262,9 +23746,6 @@
       <c r="AD174" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE174" t="s">
-        <v>212</v>
-      </c>
       <c r="AF174" t="s">
         <v>1287</v>
       </c>
@@ -24342,9 +23823,6 @@
       <c r="AD175" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE175" t="s">
-        <v>212</v>
-      </c>
       <c r="AL175" t="s">
         <v>1754</v>
       </c>
@@ -24413,9 +23891,6 @@
       <c r="AD176" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE176" t="s">
-        <v>212</v>
-      </c>
       <c r="AF176" t="s">
         <v>1287</v>
       </c>
@@ -24493,9 +23968,6 @@
       <c r="AD177" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE177" t="s">
-        <v>212</v>
-      </c>
       <c r="AF177" t="s">
         <v>1287</v>
       </c>
@@ -24573,9 +24045,6 @@
       <c r="AD178" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE178" t="s">
-        <v>212</v>
-      </c>
       <c r="AF178" t="s">
         <v>1287</v>
       </c>
@@ -24653,9 +24122,6 @@
       <c r="AD179" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE179" t="s">
-        <v>212</v>
-      </c>
       <c r="AF179" t="s">
         <v>1287</v>
       </c>
@@ -24730,9 +24196,6 @@
       <c r="AD180" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE180" t="s">
-        <v>212</v>
-      </c>
       <c r="AF180" t="s">
         <v>1287</v>
       </c>
@@ -24816,9 +24279,6 @@
       <c r="AD181" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE181" t="s">
-        <v>212</v>
-      </c>
       <c r="AF181" t="s">
         <v>1287</v>
       </c>
@@ -24902,9 +24362,6 @@
       <c r="AD182" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE182" t="s">
-        <v>212</v>
-      </c>
       <c r="AF182" t="s">
         <v>1287</v>
       </c>
@@ -24991,9 +24448,6 @@
       <c r="AD183" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE183" t="s">
-        <v>212</v>
-      </c>
       <c r="AF183" t="s">
         <v>1287</v>
       </c>
@@ -25071,9 +24525,6 @@
       <c r="AD184" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE184" t="s">
-        <v>212</v>
-      </c>
       <c r="AF184" t="s">
         <v>1287</v>
       </c>
@@ -25151,9 +24602,6 @@
       <c r="AD185" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE185" t="s">
-        <v>212</v>
-      </c>
       <c r="AF185" t="s">
         <v>1287</v>
       </c>
@@ -25231,9 +24679,6 @@
       <c r="AD186" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE186" t="s">
-        <v>212</v>
-      </c>
       <c r="AF186" t="s">
         <v>1287</v>
       </c>
@@ -25308,9 +24753,6 @@
       <c r="AD187" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE187" t="s">
-        <v>212</v>
-      </c>
       <c r="AF187" t="s">
         <v>1287</v>
       </c>
@@ -25388,9 +24830,6 @@
       <c r="AD188" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE188" t="s">
-        <v>212</v>
-      </c>
       <c r="AF188" t="s">
         <v>1287</v>
       </c>
@@ -25468,9 +24907,6 @@
       <c r="AD189" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE189" t="s">
-        <v>212</v>
-      </c>
       <c r="AF189" t="s">
         <v>1287</v>
       </c>
@@ -25548,9 +24984,6 @@
       <c r="AD190" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE190" t="s">
-        <v>212</v>
-      </c>
       <c r="AF190" t="s">
         <v>1287</v>
       </c>
@@ -25628,9 +25061,6 @@
       <c r="AD191" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE191" t="s">
-        <v>212</v>
-      </c>
       <c r="AF191" t="s">
         <v>1287</v>
       </c>
@@ -25708,9 +25138,6 @@
       <c r="AD192" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE192" t="s">
-        <v>212</v>
-      </c>
       <c r="AF192" t="s">
         <v>1287</v>
       </c>
@@ -25788,9 +25215,6 @@
       <c r="AD193" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE193" t="s">
-        <v>212</v>
-      </c>
       <c r="AF193" t="s">
         <v>1287</v>
       </c>
@@ -25868,9 +25292,6 @@
       <c r="AD194" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE194" t="s">
-        <v>212</v>
-      </c>
       <c r="AF194" t="s">
         <v>1287</v>
       </c>
@@ -25948,9 +25369,6 @@
       <c r="AD195" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE195" t="s">
-        <v>212</v>
-      </c>
       <c r="AF195" t="s">
         <v>1287</v>
       </c>
@@ -26028,9 +25446,6 @@
       <c r="AD196" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE196" t="s">
-        <v>212</v>
-      </c>
       <c r="AF196" t="s">
         <v>1287</v>
       </c>
@@ -26108,9 +25523,6 @@
       <c r="AD197" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE197" t="s">
-        <v>212</v>
-      </c>
       <c r="AF197" t="s">
         <v>1287</v>
       </c>
@@ -26188,9 +25600,6 @@
       <c r="AD198" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE198" t="s">
-        <v>212</v>
-      </c>
       <c r="AF198" t="s">
         <v>1287</v>
       </c>
@@ -26268,9 +25677,6 @@
       <c r="AD199" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE199" t="s">
-        <v>212</v>
-      </c>
       <c r="AF199" t="s">
         <v>1287</v>
       </c>
@@ -26348,9 +25754,6 @@
       <c r="AD200" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE200" t="s">
-        <v>212</v>
-      </c>
       <c r="AF200" t="s">
         <v>1287</v>
       </c>
@@ -26428,9 +25831,6 @@
       <c r="AD201" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE201" t="s">
-        <v>212</v>
-      </c>
       <c r="AF201" t="s">
         <v>1287</v>
       </c>
@@ -26508,9 +25908,6 @@
       <c r="AD202" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE202" t="s">
-        <v>212</v>
-      </c>
       <c r="AF202" t="s">
         <v>1287</v>
       </c>
@@ -26588,9 +25985,6 @@
       <c r="AD203" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE203" t="s">
-        <v>212</v>
-      </c>
       <c r="AF203" t="s">
         <v>1287</v>
       </c>
@@ -26668,9 +26062,6 @@
       <c r="AD204" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE204" t="s">
-        <v>212</v>
-      </c>
       <c r="AL204" t="s">
         <v>1783</v>
       </c>
@@ -26739,9 +26130,6 @@
       <c r="AD205" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE205" t="s">
-        <v>212</v>
-      </c>
       <c r="AF205" t="s">
         <v>1287</v>
       </c>
@@ -26819,9 +26207,6 @@
       <c r="AD206" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE206" t="s">
-        <v>212</v>
-      </c>
       <c r="AL206" t="s">
         <v>1785</v>
       </c>
@@ -26890,9 +26275,6 @@
       <c r="AD207" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE207" t="s">
-        <v>212</v>
-      </c>
       <c r="AF207" t="s">
         <v>1287</v>
       </c>
@@ -26970,9 +26352,6 @@
       <c r="AD208" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE208" t="s">
-        <v>212</v>
-      </c>
       <c r="AF208" t="s">
         <v>1287</v>
       </c>
@@ -27050,9 +26429,6 @@
       <c r="AD209" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE209" t="s">
-        <v>212</v>
-      </c>
       <c r="AF209" t="s">
         <v>1287</v>
       </c>
@@ -27130,9 +26506,6 @@
       <c r="AD210" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE210" t="s">
-        <v>212</v>
-      </c>
       <c r="AF210" t="s">
         <v>1287</v>
       </c>
@@ -27207,9 +26580,6 @@
       <c r="AD211" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE211" t="s">
-        <v>212</v>
-      </c>
       <c r="AF211" t="s">
         <v>1287</v>
       </c>
@@ -27293,9 +26663,6 @@
       <c r="AD212" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE212" t="s">
-        <v>212</v>
-      </c>
       <c r="AF212" t="s">
         <v>1287</v>
       </c>
@@ -27379,9 +26746,6 @@
       <c r="AD213" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE213" t="s">
-        <v>212</v>
-      </c>
       <c r="AF213" t="s">
         <v>1287</v>
       </c>
@@ -27468,9 +26832,6 @@
       <c r="AD214" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE214" t="s">
-        <v>212</v>
-      </c>
       <c r="AF214" t="s">
         <v>1287</v>
       </c>
@@ -27548,9 +26909,6 @@
       <c r="AD215" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE215" t="s">
-        <v>212</v>
-      </c>
       <c r="AF215" t="s">
         <v>1287</v>
       </c>
@@ -27628,9 +26986,6 @@
       <c r="AD216" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE216" t="s">
-        <v>212</v>
-      </c>
       <c r="AF216" t="s">
         <v>1287</v>
       </c>
@@ -27708,9 +27063,6 @@
       <c r="AD217" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE217" t="s">
-        <v>212</v>
-      </c>
       <c r="AF217" t="s">
         <v>1287</v>
       </c>
@@ -27785,9 +27137,6 @@
       <c r="AD218" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE218" t="s">
-        <v>212</v>
-      </c>
       <c r="AF218" t="s">
         <v>1287</v>
       </c>
@@ -27865,9 +27214,6 @@
       <c r="AD219" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE219" t="s">
-        <v>212</v>
-      </c>
       <c r="AF219" t="s">
         <v>1287</v>
       </c>
@@ -27945,9 +27291,6 @@
       <c r="AD220" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE220" t="s">
-        <v>212</v>
-      </c>
       <c r="AF220" t="s">
         <v>1287</v>
       </c>
@@ -28025,9 +27368,6 @@
       <c r="AD221" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE221" t="s">
-        <v>212</v>
-      </c>
       <c r="AF221" t="s">
         <v>1287</v>
       </c>
@@ -28105,9 +27445,6 @@
       <c r="AD222" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE222" t="s">
-        <v>212</v>
-      </c>
       <c r="AF222" t="s">
         <v>1287</v>
       </c>
@@ -28185,9 +27522,6 @@
       <c r="AD223" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE223" t="s">
-        <v>212</v>
-      </c>
       <c r="AL223" t="s">
         <v>1802</v>
       </c>
@@ -28256,9 +27590,6 @@
       <c r="AD224" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE224" t="s">
-        <v>212</v>
-      </c>
       <c r="AF224" t="s">
         <v>1287</v>
       </c>
@@ -28336,9 +27667,6 @@
       <c r="AD225" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE225" t="s">
-        <v>212</v>
-      </c>
       <c r="AF225" t="s">
         <v>1287</v>
       </c>
@@ -28416,9 +27744,6 @@
       <c r="AD226" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE226" t="s">
-        <v>212</v>
-      </c>
       <c r="AF226" t="s">
         <v>1287</v>
       </c>
@@ -28496,9 +27821,6 @@
       <c r="AD227" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE227" t="s">
-        <v>212</v>
-      </c>
       <c r="AF227" t="s">
         <v>1287</v>
       </c>
@@ -28576,9 +27898,6 @@
       <c r="AD228" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE228" t="s">
-        <v>212</v>
-      </c>
       <c r="AF228" t="s">
         <v>1287</v>
       </c>
@@ -28656,9 +27975,6 @@
       <c r="AD229" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE229" t="s">
-        <v>212</v>
-      </c>
       <c r="AF229" t="s">
         <v>1287</v>
       </c>
@@ -28736,9 +28052,6 @@
       <c r="AD230" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE230" t="s">
-        <v>212</v>
-      </c>
       <c r="AF230" t="s">
         <v>1287</v>
       </c>
@@ -28816,9 +28129,6 @@
       <c r="AD231" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE231" t="s">
-        <v>212</v>
-      </c>
       <c r="AF231" t="s">
         <v>1287</v>
       </c>
@@ -28896,9 +28206,6 @@
       <c r="AD232" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE232" t="s">
-        <v>212</v>
-      </c>
       <c r="AL232" t="s">
         <v>1811</v>
       </c>
@@ -28967,9 +28274,6 @@
       <c r="AD233" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE233" t="s">
-        <v>212</v>
-      </c>
       <c r="AF233" t="s">
         <v>1287</v>
       </c>
@@ -29047,9 +28351,6 @@
       <c r="AD234" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE234" t="s">
-        <v>212</v>
-      </c>
       <c r="AF234" t="s">
         <v>1287</v>
       </c>
@@ -29127,9 +28428,6 @@
       <c r="AD235" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE235" t="s">
-        <v>212</v>
-      </c>
       <c r="AL235" t="s">
         <v>1814</v>
       </c>
@@ -29198,9 +28496,6 @@
       <c r="AD236" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE236" t="s">
-        <v>212</v>
-      </c>
       <c r="AF236" t="s">
         <v>1287</v>
       </c>
@@ -29278,9 +28573,6 @@
       <c r="AD237" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE237" t="s">
-        <v>212</v>
-      </c>
       <c r="AL237" t="s">
         <v>1816</v>
       </c>
@@ -29349,9 +28641,6 @@
       <c r="AD238" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE238" t="s">
-        <v>212</v>
-      </c>
       <c r="AF238" t="s">
         <v>1287</v>
       </c>
@@ -29429,9 +28718,6 @@
       <c r="AD239" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE239" t="s">
-        <v>212</v>
-      </c>
       <c r="AF239" t="s">
         <v>1287</v>
       </c>
@@ -29509,9 +28795,6 @@
       <c r="AD240" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE240" t="s">
-        <v>212</v>
-      </c>
       <c r="AF240" t="s">
         <v>1287</v>
       </c>
@@ -29589,9 +28872,6 @@
       <c r="AD241" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE241" t="s">
-        <v>212</v>
-      </c>
       <c r="AF241" t="s">
         <v>1287</v>
       </c>
@@ -29666,9 +28946,6 @@
       <c r="AD242" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE242" t="s">
-        <v>212</v>
-      </c>
       <c r="AF242" t="s">
         <v>1287</v>
       </c>
@@ -29752,9 +29029,6 @@
       <c r="AD243" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE243" t="s">
-        <v>212</v>
-      </c>
       <c r="AF243" t="s">
         <v>1287</v>
       </c>
@@ -29838,9 +29112,6 @@
       <c r="AD244" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE244" t="s">
-        <v>212</v>
-      </c>
       <c r="AF244" t="s">
         <v>1287</v>
       </c>
@@ -29927,9 +29198,6 @@
       <c r="AD245" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE245" t="s">
-        <v>212</v>
-      </c>
       <c r="AF245" t="s">
         <v>1287</v>
       </c>
@@ -30007,9 +29275,6 @@
       <c r="AD246" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE246" t="s">
-        <v>212</v>
-      </c>
       <c r="AF246" t="s">
         <v>1287</v>
       </c>
@@ -30087,9 +29352,6 @@
       <c r="AD247" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE247" t="s">
-        <v>212</v>
-      </c>
       <c r="AF247" t="s">
         <v>1287</v>
       </c>
@@ -30167,9 +29429,6 @@
       <c r="AD248" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE248" t="s">
-        <v>212</v>
-      </c>
       <c r="AF248" t="s">
         <v>1287</v>
       </c>
@@ -30244,9 +29503,6 @@
       <c r="AD249" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE249" t="s">
-        <v>212</v>
-      </c>
       <c r="AF249" t="s">
         <v>1287</v>
       </c>
@@ -30324,9 +29580,6 @@
       <c r="AD250" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE250" t="s">
-        <v>212</v>
-      </c>
       <c r="AF250" t="s">
         <v>1287</v>
       </c>
@@ -30404,9 +29657,6 @@
       <c r="AD251" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE251" t="s">
-        <v>212</v>
-      </c>
       <c r="AF251" t="s">
         <v>1287</v>
       </c>
@@ -30484,9 +29734,6 @@
       <c r="AD252" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE252" t="s">
-        <v>212</v>
-      </c>
       <c r="AF252" t="s">
         <v>1287</v>
       </c>
@@ -30564,9 +29811,6 @@
       <c r="AD253" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE253" t="s">
-        <v>212</v>
-      </c>
       <c r="AF253" t="s">
         <v>1287</v>
       </c>
@@ -30644,9 +29888,6 @@
       <c r="AD254" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE254" t="s">
-        <v>212</v>
-      </c>
       <c r="AL254" t="s">
         <v>1833</v>
       </c>
@@ -30715,9 +29956,6 @@
       <c r="AD255" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE255" t="s">
-        <v>212</v>
-      </c>
       <c r="AF255" t="s">
         <v>1287</v>
       </c>
@@ -30795,9 +30033,6 @@
       <c r="AD256" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE256" t="s">
-        <v>212</v>
-      </c>
       <c r="AL256" t="s">
         <v>1835</v>
       </c>
@@ -30866,9 +30101,6 @@
       <c r="AD257" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE257" t="s">
-        <v>212</v>
-      </c>
       <c r="AF257" t="s">
         <v>1287</v>
       </c>
@@ -30946,9 +30178,6 @@
       <c r="AD258" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE258" t="s">
-        <v>212</v>
-      </c>
       <c r="AF258" t="s">
         <v>1287</v>
       </c>
@@ -31026,9 +30255,6 @@
       <c r="AD259" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE259" t="s">
-        <v>212</v>
-      </c>
       <c r="AF259" t="s">
         <v>1287</v>
       </c>
@@ -31106,9 +30332,6 @@
       <c r="AD260" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE260" t="s">
-        <v>212</v>
-      </c>
       <c r="AF260" t="s">
         <v>1287</v>
       </c>
@@ -31186,9 +30409,6 @@
       <c r="AD261" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE261" t="s">
-        <v>212</v>
-      </c>
       <c r="AF261" t="s">
         <v>1287</v>
       </c>
@@ -31266,9 +30486,6 @@
       <c r="AD262" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE262" t="s">
-        <v>212</v>
-      </c>
       <c r="AF262" t="s">
         <v>1287</v>
       </c>
@@ -31346,9 +30563,6 @@
       <c r="AD263" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE263" t="s">
-        <v>212</v>
-      </c>
       <c r="AF263" t="s">
         <v>1287</v>
       </c>
@@ -31426,9 +30640,6 @@
       <c r="AD264" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE264" t="s">
-        <v>212</v>
-      </c>
       <c r="AF264" t="s">
         <v>1287</v>
       </c>
@@ -31506,9 +30717,6 @@
       <c r="AD265" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE265" t="s">
-        <v>212</v>
-      </c>
       <c r="AF265" t="s">
         <v>1287</v>
       </c>
@@ -31586,9 +30794,6 @@
       <c r="AD266" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE266" t="s">
-        <v>212</v>
-      </c>
       <c r="AL266" t="s">
         <v>1845</v>
       </c>
@@ -31657,9 +30862,6 @@
       <c r="AD267" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE267" t="s">
-        <v>212</v>
-      </c>
       <c r="AF267" t="s">
         <v>1287</v>
       </c>
@@ -31737,9 +30939,6 @@
       <c r="AD268" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE268" t="s">
-        <v>212</v>
-      </c>
       <c r="AL268" t="s">
         <v>1847</v>
       </c>
@@ -31808,9 +31007,6 @@
       <c r="AD269" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE269" t="s">
-        <v>212</v>
-      </c>
       <c r="AF269" t="s">
         <v>1287</v>
       </c>
@@ -31888,9 +31084,6 @@
       <c r="AD270" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE270" t="s">
-        <v>212</v>
-      </c>
       <c r="AF270" t="s">
         <v>1287</v>
       </c>
@@ -31968,9 +31161,6 @@
       <c r="AD271" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE271" t="s">
-        <v>212</v>
-      </c>
       <c r="AF271" t="s">
         <v>1287</v>
       </c>
@@ -32048,9 +31238,6 @@
       <c r="AD272" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE272" t="s">
-        <v>212</v>
-      </c>
       <c r="AF272" t="s">
         <v>1287</v>
       </c>
@@ -32125,9 +31312,6 @@
       <c r="AD273" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE273" t="s">
-        <v>212</v>
-      </c>
       <c r="AF273" t="s">
         <v>1287</v>
       </c>
@@ -32211,9 +31395,6 @@
       <c r="AD274" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE274" t="s">
-        <v>212</v>
-      </c>
       <c r="AF274" t="s">
         <v>1287</v>
       </c>
@@ -32297,9 +31478,6 @@
       <c r="AD275" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE275" t="s">
-        <v>212</v>
-      </c>
       <c r="AF275" t="s">
         <v>1287</v>
       </c>
@@ -32386,9 +31564,6 @@
       <c r="AD276" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE276" t="s">
-        <v>212</v>
-      </c>
       <c r="AF276" t="s">
         <v>1287</v>
       </c>
@@ -32466,9 +31641,6 @@
       <c r="AD277" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE277" t="s">
-        <v>212</v>
-      </c>
       <c r="AF277" t="s">
         <v>1287</v>
       </c>
@@ -32546,9 +31718,6 @@
       <c r="AD278" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE278" t="s">
-        <v>212</v>
-      </c>
       <c r="AF278" t="s">
         <v>1287</v>
       </c>
@@ -32626,9 +31795,6 @@
       <c r="AD279" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE279" t="s">
-        <v>212</v>
-      </c>
       <c r="AF279" t="s">
         <v>1287</v>
       </c>
@@ -32703,9 +31869,6 @@
       <c r="AD280" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE280" t="s">
-        <v>212</v>
-      </c>
       <c r="AF280" t="s">
         <v>1287</v>
       </c>
@@ -32783,9 +31946,6 @@
       <c r="AD281" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE281" t="s">
-        <v>212</v>
-      </c>
       <c r="AF281" t="s">
         <v>1287</v>
       </c>
@@ -32863,9 +32023,6 @@
       <c r="AD282" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE282" t="s">
-        <v>212</v>
-      </c>
       <c r="AF282" t="s">
         <v>1287</v>
       </c>
@@ -32943,9 +32100,6 @@
       <c r="AD283" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE283" t="s">
-        <v>212</v>
-      </c>
       <c r="AF283" t="s">
         <v>1287</v>
       </c>
@@ -33023,9 +32177,6 @@
       <c r="AD284" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE284" t="s">
-        <v>212</v>
-      </c>
       <c r="AF284" t="s">
         <v>1287</v>
       </c>
@@ -33103,9 +32254,6 @@
       <c r="AD285" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE285" t="s">
-        <v>212</v>
-      </c>
       <c r="AF285" t="s">
         <v>1287</v>
       </c>
@@ -33183,9 +32331,6 @@
       <c r="AD286" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE286" t="s">
-        <v>212</v>
-      </c>
       <c r="AF286" t="s">
         <v>1287</v>
       </c>
@@ -33263,9 +32408,6 @@
       <c r="AD287" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE287" t="s">
-        <v>212</v>
-      </c>
       <c r="AF287" t="s">
         <v>1287</v>
       </c>
@@ -33340,9 +32482,6 @@
       <c r="AD288" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE288" t="s">
-        <v>212</v>
-      </c>
       <c r="AF288" t="s">
         <v>1287</v>
       </c>
@@ -33420,9 +32559,6 @@
       <c r="AD289" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE289" t="s">
-        <v>212</v>
-      </c>
       <c r="AL289" t="s">
         <v>1868</v>
       </c>
@@ -33491,9 +32627,6 @@
       <c r="AD290" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE290" t="s">
-        <v>212</v>
-      </c>
       <c r="AF290" t="s">
         <v>1287</v>
       </c>
@@ -33571,9 +32704,6 @@
       <c r="AD291" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE291" t="s">
-        <v>212</v>
-      </c>
       <c r="AF291" t="s">
         <v>1287</v>
       </c>
@@ -33648,9 +32778,6 @@
       <c r="AD292" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE292" t="s">
-        <v>212</v>
-      </c>
       <c r="AF292" t="s">
         <v>1287</v>
       </c>
@@ -33728,9 +32855,6 @@
       <c r="AD293" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE293" t="s">
-        <v>212</v>
-      </c>
       <c r="AF293" t="s">
         <v>1287</v>
       </c>
@@ -33808,9 +32932,6 @@
       <c r="AD294" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE294" t="s">
-        <v>212</v>
-      </c>
       <c r="AF294" t="s">
         <v>1287</v>
       </c>
@@ -33888,9 +33009,6 @@
       <c r="AD295" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE295" t="s">
-        <v>212</v>
-      </c>
       <c r="AF295" t="s">
         <v>1287</v>
       </c>
@@ -33968,9 +33086,6 @@
       <c r="AD296" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE296" t="s">
-        <v>212</v>
-      </c>
       <c r="AF296" t="s">
         <v>1287</v>
       </c>
@@ -34048,9 +33163,6 @@
       <c r="AD297" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE297" t="s">
-        <v>212</v>
-      </c>
       <c r="AF297" t="s">
         <v>1287</v>
       </c>
@@ -34125,9 +33237,6 @@
       <c r="AD298" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE298" t="s">
-        <v>212</v>
-      </c>
       <c r="AF298" t="s">
         <v>1287</v>
       </c>
@@ -34205,9 +33314,6 @@
       <c r="AD299" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE299" t="s">
-        <v>212</v>
-      </c>
       <c r="AL299" t="s">
         <v>1878</v>
       </c>
@@ -34276,9 +33382,6 @@
       <c r="AD300" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE300" t="s">
-        <v>212</v>
-      </c>
       <c r="AF300" t="s">
         <v>1287</v>
       </c>
@@ -34356,9 +33459,6 @@
       <c r="AD301" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE301" t="s">
-        <v>212</v>
-      </c>
       <c r="AF301" t="s">
         <v>1287</v>
       </c>
@@ -34433,9 +33533,6 @@
       <c r="AD302" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE302" t="s">
-        <v>212</v>
-      </c>
       <c r="AF302" t="s">
         <v>1287</v>
       </c>
@@ -34513,9 +33610,6 @@
       <c r="AD303" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE303" t="s">
-        <v>212</v>
-      </c>
       <c r="AF303" t="s">
         <v>1287</v>
       </c>
@@ -34593,9 +33687,6 @@
       <c r="AD304" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE304" t="s">
-        <v>212</v>
-      </c>
       <c r="AF304" t="s">
         <v>1287</v>
       </c>
@@ -34673,9 +33764,6 @@
       <c r="AD305" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE305" t="s">
-        <v>212</v>
-      </c>
       <c r="AF305" t="s">
         <v>1287</v>
       </c>
@@ -34750,9 +33838,6 @@
       <c r="AD306" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE306" t="s">
-        <v>212</v>
-      </c>
       <c r="AF306" t="s">
         <v>1287</v>
       </c>
@@ -34830,9 +33915,6 @@
       <c r="AD307" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE307" t="s">
-        <v>212</v>
-      </c>
       <c r="AL307" t="s">
         <v>1886</v>
       </c>
@@ -34901,9 +33983,6 @@
       <c r="AD308" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE308" t="s">
-        <v>212</v>
-      </c>
       <c r="AF308" t="s">
         <v>1287</v>
       </c>
@@ -34981,9 +34060,6 @@
       <c r="AD309" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE309" t="s">
-        <v>212</v>
-      </c>
       <c r="AF309" t="s">
         <v>1287</v>
       </c>
@@ -35058,9 +34134,6 @@
       <c r="AD310" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE310" t="s">
-        <v>212</v>
-      </c>
       <c r="AF310" t="s">
         <v>1287</v>
       </c>
@@ -35138,9 +34211,6 @@
       <c r="AD311" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE311" t="s">
-        <v>212</v>
-      </c>
       <c r="AF311" t="s">
         <v>1287</v>
       </c>
@@ -35218,9 +34288,6 @@
       <c r="AD312" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE312" t="s">
-        <v>212</v>
-      </c>
       <c r="AF312" t="s">
         <v>1287</v>
       </c>
@@ -35298,9 +34365,6 @@
       <c r="AD313" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE313" t="s">
-        <v>212</v>
-      </c>
       <c r="AF313" t="s">
         <v>1287</v>
       </c>
@@ -35378,9 +34442,6 @@
       <c r="AD314" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE314" t="s">
-        <v>212</v>
-      </c>
       <c r="AF314" t="s">
         <v>1287</v>
       </c>
@@ -35458,9 +34519,6 @@
       <c r="AD315" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE315" t="s">
-        <v>212</v>
-      </c>
       <c r="AF315" t="s">
         <v>1287</v>
       </c>
@@ -35535,9 +34593,6 @@
       <c r="AD316" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE316" t="s">
-        <v>212</v>
-      </c>
       <c r="AF316" t="s">
         <v>1287</v>
       </c>
@@ -35615,9 +34670,6 @@
       <c r="AD317" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE317" t="s">
-        <v>212</v>
-      </c>
       <c r="AL317" t="s">
         <v>1896</v>
       </c>
@@ -35686,9 +34738,6 @@
       <c r="AD318" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE318" t="s">
-        <v>212</v>
-      </c>
       <c r="AF318" t="s">
         <v>1287</v>
       </c>
@@ -35766,9 +34815,6 @@
       <c r="AD319" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE319" t="s">
-        <v>212</v>
-      </c>
       <c r="AF319" t="s">
         <v>1287</v>
       </c>
@@ -35843,9 +34889,6 @@
       <c r="AD320" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE320" t="s">
-        <v>212</v>
-      </c>
       <c r="AF320" t="s">
         <v>1287</v>
       </c>
@@ -35923,9 +34966,6 @@
       <c r="AD321" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE321" t="s">
-        <v>212</v>
-      </c>
       <c r="AF321" t="s">
         <v>1287</v>
       </c>
@@ -36003,9 +35043,6 @@
       <c r="AD322" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE322" t="s">
-        <v>212</v>
-      </c>
       <c r="AF322" t="s">
         <v>1287</v>
       </c>
@@ -36083,9 +35120,6 @@
       <c r="AD323" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE323" t="s">
-        <v>212</v>
-      </c>
       <c r="AF323" t="s">
         <v>1287</v>
       </c>
@@ -36163,9 +35197,6 @@
       <c r="AD324" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE324" t="s">
-        <v>212</v>
-      </c>
       <c r="AF324" t="s">
         <v>1287</v>
       </c>
@@ -36243,9 +35274,6 @@
       <c r="AD325" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE325" t="s">
-        <v>212</v>
-      </c>
       <c r="AF325" t="s">
         <v>1287</v>
       </c>
@@ -36320,9 +35348,6 @@
       <c r="AD326" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE326" t="s">
-        <v>212</v>
-      </c>
       <c r="AF326" t="s">
         <v>1287</v>
       </c>
@@ -36400,9 +35425,6 @@
       <c r="AD327" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE327" t="s">
-        <v>212</v>
-      </c>
       <c r="AL327" t="s">
         <v>1906</v>
       </c>
@@ -36471,9 +35493,6 @@
       <c r="AD328" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE328" t="s">
-        <v>212</v>
-      </c>
       <c r="AF328" t="s">
         <v>1287</v>
       </c>
@@ -36551,9 +35570,6 @@
       <c r="AD329" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE329" t="s">
-        <v>212</v>
-      </c>
       <c r="AF329" t="s">
         <v>1287</v>
       </c>
@@ -36628,9 +35644,6 @@
       <c r="AD330" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE330" t="s">
-        <v>212</v>
-      </c>
       <c r="AF330" t="s">
         <v>1287</v>
       </c>
@@ -36708,9 +35721,6 @@
       <c r="AD331" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE331" t="s">
-        <v>212</v>
-      </c>
       <c r="AF331" t="s">
         <v>1287</v>
       </c>
@@ -36788,9 +35798,6 @@
       <c r="AD332" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE332" t="s">
-        <v>212</v>
-      </c>
       <c r="AF332" t="s">
         <v>1287</v>
       </c>
@@ -36865,9 +35872,6 @@
       <c r="AD333" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE333" t="s">
-        <v>212</v>
-      </c>
       <c r="AF333" t="s">
         <v>1287</v>
       </c>
@@ -36942,9 +35946,6 @@
       <c r="AD334" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE334" t="s">
-        <v>212</v>
-      </c>
       <c r="AF334" t="s">
         <v>1287</v>
       </c>
@@ -37019,9 +36020,6 @@
       <c r="AD335" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE335" t="s">
-        <v>212</v>
-      </c>
       <c r="AF335" t="s">
         <v>1287</v>
       </c>
@@ -37096,9 +36094,6 @@
       <c r="AD336" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE336" t="s">
-        <v>212</v>
-      </c>
       <c r="AF336" t="s">
         <v>1287</v>
       </c>
@@ -37173,9 +36168,6 @@
       <c r="AD337" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE337" t="s">
-        <v>212</v>
-      </c>
       <c r="AF337" t="s">
         <v>1287</v>
       </c>
@@ -37250,9 +36242,6 @@
       <c r="AD338" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE338" t="s">
-        <v>212</v>
-      </c>
       <c r="AF338" t="s">
         <v>1287</v>
       </c>
@@ -37330,9 +36319,6 @@
       <c r="AD339" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE339" t="s">
-        <v>212</v>
-      </c>
       <c r="AF339" t="s">
         <v>1287</v>
       </c>
@@ -37410,9 +36396,6 @@
       <c r="AD340" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE340" t="s">
-        <v>212</v>
-      </c>
       <c r="AF340" t="s">
         <v>1287</v>
       </c>
@@ -37490,9 +36473,6 @@
       <c r="AD341" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE341" t="s">
-        <v>212</v>
-      </c>
       <c r="AF341" t="s">
         <v>1287</v>
       </c>
@@ -37567,9 +36547,6 @@
       <c r="AD342" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE342" t="s">
-        <v>212</v>
-      </c>
       <c r="AF342" t="s">
         <v>1287</v>
       </c>
@@ -37647,9 +36624,6 @@
       <c r="AD343" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE343" t="s">
-        <v>212</v>
-      </c>
       <c r="AF343" t="s">
         <v>1287</v>
       </c>
@@ -37727,9 +36701,6 @@
       <c r="AD344" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE344" t="s">
-        <v>212</v>
-      </c>
       <c r="AF344" t="s">
         <v>1287</v>
       </c>
@@ -37807,9 +36778,6 @@
       <c r="AD345" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE345" t="s">
-        <v>212</v>
-      </c>
       <c r="AF345" t="s">
         <v>1287</v>
       </c>
@@ -37884,9 +36852,6 @@
       <c r="AD346" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE346" t="s">
-        <v>212</v>
-      </c>
       <c r="AF346" t="s">
         <v>1287</v>
       </c>
@@ -37964,9 +36929,6 @@
       <c r="AD347" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE347" t="s">
-        <v>212</v>
-      </c>
       <c r="AF347" t="s">
         <v>1287</v>
       </c>
@@ -38044,9 +37006,6 @@
       <c r="AD348" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE348" t="s">
-        <v>212</v>
-      </c>
       <c r="AF348" t="s">
         <v>1287</v>
       </c>
@@ -38121,9 +37080,6 @@
       <c r="AD349" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE349" t="s">
-        <v>212</v>
-      </c>
       <c r="AF349" t="s">
         <v>1287</v>
       </c>
@@ -38198,9 +37154,6 @@
       <c r="AD350" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE350" t="s">
-        <v>212</v>
-      </c>
       <c r="AF350" t="s">
         <v>1287</v>
       </c>
@@ -38278,9 +37231,6 @@
       <c r="AD351" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE351" t="s">
-        <v>212</v>
-      </c>
       <c r="AL351" t="s">
         <v>1930</v>
       </c>
@@ -38349,9 +37299,6 @@
       <c r="AD352" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE352" t="s">
-        <v>212</v>
-      </c>
       <c r="AL352" t="s">
         <v>1931</v>
       </c>
@@ -38420,9 +37367,6 @@
       <c r="AD353" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE353" t="s">
-        <v>212</v>
-      </c>
       <c r="AL353" t="s">
         <v>1932</v>
       </c>
@@ -38491,9 +37435,6 @@
       <c r="AD354" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE354" t="s">
-        <v>212</v>
-      </c>
       <c r="AL354" t="s">
         <v>1933</v>
       </c>
@@ -38562,9 +37503,6 @@
       <c r="AD355" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE355" t="s">
-        <v>212</v>
-      </c>
       <c r="AL355" t="s">
         <v>1934</v>
       </c>
@@ -38633,9 +37571,6 @@
       <c r="AD356" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE356" t="s">
-        <v>212</v>
-      </c>
       <c r="AL356" t="s">
         <v>1935</v>
       </c>
@@ -38704,9 +37639,6 @@
       <c r="AD357" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE357" t="s">
-        <v>212</v>
-      </c>
       <c r="AL357" t="s">
         <v>1936</v>
       </c>
@@ -38775,9 +37707,6 @@
       <c r="AD358" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE358" t="s">
-        <v>212</v>
-      </c>
       <c r="AL358" t="s">
         <v>1937</v>
       </c>
@@ -38846,9 +37775,6 @@
       <c r="AD359" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE359" t="s">
-        <v>212</v>
-      </c>
       <c r="AL359" t="s">
         <v>1938</v>
       </c>
@@ -38917,9 +37843,6 @@
       <c r="AD360" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE360" t="s">
-        <v>212</v>
-      </c>
       <c r="AL360" t="s">
         <v>1939</v>
       </c>
@@ -38988,9 +37911,6 @@
       <c r="AD361" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE361" t="s">
-        <v>212</v>
-      </c>
       <c r="AL361" t="s">
         <v>1940</v>
       </c>
@@ -39059,9 +37979,6 @@
       <c r="AD362" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE362" t="s">
-        <v>212</v>
-      </c>
       <c r="AL362" t="s">
         <v>1941</v>
       </c>
@@ -39130,9 +38047,6 @@
       <c r="AD363" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE363" t="s">
-        <v>212</v>
-      </c>
       <c r="AL363" t="s">
         <v>1942</v>
       </c>
@@ -39201,9 +38115,6 @@
       <c r="AD364" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE364" t="s">
-        <v>212</v>
-      </c>
       <c r="AL364" t="s">
         <v>1943</v>
       </c>
@@ -39272,9 +38183,6 @@
       <c r="AD365" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE365" t="s">
-        <v>212</v>
-      </c>
       <c r="AL365" t="s">
         <v>1944</v>
       </c>
@@ -39343,9 +38251,6 @@
       <c r="AD366" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE366" t="s">
-        <v>212</v>
-      </c>
       <c r="AL366" t="s">
         <v>1945</v>
       </c>
@@ -39414,9 +38319,6 @@
       <c r="AD367" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE367" t="s">
-        <v>212</v>
-      </c>
       <c r="AL367" t="s">
         <v>1946</v>
       </c>
@@ -39485,9 +38387,6 @@
       <c r="AD368" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE368" t="s">
-        <v>212</v>
-      </c>
       <c r="AL368" t="s">
         <v>1947</v>
       </c>
@@ -39556,9 +38455,6 @@
       <c r="AD369" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE369" t="s">
-        <v>212</v>
-      </c>
       <c r="AL369" t="s">
         <v>1948</v>
       </c>
@@ -39627,9 +38523,6 @@
       <c r="AD370" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE370" t="s">
-        <v>212</v>
-      </c>
       <c r="AL370" t="s">
         <v>1949</v>
       </c>
@@ -39698,9 +38591,6 @@
       <c r="AD371" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE371" t="s">
-        <v>212</v>
-      </c>
       <c r="AL371" t="s">
         <v>1950</v>
       </c>
@@ -39769,9 +38659,6 @@
       <c r="AD372" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE372" t="s">
-        <v>212</v>
-      </c>
       <c r="AL372" t="s">
         <v>1951</v>
       </c>
@@ -39837,9 +38724,6 @@
       <c r="AD373" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE373" t="s">
-        <v>212</v>
-      </c>
       <c r="AL373" t="s">
         <v>1952</v>
       </c>
@@ -39908,9 +38792,6 @@
       <c r="AD374" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE374" t="s">
-        <v>212</v>
-      </c>
       <c r="AL374" t="s">
         <v>1953</v>
       </c>
@@ -39979,9 +38860,6 @@
       <c r="AD375" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE375" t="s">
-        <v>212</v>
-      </c>
       <c r="AL375" t="s">
         <v>1954</v>
       </c>
@@ -40050,9 +38928,6 @@
       <c r="AD376" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE376" t="s">
-        <v>212</v>
-      </c>
       <c r="AL376" t="s">
         <v>1955</v>
       </c>
@@ -40121,9 +38996,6 @@
       <c r="AD377" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE377" t="s">
-        <v>212</v>
-      </c>
       <c r="AL377" t="s">
         <v>1956</v>
       </c>
@@ -40192,9 +39064,6 @@
       <c r="AD378" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE378" t="s">
-        <v>212</v>
-      </c>
       <c r="AL378" t="s">
         <v>1957</v>
       </c>
@@ -40263,9 +39132,6 @@
       <c r="AD379" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE379" t="s">
-        <v>212</v>
-      </c>
       <c r="AL379" t="s">
         <v>1958</v>
       </c>
@@ -40334,9 +39200,6 @@
       <c r="AD380" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE380" t="s">
-        <v>212</v>
-      </c>
       <c r="AL380" t="s">
         <v>1959</v>
       </c>
@@ -40405,9 +39268,6 @@
       <c r="AD381" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE381" t="s">
-        <v>212</v>
-      </c>
       <c r="AL381" t="s">
         <v>1960</v>
       </c>
@@ -40476,9 +39336,6 @@
       <c r="AD382" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE382" t="s">
-        <v>212</v>
-      </c>
       <c r="AL382" t="s">
         <v>1961</v>
       </c>
@@ -40547,9 +39404,6 @@
       <c r="AD383" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE383" t="s">
-        <v>212</v>
-      </c>
       <c r="AL383" t="s">
         <v>1962</v>
       </c>
@@ -40618,9 +39472,6 @@
       <c r="AD384" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE384" t="s">
-        <v>212</v>
-      </c>
       <c r="AL384" t="s">
         <v>1963</v>
       </c>
@@ -40689,9 +39540,6 @@
       <c r="AD385" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE385" t="s">
-        <v>212</v>
-      </c>
       <c r="AL385" t="s">
         <v>1964</v>
       </c>
@@ -40760,9 +39608,6 @@
       <c r="AD386" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE386" t="s">
-        <v>212</v>
-      </c>
       <c r="AL386" t="s">
         <v>1965</v>
       </c>
@@ -40831,9 +39676,6 @@
       <c r="AD387" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE387" t="s">
-        <v>212</v>
-      </c>
       <c r="AL387" t="s">
         <v>1966</v>
       </c>
@@ -40902,9 +39744,6 @@
       <c r="AD388" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE388" t="s">
-        <v>212</v>
-      </c>
       <c r="AL388" t="s">
         <v>1967</v>
       </c>
@@ -40973,9 +39812,6 @@
       <c r="AD389" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE389" t="s">
-        <v>212</v>
-      </c>
       <c r="AL389" t="s">
         <v>1968</v>
       </c>
@@ -41044,9 +39880,6 @@
       <c r="AD390" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE390" t="s">
-        <v>212</v>
-      </c>
       <c r="AL390" t="s">
         <v>1969</v>
       </c>
@@ -41115,9 +39948,6 @@
       <c r="AD391" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE391" t="s">
-        <v>212</v>
-      </c>
       <c r="AL391" t="s">
         <v>1970</v>
       </c>
@@ -41186,9 +40016,6 @@
       <c r="AD392" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE392" t="s">
-        <v>212</v>
-      </c>
       <c r="AL392" t="s">
         <v>1971</v>
       </c>
@@ -41257,9 +40084,6 @@
       <c r="AD393" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE393" t="s">
-        <v>212</v>
-      </c>
       <c r="AL393" t="s">
         <v>1972</v>
       </c>
@@ -41328,9 +40152,6 @@
       <c r="AD394" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE394" t="s">
-        <v>212</v>
-      </c>
       <c r="AL394" t="s">
         <v>1973</v>
       </c>
@@ -41399,9 +40220,6 @@
       <c r="AD395" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE395" t="s">
-        <v>212</v>
-      </c>
       <c r="AL395" t="s">
         <v>1974</v>
       </c>
@@ -41470,9 +40288,6 @@
       <c r="AD396" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE396" t="s">
-        <v>212</v>
-      </c>
       <c r="AL396" t="s">
         <v>1975</v>
       </c>
@@ -41541,9 +40356,6 @@
       <c r="AD397" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE397" t="s">
-        <v>212</v>
-      </c>
       <c r="AL397" t="s">
         <v>1976</v>
       </c>
@@ -41612,9 +40424,6 @@
       <c r="AD398" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE398" t="s">
-        <v>212</v>
-      </c>
       <c r="AL398" t="s">
         <v>1977</v>
       </c>
@@ -41683,9 +40492,6 @@
       <c r="AD399" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE399" t="s">
-        <v>212</v>
-      </c>
       <c r="AL399" t="s">
         <v>1978</v>
       </c>
@@ -41751,9 +40557,6 @@
       <c r="AD400" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE400" t="s">
-        <v>212</v>
-      </c>
       <c r="AL400" t="s">
         <v>1979</v>
       </c>
@@ -41822,9 +40625,6 @@
       <c r="AD401" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE401" t="s">
-        <v>212</v>
-      </c>
       <c r="AL401" t="s">
         <v>1980</v>
       </c>
@@ -41893,9 +40693,6 @@
       <c r="AD402" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE402" t="s">
-        <v>212</v>
-      </c>
       <c r="AL402" t="s">
         <v>1981</v>
       </c>
@@ -41964,9 +40761,6 @@
       <c r="AD403" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE403" t="s">
-        <v>212</v>
-      </c>
       <c r="AL403" t="s">
         <v>1982</v>
       </c>
@@ -42035,9 +40829,6 @@
       <c r="AD404" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE404" t="s">
-        <v>212</v>
-      </c>
       <c r="AL404" t="s">
         <v>1983</v>
       </c>
@@ -42109,9 +40900,6 @@
       <c r="AD405" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE405" t="s">
-        <v>212</v>
-      </c>
       <c r="AF405" t="s">
         <v>1287</v>
       </c>
@@ -42192,9 +40980,6 @@
       <c r="AD406" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE406" t="s">
-        <v>212</v>
-      </c>
       <c r="AF406" t="s">
         <v>1287</v>
       </c>
@@ -42275,9 +41060,6 @@
       <c r="AD407" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE407" t="s">
-        <v>212</v>
-      </c>
       <c r="AF407" t="s">
         <v>1287</v>
       </c>
@@ -42358,9 +41140,6 @@
       <c r="AD408" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE408" t="s">
-        <v>212</v>
-      </c>
       <c r="AF408" t="s">
         <v>1287</v>
       </c>
@@ -42441,9 +41220,6 @@
       <c r="AD409" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE409" t="s">
-        <v>212</v>
-      </c>
       <c r="AL409" t="s">
         <v>1988</v>
       </c>
@@ -42515,9 +41291,6 @@
       <c r="AD410" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE410" t="s">
-        <v>212</v>
-      </c>
       <c r="AF410" t="s">
         <v>1287</v>
       </c>
@@ -42598,9 +41371,6 @@
       <c r="AD411" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE411" t="s">
-        <v>212</v>
-      </c>
       <c r="AF411" t="s">
         <v>1287</v>
       </c>
@@ -42684,9 +41454,6 @@
       <c r="AD412" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE412" t="s">
-        <v>212</v>
-      </c>
       <c r="AF412" t="s">
         <v>1287</v>
       </c>
@@ -42767,9 +41534,6 @@
       <c r="AD413" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE413" t="s">
-        <v>212</v>
-      </c>
       <c r="AF413" t="s">
         <v>1287</v>
       </c>
@@ -42847,9 +41611,6 @@
       <c r="AD414" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE414" t="s">
-        <v>212</v>
-      </c>
       <c r="AF414" t="s">
         <v>1287</v>
       </c>
@@ -42927,9 +41688,6 @@
       <c r="AD415" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE415" t="s">
-        <v>212</v>
-      </c>
       <c r="AF415" t="s">
         <v>1287</v>
       </c>
@@ -43007,9 +41765,6 @@
       <c r="AD416" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE416" t="s">
-        <v>212</v>
-      </c>
       <c r="AF416" t="s">
         <v>1287</v>
       </c>
@@ -43087,9 +41842,6 @@
       <c r="AD417" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE417" t="s">
-        <v>212</v>
-      </c>
       <c r="AF417" t="s">
         <v>1287</v>
       </c>
@@ -43167,9 +41919,6 @@
       <c r="AD418" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE418" t="s">
-        <v>212</v>
-      </c>
       <c r="AF418" t="s">
         <v>1287</v>
       </c>
@@ -43247,9 +41996,6 @@
       <c r="AD419" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE419" t="s">
-        <v>212</v>
-      </c>
       <c r="AF419" t="s">
         <v>1287</v>
       </c>
@@ -43327,9 +42073,6 @@
       <c r="AD420" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE420" t="s">
-        <v>212</v>
-      </c>
       <c r="AF420" t="s">
         <v>1287</v>
       </c>
@@ -43407,9 +42150,6 @@
       <c r="AD421" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE421" t="s">
-        <v>212</v>
-      </c>
       <c r="AF421" t="s">
         <v>1287</v>
       </c>
@@ -43487,9 +42227,6 @@
       <c r="AD422" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE422" t="s">
-        <v>212</v>
-      </c>
       <c r="AF422" t="s">
         <v>1287</v>
       </c>
@@ -43567,9 +42304,6 @@
       <c r="AD423" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE423" t="s">
-        <v>212</v>
-      </c>
       <c r="AF423" t="s">
         <v>1287</v>
       </c>
@@ -43647,9 +42381,6 @@
       <c r="AD424" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE424" t="s">
-        <v>212</v>
-      </c>
       <c r="AF424" t="s">
         <v>1287</v>
       </c>
@@ -43727,9 +42458,6 @@
       <c r="AD425" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE425" t="s">
-        <v>212</v>
-      </c>
       <c r="AF425" t="s">
         <v>1287</v>
       </c>
@@ -43807,9 +42535,6 @@
       <c r="AD426" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE426" t="s">
-        <v>212</v>
-      </c>
       <c r="AF426" t="s">
         <v>1287</v>
       </c>
@@ -43887,9 +42612,6 @@
       <c r="AD427" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE427" t="s">
-        <v>212</v>
-      </c>
       <c r="AF427" t="s">
         <v>1287</v>
       </c>
@@ -43967,9 +42689,6 @@
       <c r="AD428" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE428" t="s">
-        <v>212</v>
-      </c>
       <c r="AF428" t="s">
         <v>1287</v>
       </c>
@@ -44047,9 +42766,6 @@
       <c r="AD429" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE429" t="s">
-        <v>212</v>
-      </c>
       <c r="AF429" t="s">
         <v>1287</v>
       </c>
@@ -44127,9 +42843,6 @@
       <c r="AD430" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE430" t="s">
-        <v>212</v>
-      </c>
       <c r="AF430" t="s">
         <v>1287</v>
       </c>
@@ -44207,9 +42920,6 @@
       <c r="AD431" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE431" t="s">
-        <v>212</v>
-      </c>
       <c r="AF431" t="s">
         <v>1287</v>
       </c>
@@ -44287,9 +42997,6 @@
       <c r="AD432" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE432" t="s">
-        <v>212</v>
-      </c>
       <c r="AF432" t="s">
         <v>1287</v>
       </c>
@@ -44367,9 +43074,6 @@
       <c r="AD433" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE433" t="s">
-        <v>212</v>
-      </c>
       <c r="AF433" t="s">
         <v>1287</v>
       </c>
@@ -44447,9 +43151,6 @@
       <c r="AD434" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE434" t="s">
-        <v>212</v>
-      </c>
       <c r="AF434" t="s">
         <v>1287</v>
       </c>
@@ -44527,9 +43228,6 @@
       <c r="AD435" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE435" t="s">
-        <v>212</v>
-      </c>
       <c r="AF435" t="s">
         <v>1287</v>
       </c>
@@ -44607,9 +43305,6 @@
       <c r="AD436" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE436" t="s">
-        <v>212</v>
-      </c>
       <c r="AF436" t="s">
         <v>1287</v>
       </c>
@@ -44687,9 +43382,6 @@
       <c r="AD437" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE437" t="s">
-        <v>212</v>
-      </c>
       <c r="AF437" t="s">
         <v>1287</v>
       </c>
@@ -44764,9 +43456,6 @@
       <c r="AD438" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE438" t="s">
-        <v>212</v>
-      </c>
       <c r="AL438" t="s">
         <v>2017</v>
       </c>
@@ -44835,9 +43524,6 @@
       <c r="AD439" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE439" t="s">
-        <v>212</v>
-      </c>
       <c r="AF439" t="s">
         <v>1287</v>
       </c>
@@ -44915,9 +43601,6 @@
       <c r="AD440" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE440" t="s">
-        <v>212</v>
-      </c>
       <c r="AF440" t="s">
         <v>1287</v>
       </c>
@@ -44995,9 +43678,6 @@
       <c r="AD441" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE441" t="s">
-        <v>212</v>
-      </c>
       <c r="AF441" t="s">
         <v>1287</v>
       </c>
@@ -45075,9 +43755,6 @@
       <c r="AD442" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE442" t="s">
-        <v>212</v>
-      </c>
       <c r="AF442" t="s">
         <v>1287</v>
       </c>
@@ -45155,9 +43832,6 @@
       <c r="AD443" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE443" t="s">
-        <v>212</v>
-      </c>
       <c r="AF443" t="s">
         <v>1287</v>
       </c>
@@ -45232,9 +43906,6 @@
       <c r="AD444" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE444" t="s">
-        <v>212</v>
-      </c>
       <c r="AF444" t="s">
         <v>1287</v>
       </c>
@@ -45312,9 +43983,6 @@
       <c r="AD445" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE445" t="s">
-        <v>212</v>
-      </c>
       <c r="AF445" t="s">
         <v>1287</v>
       </c>
@@ -45392,9 +44060,6 @@
       <c r="AD446" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE446" t="s">
-        <v>212</v>
-      </c>
       <c r="AF446" t="s">
         <v>1287</v>
       </c>
@@ -45472,9 +44137,6 @@
       <c r="AD447" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE447" t="s">
-        <v>212</v>
-      </c>
       <c r="AF447" t="s">
         <v>1287</v>
       </c>
@@ -45548,9 +44210,6 @@
       </c>
       <c r="AD448" s="2" t="s">
         <v>1286</v>
-      </c>
-      <c r="AE448" t="s">
-        <v>212</v>
       </c>
       <c r="AF448" t="s">
         <v>1287</v>
@@ -46620,9 +45279,6 @@
       <c r="AD2" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE2" t="s">
-        <v>212</v>
-      </c>
       <c r="AL2" t="s">
         <v>2324</v>
       </c>
@@ -46688,9 +45344,6 @@
       <c r="AD3" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE3" t="s">
-        <v>212</v>
-      </c>
       <c r="AL3" t="s">
         <v>2325</v>
       </c>
@@ -46756,9 +45409,6 @@
       <c r="AD4" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE4" t="s">
-        <v>212</v>
-      </c>
       <c r="AL4" t="s">
         <v>2326</v>
       </c>
@@ -46824,9 +45474,6 @@
       <c r="AD5" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE5" t="s">
-        <v>212</v>
-      </c>
       <c r="AL5" t="s">
         <v>1607</v>
       </c>
@@ -46892,9 +45539,6 @@
       <c r="AD6" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE6" t="s">
-        <v>212</v>
-      </c>
       <c r="AL6" t="s">
         <v>2327</v>
       </c>
@@ -46960,9 +45604,6 @@
       <c r="AD7" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE7" t="s">
-        <v>212</v>
-      </c>
       <c r="AL7" t="s">
         <v>2328</v>
       </c>
@@ -47028,9 +45669,6 @@
       <c r="AD8" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE8" t="s">
-        <v>212</v>
-      </c>
       <c r="AL8" t="s">
         <v>2329</v>
       </c>
@@ -47096,9 +45734,6 @@
       <c r="AD9" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE9" t="s">
-        <v>212</v>
-      </c>
       <c r="AL9" t="s">
         <v>1602</v>
       </c>
@@ -47164,9 +45799,6 @@
       <c r="AD10" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE10" t="s">
-        <v>212</v>
-      </c>
       <c r="AL10" t="s">
         <v>2330</v>
       </c>
@@ -47232,9 +45864,6 @@
       <c r="AD11" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE11" t="s">
-        <v>212</v>
-      </c>
       <c r="AL11" t="s">
         <v>2331</v>
       </c>
@@ -47300,9 +45929,6 @@
       <c r="AD12" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE12" t="s">
-        <v>212</v>
-      </c>
       <c r="AL12" t="s">
         <v>2332</v>
       </c>
@@ -47368,9 +45994,6 @@
       <c r="AD13" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE13" t="s">
-        <v>212</v>
-      </c>
       <c r="AL13" t="s">
         <v>2333</v>
       </c>
@@ -47436,9 +46059,6 @@
       <c r="AD14" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE14" t="s">
-        <v>212</v>
-      </c>
       <c r="AL14" t="s">
         <v>2334</v>
       </c>
@@ -47504,9 +46124,6 @@
       <c r="AD15" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE15" t="s">
-        <v>212</v>
-      </c>
       <c r="AL15" t="s">
         <v>2335</v>
       </c>
@@ -47572,9 +46189,6 @@
       <c r="AD16" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE16" t="s">
-        <v>212</v>
-      </c>
       <c r="AL16" t="s">
         <v>1642</v>
       </c>
@@ -47640,9 +46254,6 @@
       <c r="AD17" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE17" t="s">
-        <v>212</v>
-      </c>
       <c r="AL17" t="s">
         <v>2336</v>
       </c>
@@ -47708,9 +46319,6 @@
       <c r="AD18" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE18" t="s">
-        <v>212</v>
-      </c>
       <c r="AL18" t="s">
         <v>2337</v>
       </c>
@@ -47776,9 +46384,6 @@
       <c r="AD19" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE19" t="s">
-        <v>212</v>
-      </c>
       <c r="AL19" t="s">
         <v>2338</v>
       </c>
@@ -47844,9 +46449,6 @@
       <c r="AD20" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE20" t="s">
-        <v>212</v>
-      </c>
       <c r="AL20" t="s">
         <v>2339</v>
       </c>
@@ -47912,9 +46514,6 @@
       <c r="AD21" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE21" t="s">
-        <v>212</v>
-      </c>
       <c r="AL21" t="s">
         <v>2340</v>
       </c>
@@ -47980,9 +46579,6 @@
       <c r="AD22" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE22" t="s">
-        <v>212</v>
-      </c>
       <c r="AL22" t="s">
         <v>2341</v>
       </c>
@@ -48048,9 +46644,6 @@
       <c r="AD23" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE23" t="s">
-        <v>212</v>
-      </c>
       <c r="AL23" t="s">
         <v>2342</v>
       </c>
@@ -48116,9 +46709,6 @@
       <c r="AD24" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE24" t="s">
-        <v>212</v>
-      </c>
       <c r="AL24" t="s">
         <v>2343</v>
       </c>
@@ -48184,9 +46774,6 @@
       <c r="AD25" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE25" t="s">
-        <v>212</v>
-      </c>
       <c r="AL25" t="s">
         <v>1673</v>
       </c>
@@ -48252,9 +46839,6 @@
       <c r="AD26" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE26" t="s">
-        <v>212</v>
-      </c>
       <c r="AL26" t="s">
         <v>2344</v>
       </c>
@@ -48320,9 +46904,6 @@
       <c r="AD27" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE27" t="s">
-        <v>212</v>
-      </c>
       <c r="AL27" t="s">
         <v>2345</v>
       </c>
@@ -48388,9 +46969,6 @@
       <c r="AD28" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE28" t="s">
-        <v>212</v>
-      </c>
       <c r="AL28" t="s">
         <v>2346</v>
       </c>
@@ -48456,9 +47034,6 @@
       <c r="AD29" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE29" t="s">
-        <v>212</v>
-      </c>
       <c r="AL29" t="s">
         <v>2347</v>
       </c>
@@ -48524,9 +47099,6 @@
       <c r="AD30" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE30" t="s">
-        <v>212</v>
-      </c>
       <c r="AL30" t="s">
         <v>2348</v>
       </c>
@@ -48592,9 +47164,6 @@
       <c r="AD31" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE31" t="s">
-        <v>212</v>
-      </c>
       <c r="AL31" t="s">
         <v>2349</v>
       </c>
@@ -48660,9 +47229,6 @@
       <c r="AD32" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE32" t="s">
-        <v>212</v>
-      </c>
       <c r="AL32" t="s">
         <v>2350</v>
       </c>
@@ -48728,9 +47294,6 @@
       <c r="AD33" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE33" t="s">
-        <v>212</v>
-      </c>
       <c r="AL33" t="s">
         <v>2351</v>
       </c>
@@ -48796,9 +47359,6 @@
       <c r="AD34" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE34" t="s">
-        <v>212</v>
-      </c>
       <c r="AL34" t="s">
         <v>1704</v>
       </c>
@@ -48864,9 +47424,6 @@
       <c r="AD35" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE35" t="s">
-        <v>212</v>
-      </c>
       <c r="AL35" t="s">
         <v>2352</v>
       </c>
@@ -48932,9 +47489,6 @@
       <c r="AD36" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE36" t="s">
-        <v>212</v>
-      </c>
       <c r="AL36" t="s">
         <v>2353</v>
       </c>
@@ -49000,9 +47554,6 @@
       <c r="AD37" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE37" t="s">
-        <v>212</v>
-      </c>
       <c r="AL37" t="s">
         <v>2354</v>
       </c>
@@ -49068,9 +47619,6 @@
       <c r="AD38" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE38" t="s">
-        <v>212</v>
-      </c>
       <c r="AL38" t="s">
         <v>2355</v>
       </c>
@@ -49136,9 +47684,6 @@
       <c r="AD39" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE39" t="s">
-        <v>212</v>
-      </c>
       <c r="AL39" t="s">
         <v>2356</v>
       </c>
@@ -49204,9 +47749,6 @@
       <c r="AD40" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE40" t="s">
-        <v>212</v>
-      </c>
       <c r="AL40" t="s">
         <v>2357</v>
       </c>
@@ -49272,9 +47814,6 @@
       <c r="AD41" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE41" t="s">
-        <v>212</v>
-      </c>
       <c r="AL41" t="s">
         <v>2358</v>
       </c>
@@ -49340,9 +47879,6 @@
       <c r="AD42" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE42" t="s">
-        <v>212</v>
-      </c>
       <c r="AL42" t="s">
         <v>2359</v>
       </c>
@@ -49408,9 +47944,6 @@
       <c r="AD43" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE43" t="s">
-        <v>212</v>
-      </c>
       <c r="AL43" t="s">
         <v>1735</v>
       </c>
@@ -49476,9 +48009,6 @@
       <c r="AD44" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE44" t="s">
-        <v>212</v>
-      </c>
       <c r="AL44" t="s">
         <v>2360</v>
       </c>
@@ -49544,9 +48074,6 @@
       <c r="AD45" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE45" t="s">
-        <v>212</v>
-      </c>
       <c r="AL45" t="s">
         <v>2361</v>
       </c>
@@ -49612,9 +48139,6 @@
       <c r="AD46" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE46" t="s">
-        <v>212</v>
-      </c>
       <c r="AL46" t="s">
         <v>2362</v>
       </c>
@@ -49680,9 +48204,6 @@
       <c r="AD47" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE47" t="s">
-        <v>212</v>
-      </c>
       <c r="AL47" t="s">
         <v>2363</v>
       </c>
@@ -49748,9 +48269,6 @@
       <c r="AD48" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE48" t="s">
-        <v>212</v>
-      </c>
       <c r="AL48" t="s">
         <v>2364</v>
       </c>
@@ -49816,9 +48334,6 @@
       <c r="AD49" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE49" t="s">
-        <v>212</v>
-      </c>
       <c r="AL49" t="s">
         <v>2365</v>
       </c>
@@ -49884,9 +48399,6 @@
       <c r="AD50" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE50" t="s">
-        <v>212</v>
-      </c>
       <c r="AL50" t="s">
         <v>2366</v>
       </c>
@@ -49952,9 +48464,6 @@
       <c r="AD51" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE51" t="s">
-        <v>212</v>
-      </c>
       <c r="AL51" t="s">
         <v>2367</v>
       </c>
@@ -50020,9 +48529,6 @@
       <c r="AD52" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE52" t="s">
-        <v>212</v>
-      </c>
       <c r="AL52" t="s">
         <v>1766</v>
       </c>
@@ -50088,9 +48594,6 @@
       <c r="AD53" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE53" t="s">
-        <v>212</v>
-      </c>
       <c r="AL53" t="s">
         <v>2368</v>
       </c>
@@ -50156,9 +48659,6 @@
       <c r="AD54" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE54" t="s">
-        <v>212</v>
-      </c>
       <c r="AL54" t="s">
         <v>2369</v>
       </c>
@@ -50224,9 +48724,6 @@
       <c r="AD55" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE55" t="s">
-        <v>212</v>
-      </c>
       <c r="AL55" t="s">
         <v>2370</v>
       </c>
@@ -50292,9 +48789,6 @@
       <c r="AD56" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE56" t="s">
-        <v>212</v>
-      </c>
       <c r="AL56" t="s">
         <v>2371</v>
       </c>
@@ -50360,9 +48854,6 @@
       <c r="AD57" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE57" t="s">
-        <v>212</v>
-      </c>
       <c r="AL57" t="s">
         <v>2372</v>
       </c>
@@ -50428,9 +48919,6 @@
       <c r="AD58" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE58" t="s">
-        <v>212</v>
-      </c>
       <c r="AL58" t="s">
         <v>2373</v>
       </c>
@@ -50496,9 +48984,6 @@
       <c r="AD59" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE59" t="s">
-        <v>212</v>
-      </c>
       <c r="AL59" t="s">
         <v>2374</v>
       </c>
@@ -50564,9 +49049,6 @@
       <c r="AD60" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE60" t="s">
-        <v>212</v>
-      </c>
       <c r="AL60" t="s">
         <v>2375</v>
       </c>
@@ -50632,9 +49114,6 @@
       <c r="AD61" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE61" t="s">
-        <v>212</v>
-      </c>
       <c r="AL61" t="s">
         <v>1797</v>
       </c>
@@ -50700,9 +49179,6 @@
       <c r="AD62" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE62" t="s">
-        <v>212</v>
-      </c>
       <c r="AL62" t="s">
         <v>2376</v>
       </c>
@@ -50768,9 +49244,6 @@
       <c r="AD63" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE63" t="s">
-        <v>212</v>
-      </c>
       <c r="AL63" t="s">
         <v>2377</v>
       </c>
@@ -50836,9 +49309,6 @@
       <c r="AD64" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE64" t="s">
-        <v>212</v>
-      </c>
       <c r="AL64" t="s">
         <v>2378</v>
       </c>
@@ -50904,9 +49374,6 @@
       <c r="AD65" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE65" t="s">
-        <v>212</v>
-      </c>
       <c r="AL65" t="s">
         <v>2379</v>
       </c>
@@ -50972,9 +49439,6 @@
       <c r="AD66" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE66" t="s">
-        <v>212</v>
-      </c>
       <c r="AL66" t="s">
         <v>2380</v>
       </c>
@@ -51040,9 +49504,6 @@
       <c r="AD67" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE67" t="s">
-        <v>212</v>
-      </c>
       <c r="AL67" t="s">
         <v>2381</v>
       </c>
@@ -51108,9 +49569,6 @@
       <c r="AD68" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE68" t="s">
-        <v>212</v>
-      </c>
       <c r="AL68" t="s">
         <v>2382</v>
       </c>
@@ -51176,9 +49634,6 @@
       <c r="AD69" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE69" t="s">
-        <v>212</v>
-      </c>
       <c r="AL69" t="s">
         <v>2383</v>
       </c>
@@ -51244,9 +49699,6 @@
       <c r="AD70" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE70" t="s">
-        <v>212</v>
-      </c>
       <c r="AL70" t="s">
         <v>1828</v>
       </c>
@@ -51312,9 +49764,6 @@
       <c r="AD71" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE71" t="s">
-        <v>212</v>
-      </c>
       <c r="AL71" t="s">
         <v>2384</v>
       </c>
@@ -51380,9 +49829,6 @@
       <c r="AD72" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE72" t="s">
-        <v>212</v>
-      </c>
       <c r="AL72" t="s">
         <v>2385</v>
       </c>
@@ -51448,9 +49894,6 @@
       <c r="AD73" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE73" t="s">
-        <v>212</v>
-      </c>
       <c r="AL73" t="s">
         <v>2386</v>
       </c>
@@ -51516,9 +49959,6 @@
       <c r="AD74" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE74" t="s">
-        <v>212</v>
-      </c>
       <c r="AL74" t="s">
         <v>2387</v>
       </c>
@@ -51584,9 +50024,6 @@
       <c r="AD75" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE75" t="s">
-        <v>212</v>
-      </c>
       <c r="AL75" t="s">
         <v>2388</v>
       </c>
@@ -51652,9 +50089,6 @@
       <c r="AD76" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE76" t="s">
-        <v>212</v>
-      </c>
       <c r="AL76" t="s">
         <v>2389</v>
       </c>
@@ -51720,9 +50154,6 @@
       <c r="AD77" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE77" t="s">
-        <v>212</v>
-      </c>
       <c r="AL77" t="s">
         <v>2390</v>
       </c>
@@ -51788,9 +50219,6 @@
       <c r="AD78" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE78" t="s">
-        <v>212</v>
-      </c>
       <c r="AL78" t="s">
         <v>2391</v>
       </c>
@@ -51856,9 +50284,6 @@
       <c r="AD79" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE79" t="s">
-        <v>212</v>
-      </c>
       <c r="AL79" t="s">
         <v>1859</v>
       </c>
@@ -51924,9 +50349,6 @@
       <c r="AD80" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE80" t="s">
-        <v>212</v>
-      </c>
       <c r="AL80" t="s">
         <v>2392</v>
       </c>
@@ -51992,9 +50414,6 @@
       <c r="AD81" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE81" t="s">
-        <v>212</v>
-      </c>
       <c r="AL81" t="s">
         <v>2393</v>
       </c>
@@ -52060,9 +50479,6 @@
       <c r="AD82" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE82" t="s">
-        <v>212</v>
-      </c>
       <c r="AL82" t="s">
         <v>2394</v>
       </c>
@@ -52128,9 +50544,6 @@
       <c r="AD83" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE83" t="s">
-        <v>212</v>
-      </c>
       <c r="AL83" t="s">
         <v>2395</v>
       </c>
@@ -52196,9 +50609,6 @@
       <c r="AD84" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE84" t="s">
-        <v>212</v>
-      </c>
       <c r="AL84" t="s">
         <v>2396</v>
       </c>
@@ -52261,9 +50671,6 @@
       <c r="AD85" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE85" t="s">
-        <v>212</v>
-      </c>
       <c r="AL85" t="s">
         <v>1866</v>
       </c>
@@ -52329,9 +50736,6 @@
       <c r="AD86" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE86" t="s">
-        <v>212</v>
-      </c>
       <c r="AL86" t="s">
         <v>1867</v>
       </c>
@@ -52397,9 +50801,6 @@
       <c r="AD87" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE87" t="s">
-        <v>212</v>
-      </c>
       <c r="AL87" t="s">
         <v>2397</v>
       </c>
@@ -52465,9 +50866,6 @@
       <c r="AD88" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE88" t="s">
-        <v>212</v>
-      </c>
       <c r="AL88" t="s">
         <v>2398</v>
       </c>
@@ -52533,9 +50931,6 @@
       <c r="AD89" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE89" t="s">
-        <v>212</v>
-      </c>
       <c r="AL89" t="s">
         <v>1871</v>
       </c>
@@ -52601,9 +50996,6 @@
       <c r="AD90" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE90" t="s">
-        <v>212</v>
-      </c>
       <c r="AL90" t="s">
         <v>2399</v>
       </c>
@@ -52669,9 +51061,6 @@
       <c r="AD91" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE91" t="s">
-        <v>212</v>
-      </c>
       <c r="AL91" t="s">
         <v>1876</v>
       </c>
@@ -52737,9 +51126,6 @@
       <c r="AD92" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE92" t="s">
-        <v>212</v>
-      </c>
       <c r="AL92" t="s">
         <v>1877</v>
       </c>
@@ -52805,9 +51191,6 @@
       <c r="AD93" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE93" t="s">
-        <v>212</v>
-      </c>
       <c r="AL93" t="s">
         <v>1874</v>
       </c>
@@ -52873,9 +51256,6 @@
       <c r="AD94" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE94" t="s">
-        <v>212</v>
-      </c>
       <c r="AL94" t="s">
         <v>2400</v>
       </c>
@@ -52941,9 +51321,6 @@
       <c r="AD95" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE95" t="s">
-        <v>212</v>
-      </c>
       <c r="AL95" t="s">
         <v>1881</v>
       </c>
@@ -53009,9 +51386,6 @@
       <c r="AD96" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE96" t="s">
-        <v>212</v>
-      </c>
       <c r="AL96" t="s">
         <v>2401</v>
       </c>
@@ -53077,9 +51451,6 @@
       <c r="AD97" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE97" t="s">
-        <v>212</v>
-      </c>
       <c r="AL97" t="s">
         <v>1884</v>
       </c>
@@ -53145,9 +51516,6 @@
       <c r="AD98" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE98" t="s">
-        <v>212</v>
-      </c>
       <c r="AL98" t="s">
         <v>1885</v>
       </c>
@@ -53213,9 +51581,6 @@
       <c r="AD99" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE99" t="s">
-        <v>212</v>
-      </c>
       <c r="AL99" t="s">
         <v>2402</v>
       </c>
@@ -53281,9 +51646,6 @@
       <c r="AD100" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE100" t="s">
-        <v>212</v>
-      </c>
       <c r="AL100" t="s">
         <v>2403</v>
       </c>
@@ -53349,9 +51711,6 @@
       <c r="AD101" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE101" t="s">
-        <v>212</v>
-      </c>
       <c r="AL101" t="s">
         <v>1889</v>
       </c>
@@ -53417,9 +51776,6 @@
       <c r="AD102" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE102" t="s">
-        <v>212</v>
-      </c>
       <c r="AL102" t="s">
         <v>2404</v>
       </c>
@@ -53485,9 +51841,6 @@
       <c r="AD103" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE103" t="s">
-        <v>212</v>
-      </c>
       <c r="AL103" t="s">
         <v>1894</v>
       </c>
@@ -53553,9 +51906,6 @@
       <c r="AD104" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE104" t="s">
-        <v>212</v>
-      </c>
       <c r="AL104" t="s">
         <v>1895</v>
       </c>
@@ -53621,9 +51971,6 @@
       <c r="AD105" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE105" t="s">
-        <v>212</v>
-      </c>
       <c r="AL105" t="s">
         <v>2405</v>
       </c>
@@ -53689,9 +52036,6 @@
       <c r="AD106" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE106" t="s">
-        <v>212</v>
-      </c>
       <c r="AL106" t="s">
         <v>2406</v>
       </c>
@@ -53757,9 +52101,6 @@
       <c r="AD107" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE107" t="s">
-        <v>212</v>
-      </c>
       <c r="AL107" t="s">
         <v>1899</v>
       </c>
@@ -53825,9 +52166,6 @@
       <c r="AD108" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE108" t="s">
-        <v>212</v>
-      </c>
       <c r="AL108" t="s">
         <v>2407</v>
       </c>
@@ -53893,9 +52231,6 @@
       <c r="AD109" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE109" t="s">
-        <v>212</v>
-      </c>
       <c r="AL109" t="s">
         <v>1904</v>
       </c>
@@ -53961,9 +52296,6 @@
       <c r="AD110" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE110" t="s">
-        <v>212</v>
-      </c>
       <c r="AL110" t="s">
         <v>1905</v>
       </c>
@@ -54029,9 +52361,6 @@
       <c r="AD111" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE111" t="s">
-        <v>212</v>
-      </c>
       <c r="AL111" t="s">
         <v>2408</v>
       </c>
@@ -54097,9 +52426,6 @@
       <c r="AD112" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE112" t="s">
-        <v>212</v>
-      </c>
       <c r="AL112" t="s">
         <v>2409</v>
       </c>
@@ -54165,9 +52491,6 @@
       <c r="AD113" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE113" t="s">
-        <v>212</v>
-      </c>
       <c r="AL113" t="s">
         <v>1909</v>
       </c>
@@ -54233,9 +52556,6 @@
       <c r="AD114" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE114" t="s">
-        <v>212</v>
-      </c>
       <c r="AL114" t="s">
         <v>1912</v>
       </c>
@@ -54301,9 +52621,6 @@
       <c r="AD115" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE115" t="s">
-        <v>212</v>
-      </c>
       <c r="AL115" t="s">
         <v>1913</v>
       </c>
@@ -54369,9 +52686,6 @@
       <c r="AD116" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE116" t="s">
-        <v>212</v>
-      </c>
       <c r="AL116" t="s">
         <v>1914</v>
       </c>
@@ -54437,9 +52751,6 @@
       <c r="AD117" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE117" t="s">
-        <v>212</v>
-      </c>
       <c r="AL117" t="s">
         <v>1915</v>
       </c>
@@ -54505,9 +52816,6 @@
       <c r="AD118" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE118" t="s">
-        <v>212</v>
-      </c>
       <c r="AL118" t="s">
         <v>1916</v>
       </c>
@@ -54573,9 +52881,6 @@
       <c r="AD119" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE119" t="s">
-        <v>212</v>
-      </c>
       <c r="AL119" t="s">
         <v>1917</v>
       </c>
@@ -54641,9 +52946,6 @@
       <c r="AD120" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE120" t="s">
-        <v>212</v>
-      </c>
       <c r="AL120" t="s">
         <v>2410</v>
       </c>
@@ -54709,9 +53011,6 @@
       <c r="AD121" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE121" t="s">
-        <v>212</v>
-      </c>
       <c r="AL121" t="s">
         <v>1920</v>
       </c>
@@ -54777,9 +53076,6 @@
       <c r="AD122" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE122" t="s">
-        <v>212</v>
-      </c>
       <c r="AL122" t="s">
         <v>1921</v>
       </c>
@@ -54845,9 +53141,6 @@
       <c r="AD123" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE123" t="s">
-        <v>212</v>
-      </c>
       <c r="AL123" t="s">
         <v>2411</v>
       </c>
@@ -54913,9 +53206,6 @@
       <c r="AD124" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE124" t="s">
-        <v>212</v>
-      </c>
       <c r="AL124" t="s">
         <v>2412</v>
       </c>
@@ -54981,9 +53271,6 @@
       <c r="AD125" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE125" t="s">
-        <v>212</v>
-      </c>
       <c r="AL125" t="s">
         <v>1925</v>
       </c>
@@ -55049,9 +53336,6 @@
       <c r="AD126" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE126" t="s">
-        <v>212</v>
-      </c>
       <c r="AL126" t="s">
         <v>1928</v>
       </c>
@@ -55117,9 +53401,6 @@
       <c r="AD127" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE127" t="s">
-        <v>212</v>
-      </c>
       <c r="AL127" t="s">
         <v>1929</v>
       </c>
@@ -55185,9 +53466,6 @@
       <c r="AD128" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE128" t="s">
-        <v>212</v>
-      </c>
       <c r="AL128" t="s">
         <v>2413</v>
       </c>
@@ -55253,9 +53531,6 @@
       <c r="AD129" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE129" t="s">
-        <v>212</v>
-      </c>
       <c r="AL129" t="s">
         <v>2414</v>
       </c>
@@ -55321,9 +53596,6 @@
       <c r="AD130" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE130" t="s">
-        <v>212</v>
-      </c>
       <c r="AL130" t="s">
         <v>2415</v>
       </c>
@@ -55389,9 +53661,6 @@
       <c r="AD131" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE131" t="s">
-        <v>212</v>
-      </c>
       <c r="AL131" t="s">
         <v>1952</v>
       </c>
@@ -55457,9 +53726,6 @@
       <c r="AD132" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE132" t="s">
-        <v>212</v>
-      </c>
       <c r="AL132" t="s">
         <v>2416</v>
       </c>
@@ -55525,9 +53791,6 @@
       <c r="AD133" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE133" t="s">
-        <v>212</v>
-      </c>
       <c r="AL133" t="s">
         <v>2417</v>
       </c>
@@ -55593,9 +53856,6 @@
       <c r="AD134" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE134" t="s">
-        <v>212</v>
-      </c>
       <c r="AL134" t="s">
         <v>2418</v>
       </c>
@@ -55661,9 +53921,6 @@
       <c r="AD135" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE135" t="s">
-        <v>212</v>
-      </c>
       <c r="AL135" t="s">
         <v>2419</v>
       </c>
@@ -55729,9 +53986,6 @@
       <c r="AD136" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE136" t="s">
-        <v>212</v>
-      </c>
       <c r="AL136" t="s">
         <v>2420</v>
       </c>
@@ -55797,9 +54051,6 @@
       <c r="AD137" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE137" t="s">
-        <v>212</v>
-      </c>
       <c r="AL137" t="s">
         <v>2421</v>
       </c>
@@ -55865,9 +54116,6 @@
       <c r="AD138" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE138" t="s">
-        <v>212</v>
-      </c>
       <c r="AL138" t="s">
         <v>1979</v>
       </c>
@@ -55933,9 +54181,6 @@
       <c r="AD139" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE139" t="s">
-        <v>212</v>
-      </c>
       <c r="AL139" t="s">
         <v>2422</v>
       </c>
@@ -56001,9 +54246,6 @@
       <c r="AD140" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE140" t="s">
-        <v>212</v>
-      </c>
       <c r="AL140" t="s">
         <v>2423</v>
       </c>
@@ -56069,9 +54311,6 @@
       <c r="AD141" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE141" t="s">
-        <v>212</v>
-      </c>
       <c r="AL141" t="s">
         <v>2424</v>
       </c>
@@ -56137,9 +54376,6 @@
       <c r="AD142" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE142" t="s">
-        <v>212</v>
-      </c>
       <c r="AL142" t="s">
         <v>2425</v>
       </c>
@@ -56205,9 +54441,6 @@
       <c r="AD143" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE143" t="s">
-        <v>212</v>
-      </c>
       <c r="AL143" t="s">
         <v>2426</v>
       </c>
@@ -56273,9 +54506,6 @@
       <c r="AD144" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE144" t="s">
-        <v>212</v>
-      </c>
       <c r="AL144" t="s">
         <v>2427</v>
       </c>
@@ -56341,9 +54571,6 @@
       <c r="AD145" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE145" t="s">
-        <v>212</v>
-      </c>
       <c r="AL145" t="s">
         <v>2023</v>
       </c>
@@ -56409,9 +54636,6 @@
       <c r="AD146" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE146" t="s">
-        <v>212</v>
-      </c>
       <c r="AL146" t="s">
         <v>2428</v>
       </c>
@@ -56477,9 +54701,6 @@
       <c r="AD147" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE147" t="s">
-        <v>212</v>
-      </c>
       <c r="AL147" t="s">
         <v>2003</v>
       </c>
@@ -56545,9 +54766,6 @@
       <c r="AD148" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE148" t="s">
-        <v>212</v>
-      </c>
       <c r="AL148" t="s">
         <v>2429</v>
       </c>
@@ -56613,9 +54831,6 @@
       <c r="AD149" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE149" t="s">
-        <v>212</v>
-      </c>
       <c r="AL149" t="s">
         <v>2430</v>
       </c>
@@ -56681,9 +54896,6 @@
       <c r="AD150" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="AE150" t="s">
-        <v>212</v>
-      </c>
       <c r="AL150" t="s">
         <v>2017</v>
       </c>
@@ -56748,9 +54960,6 @@
       </c>
       <c r="AD151" s="2" t="s">
         <v>1286</v>
-      </c>
-      <c r="AE151" t="s">
-        <v>212</v>
       </c>
       <c r="AL151" t="s">
         <v>2027</v>

--- a/resources/metadata_process_scripts/sources/catalog.xlsx
+++ b/resources/metadata_process_scripts/sources/catalog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11865" uniqueCount="2446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11862" uniqueCount="2446">
   <si>
     <t>ds:prjTitle</t>
   </si>
@@ -10137,15 +10137,6 @@
       <c r="AD25" t="s">
         <v>205</v>
       </c>
-      <c r="AI25" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ25" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>211</v>
-      </c>
       <c r="AL25" t="s">
         <v>219</v>
       </c>
@@ -10321,9 +10312,8 @@
     <hyperlink ref="B24" r:id="rId60"/>
     <hyperlink ref="C24" r:id="rId61"/>
     <hyperlink ref="B25" r:id="rId62"/>
-    <hyperlink ref="AJ25" r:id="rId63"/>
-    <hyperlink ref="B26" r:id="rId64"/>
-    <hyperlink ref="AJ26" r:id="rId65"/>
+    <hyperlink ref="B26" r:id="rId63"/>
+    <hyperlink ref="AJ26" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
